--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,6 +572,40 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>335</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>176</v>
+      </c>
+      <c r="F5" t="n">
+        <v>119</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -586,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I354"/>
+  <dimension ref="A1:I355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,7 +693,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -699,7 +733,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -739,7 +773,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -779,7 +813,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -819,7 +853,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -859,7 +893,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -899,7 +933,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -939,7 +973,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -979,7 +1013,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1019,7 +1053,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1059,7 +1093,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1099,7 +1133,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1139,7 +1173,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1179,7 +1213,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1219,7 +1253,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1259,7 +1293,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1299,7 +1333,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1339,7 +1373,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1379,7 +1413,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1419,7 +1453,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1489,7 +1523,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1529,7 +1563,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1569,7 +1603,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1609,7 +1643,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -1649,7 +1683,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -1689,7 +1723,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -1729,7 +1763,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -1769,7 +1803,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -1809,7 +1843,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -1849,7 +1883,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -1914,7 +1948,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -1954,7 +1988,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -1994,7 +2028,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2034,7 +2068,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2074,7 +2108,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2114,7 +2148,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2154,7 +2188,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2194,7 +2228,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2234,7 +2268,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2274,7 +2308,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2314,7 +2348,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2354,7 +2388,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2394,7 +2428,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2434,7 +2468,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2474,7 +2508,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2514,7 +2548,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2554,7 +2588,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -2594,7 +2628,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -2634,7 +2668,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -2674,7 +2708,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -2714,7 +2748,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -2784,7 +2818,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -2824,7 +2858,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -2864,7 +2898,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -2904,7 +2938,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -2944,7 +2978,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -2984,7 +3018,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3024,7 +3058,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3064,7 +3098,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3104,7 +3138,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3144,7 +3178,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3184,7 +3218,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3224,7 +3258,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3264,7 +3298,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3304,7 +3338,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3344,7 +3378,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3384,7 +3418,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3424,7 +3458,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3464,7 +3498,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3504,7 +3538,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3544,7 +3578,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -3584,7 +3618,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -3624,7 +3658,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -3664,7 +3698,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -3704,7 +3738,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -3744,7 +3778,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -3784,7 +3818,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -3824,7 +3858,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -3864,7 +3898,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -3899,7 +3933,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -3934,7 +3968,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -3974,7 +4008,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4014,7 +4048,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4054,7 +4088,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4094,7 +4128,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4134,7 +4168,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4174,7 +4208,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4214,7 +4248,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4254,7 +4288,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4294,7 +4328,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4334,7 +4368,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4374,7 +4408,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4414,7 +4448,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4454,7 +4488,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4494,7 +4528,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4534,7 +4568,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -4574,7 +4608,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -4614,7 +4648,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -4654,7 +4688,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -4694,7 +4728,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -4734,7 +4768,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -4774,7 +4808,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -4814,7 +4848,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -4854,7 +4888,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -4894,7 +4928,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -4934,7 +4968,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -4984,27 +5018,27 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>gdfasno.opter.cloud</t>
+          <t>futuremobilityse.opter.cloud</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>gdfasno</t>
+          <t>futuremobilityse</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5012,29 +5046,29 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>gftse.opter.cloud</t>
+          <t>gdfasno.opter.cloud</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>gftse</t>
+          <t>gdfasno</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5044,7 +5078,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5052,7 +5086,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5064,17 +5098,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>gjersundtransportno.opter.cloud</t>
+          <t>gftse.opter.cloud</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>gjersundtransportno</t>
+          <t>gftse</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5084,7 +5118,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5092,7 +5126,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5104,17 +5138,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>globexlinkse.opter.cloud</t>
+          <t>gjersundtransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>globexlinkse</t>
+          <t>gjersundtransportno</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5124,7 +5158,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5132,7 +5166,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5144,12 +5178,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>glogistikse.opter.cloud</t>
+          <t>globexlinkse.opter.cloud</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>glogistikse</t>
+          <t>globexlinkse</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5159,12 +5193,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5177,19 +5211,19 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>godslogistikse.opter.cloud</t>
+          <t>glogistikse.opter.cloud</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>godslogistikse</t>
+          <t>glogistikse</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5199,12 +5233,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5217,19 +5251,19 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>greenbowse.opter.cloud</t>
+          <t>godslogistikse.opter.cloud</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>greenbowse</t>
+          <t>godslogistikse</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -5244,7 +5278,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5264,27 +5298,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>greentechdk.opter.cloud</t>
+          <t>greenbowse.opter.cloud</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>greentechdk</t>
+          <t>greenbowse</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>dk</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5297,34 +5331,34 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>grimsasakerise.opter.cloud</t>
+          <t>greentechdk.opter.cloud</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>grimsasakerise</t>
+          <t>greentechdk</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>dk</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5337,24 +5371,24 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>gstransportno.opter.cloud</t>
+          <t>grimsasakerise.opter.cloud</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>gstransportno</t>
+          <t>grimsasakerise</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5364,7 +5398,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5372,7 +5406,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5384,12 +5418,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>gtlogistikkno.opter.cloud</t>
+          <t>gstransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>gtlogistikkno</t>
+          <t>gstransportno</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -5404,7 +5438,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5424,12 +5458,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>hadelandbudno.opter.cloud</t>
+          <t>gtlogistikkno.opter.cloud</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>hadelandbudno</t>
+          <t>gtlogistikkno</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5444,7 +5478,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5464,17 +5498,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>hajtrpse.opter.cloud</t>
+          <t>hadelandbudno.opter.cloud</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>hajtrpse</t>
+          <t>hadelandbudno</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -5484,7 +5518,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5492,7 +5526,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -5504,12 +5538,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>hardabudse.opter.cloud</t>
+          <t>hajtrpse.opter.cloud</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>hardabudse</t>
+          <t>hajtrpse</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -5524,7 +5558,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5544,12 +5578,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>hardstransse.opter.cloud</t>
+          <t>hardabudse.opter.cloud</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>hardstransse</t>
+          <t>hardabudse</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5564,7 +5598,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -5584,17 +5618,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>harlemno.opter.cloud</t>
+          <t>hardstransse.opter.cloud</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>harlemno</t>
+          <t>hardstransse</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5604,7 +5638,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -5612,7 +5646,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -5624,12 +5658,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>haukeboegassno.opter.cloud</t>
+          <t>harlemno.opter.cloud</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>haukeboegassno</t>
+          <t>harlemno</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5644,7 +5678,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -5664,12 +5698,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>haukeboeno.opter.cloud</t>
+          <t>haukeboegassno.opter.cloud</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>haukeboeno</t>
+          <t>haukeboegassno</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5684,7 +5718,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -5704,12 +5738,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>haukeboetankno.opter.cloud</t>
+          <t>haukeboeno.opter.cloud</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>haukeboetankno</t>
+          <t>haukeboeno</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5724,7 +5758,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -5744,12 +5778,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>helthjemno.opter.cloud</t>
+          <t>haukeboetankno.opter.cloud</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>helthjemno</t>
+          <t>haukeboetankno</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5764,7 +5798,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -5784,27 +5818,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>hemmonktkfi.opter.cloud</t>
+          <t>helthjemno.opter.cloud</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>hemmonktkfi</t>
+          <t>helthjemno</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -5812,29 +5846,29 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>hftabse.opter.cloud</t>
+          <t>hemmonktkfi.opter.cloud</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>hftabse</t>
+          <t>hemmonktkfi</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5844,7 +5878,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -5864,12 +5898,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>hillblomse.opter.cloud</t>
+          <t>hftabse.opter.cloud</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>hillblomse</t>
+          <t>hftabse</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -5879,12 +5913,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -5897,19 +5931,19 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>himmetaakerise.opter.cloud</t>
+          <t>hillblomse.opter.cloud</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>himmetaakerise</t>
+          <t>hillblomse</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -5924,7 +5958,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -5944,12 +5978,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>hlogistikse.opter.cloud</t>
+          <t>himmetaakerise.opter.cloud</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>hlogistikse</t>
+          <t>himmetaakerise</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5959,12 +5993,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -5977,34 +6011,34 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>hogkvistfi.opter.cloud</t>
+          <t>hlogistikse.opter.cloud</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>hogkvistfi</t>
+          <t>hlogistikse</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6017,34 +6051,34 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>holmenstransportse.opter.cloud</t>
+          <t>hogkvistfi.opter.cloud</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>holmenstransportse</t>
+          <t>hogkvistfi</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6057,34 +6091,34 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>holmshippingno.opter.cloud</t>
+          <t>holmenstransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>holmshippingno</t>
+          <t>holmenstransportse</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6092,29 +6126,29 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>hrtransportdk.opter.cloud</t>
+          <t>holmshippingno.opter.cloud</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>hrtransportdk</t>
+          <t>holmshippingno</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>dk</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6122,8 +6156,18 @@
           <t>2026-10-02</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="F140" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>20.251.106.235</t>
+        </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -6134,52 +6178,42 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>hssno.opter.cloud</t>
+          <t>hrtransportdk.opter.cloud</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>hssno</t>
+          <t>hrtransportdk</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dk</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
           <t>2026-10-02</t>
         </is>
       </c>
       <c r="F141" t="b">
-        <v>1</v>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>20.251.106.235</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>hurtigguttano.opter.cloud</t>
+          <t>hssno.opter.cloud</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>hurtigguttano</t>
+          <t>hssno</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -6194,7 +6228,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6214,17 +6248,17 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ibtransportse.opter.cloud</t>
+          <t>hurtigguttano.opter.cloud</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ibtransportse</t>
+          <t>hurtigguttano</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -6234,7 +6268,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6242,7 +6276,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -6254,12 +6288,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>icetransportse.opter.cloud</t>
+          <t>ibtransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>icetransportse</t>
+          <t>ibtransportse</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -6274,7 +6308,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6294,12 +6328,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>intactse.opter.cloud</t>
+          <t>icetransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>intactse</t>
+          <t>icetransportse</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -6314,7 +6348,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6334,17 +6368,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>interspeddk.opter.cloud</t>
+          <t>intactse.opter.cloud</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>interspeddk</t>
+          <t>intactse</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>dk</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -6354,7 +6388,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6374,27 +6408,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>italspedse.opter.cloud</t>
+          <t>interspeddk.opter.cloud</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>italspedse</t>
+          <t>interspeddk</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>dk</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6407,34 +6441,34 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>itideno.opter.cloud</t>
+          <t>italspedse.opter.cloud</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>itideno</t>
+          <t>italspedse</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6442,29 +6476,29 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>jabslse.opter.cloud</t>
+          <t>itideno.opter.cloud</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>jabslse</t>
+          <t>itideno</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -6474,7 +6508,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6482,7 +6516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -6494,17 +6528,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>jakobsentransno.opter.cloud</t>
+          <t>jabslse.opter.cloud</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>jakobsentransno</t>
+          <t>jabslse</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -6514,7 +6548,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6522,7 +6556,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -6534,17 +6568,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>jareksfi.opter.cloud</t>
+          <t>jakobsentransno.opter.cloud</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>jareksfi</t>
+          <t>jakobsentransno</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -6554,7 +6588,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -6562,7 +6596,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -6574,12 +6608,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>jarvimakifi.opter.cloud</t>
+          <t>jareksfi.opter.cloud</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>jarvimakifi</t>
+          <t>jareksfi</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6594,7 +6628,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -6614,17 +6648,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>jessenno.opter.cloud</t>
+          <t>jarvimakifi.opter.cloud</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jessenno</t>
+          <t>jarvimakifi</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -6634,7 +6668,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -6642,7 +6676,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -6654,12 +6688,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>jktransportno.opter.cloud</t>
+          <t>jessenno.opter.cloud</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>jktransportno</t>
+          <t>jessenno</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6674,7 +6708,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -6694,17 +6728,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>jobyhovase.opter.cloud</t>
+          <t>jktransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>jobyhovase</t>
+          <t>jktransportno</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -6714,7 +6748,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -6722,7 +6756,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -6734,17 +6768,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>jotrano.opter.cloud</t>
+          <t>jobyhovase.opter.cloud</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>jotrano</t>
+          <t>jobyhovase</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6754,7 +6788,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -6762,7 +6796,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -6774,12 +6808,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>jpaarsethno.opter.cloud</t>
+          <t>jotrano.opter.cloud</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>jpaarsethno</t>
+          <t>jotrano</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6794,7 +6828,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -6814,17 +6848,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>jpylvainencofi.opter.cloud</t>
+          <t>jpaarsethno.opter.cloud</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>jpylvainencofi</t>
+          <t>jpaarsethno</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -6834,7 +6868,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -6842,7 +6876,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -6854,17 +6888,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>jsakerise.opter.cloud</t>
+          <t>jpylvainencofi.opter.cloud</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>jsakerise</t>
+          <t>jpylvainencofi</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -6874,7 +6908,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -6894,12 +6928,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>jtptransportse.opter.cloud</t>
+          <t>jsakerise.opter.cloud</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>jtptransportse</t>
+          <t>jsakerise</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6914,7 +6948,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -6934,12 +6968,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>jtwtransportse.opter.cloud</t>
+          <t>jtptransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>jtwtransportse</t>
+          <t>jtptransportse</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6954,7 +6988,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -6974,12 +7008,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>julalogisticsse.opter.cloud</t>
+          <t>jtwtransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>julalogisticsse</t>
+          <t>jtwtransportse</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6989,12 +7023,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7007,34 +7041,34 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>jumbotransportno.opter.cloud</t>
+          <t>julalogisticsse.opter.cloud</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>jumbotransportno</t>
+          <t>julalogisticsse</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7042,39 +7076,39 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>jumbotransportse.opter.cloud</t>
+          <t>jumbotransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>jumbotransportse</t>
+          <t>jumbotransportno</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7082,24 +7116,24 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>kaliberse.opter.cloud</t>
+          <t>jumbotransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>kaliberse</t>
+          <t>jumbotransportse</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7114,7 +7148,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7134,12 +7168,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kallesbudse.opter.cloud</t>
+          <t>kaliberse.opter.cloud</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>kallesbudse</t>
+          <t>kaliberse</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -7149,12 +7183,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7167,24 +7201,24 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>karjalaisenfi.opter.cloud</t>
+          <t>kallesbudse.opter.cloud</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>karjalaisenfi</t>
+          <t>kallesbudse</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -7194,7 +7228,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7214,17 +7248,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>karlstadsakerise.opter.cloud</t>
+          <t>karjalaisenfi.opter.cloud</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>karlstadsakerise</t>
+          <t>karjalaisenfi</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -7234,7 +7268,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7254,12 +7288,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>kaubaekspress.opter.cloud</t>
+          <t>karlstadsakerise.opter.cloud</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>kaubaekspress</t>
+          <t>karlstadsakerise</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>se</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -7269,7 +7308,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7289,17 +7328,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>kbtangenno.opter.cloud</t>
+          <t>kaubaekspress.opter.cloud</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>kbtangenno</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>kaubaekspress</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -7309,7 +7343,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7317,7 +7351,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -7329,12 +7363,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>kingsrodno.opter.cloud</t>
+          <t>kbtangenno.opter.cloud</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>kingsrodno</t>
+          <t>kbtangenno</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -7349,7 +7383,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7369,17 +7403,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>kjellandse.opter.cloud</t>
+          <t>kingsrodno.opter.cloud</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>kjellandse</t>
+          <t>kingsrodno</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -7389,7 +7423,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7397,7 +7431,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -7409,12 +7443,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>kjellssonse.opter.cloud</t>
+          <t>kjellandse.opter.cloud</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>kjellssonse</t>
+          <t>kjellandse</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -7429,7 +7463,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7449,12 +7483,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>klevefjordsse.opter.cloud</t>
+          <t>kjellssonse.opter.cloud</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>klevefjordsse</t>
+          <t>kjellssonse</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -7469,7 +7503,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7489,17 +7523,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>kolsbyno.opter.cloud</t>
+          <t>klevefjordsse.opter.cloud</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>kolsbyno</t>
+          <t>klevefjordsse</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -7509,7 +7543,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7517,7 +7551,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -7529,12 +7563,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kpmtransportno.opter.cloud</t>
+          <t>kolsbyno.opter.cloud</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>kpmtransportno</t>
+          <t>kolsbyno</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -7549,7 +7583,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -7569,27 +7603,27 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>krpee.opter.cloud</t>
+          <t>kpmtransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>krpee</t>
+          <t>kpmtransportno</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ee</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -7597,39 +7631,39 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>kslogisticsfi.opter.cloud</t>
+          <t>krpee.opter.cloud</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>kslogisticsfi</t>
+          <t>krpee</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>ee</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -7642,34 +7676,34 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ktno.opter.cloud</t>
+          <t>kslogisticsfi.opter.cloud</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ktno</t>
+          <t>kslogisticsfi</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -7677,29 +7711,29 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>kungsbudse.opter.cloud</t>
+          <t>ktno.opter.cloud</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>kungsbudse</t>
+          <t>ktno</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -7709,7 +7743,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -7717,7 +7751,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -7729,17 +7763,17 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>kurtsimonsenno.opter.cloud</t>
+          <t>kungsbudse.opter.cloud</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>kurtsimonsenno</t>
+          <t>kungsbudse</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -7747,8 +7781,18 @@
           <t>2026-10-02</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="F181" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>74.241.233.90</t>
+        </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -7759,12 +7803,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kvikkbagno.opter.cloud</t>
+          <t>kurtsimonsenno.opter.cloud</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>kvikkbagno</t>
+          <t>kurtsimonsenno</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -7774,37 +7818,27 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
           <t>2026-10-02</t>
         </is>
       </c>
       <c r="F182" t="b">
-        <v>1</v>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>20.251.106.235</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kystbudetno.opter.cloud</t>
+          <t>kvikkbagno.opter.cloud</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>kystbudetno</t>
+          <t>kvikkbagno</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -7819,7 +7853,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -7839,17 +7873,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>landetruntse.opter.cloud</t>
+          <t>kystbudetno.opter.cloud</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>landetruntse</t>
+          <t>kystbudetno</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -7859,7 +7893,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -7867,7 +7901,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -7879,17 +7913,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>lansiofi.opter.cloud</t>
+          <t>landetruntse.opter.cloud</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>lansiofi</t>
+          <t>landetruntse</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -7899,7 +7933,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -7919,17 +7953,17 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>larssonakerise.opter.cloud</t>
+          <t>lansiofi.opter.cloud</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>larssonakerise</t>
+          <t>lansiofi</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -7939,7 +7973,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -7959,17 +7993,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>leirvikvaretaxino.opter.cloud</t>
+          <t>larssonakerise.opter.cloud</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>leirvikvaretaxino</t>
+          <t>larssonakerise</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -7979,7 +8013,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -7987,7 +8021,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -7999,17 +8033,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>linjegodsse.opter.cloud</t>
+          <t>leirvikvaretaxino.opter.cloud</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>linjegodsse</t>
+          <t>leirvikvaretaxino</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -8019,7 +8053,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8027,7 +8061,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -8039,82 +8073,82 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>liuttu.opter.cloud</t>
+          <t>linjegodsse.opter.cloud</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>liuttu</t>
+          <t>linjegodsse</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>se</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F189" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>74.241.233.90</t>
+        </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>passive_dns</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>lkptransportse.opter.cloud</t>
+          <t>liuttu.opter.cloud</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>lkptransportse</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>se</t>
+          <t>liuttu</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F190" t="b">
-        <v>1</v>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>74.241.233.90</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>passive_dns</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>loadmasterno.opter.cloud</t>
+          <t>lkptransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>loadmasterno</t>
+          <t>lkptransportse</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -8124,7 +8158,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8132,7 +8166,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -8144,17 +8178,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>loffesse.opter.cloud</t>
+          <t>loadmasterno.opter.cloud</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>loffesse</t>
+          <t>loadmasterno</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -8164,7 +8198,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8172,7 +8206,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -8184,12 +8218,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>lofgrentransportse.opter.cloud</t>
+          <t>loffesse.opter.cloud</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>lofgrentransportse</t>
+          <t>loffesse</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -8199,12 +8233,12 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8217,19 +8251,19 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>logsltse.opter.cloud</t>
+          <t>lofgrentransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>logsltse</t>
+          <t>lofgrentransportse</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -8239,12 +8273,12 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8257,19 +8291,19 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>logsse.opter.cloud</t>
+          <t>logsltse.opter.cloud</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>logsse</t>
+          <t>logsltse</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -8284,16 +8318,11 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F195" t="b">
-        <v>0</v>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -8309,12 +8338,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>loodsakerise.opter.cloud</t>
+          <t>logsse.opter.cloud</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>loodsakerise</t>
+          <t>logsse</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8329,11 +8358,16 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="F196" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -8349,17 +8383,17 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>lrnno.opter.cloud</t>
+          <t>loodsakerise.opter.cloud</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>lrnno</t>
+          <t>loodsakerise</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -8369,7 +8403,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8377,7 +8411,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -8389,17 +8423,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ltsjonkopingse.opter.cloud</t>
+          <t>lrnno.opter.cloud</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ltsjonkopingse</t>
+          <t>lrnno</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -8409,7 +8443,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8417,7 +8451,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -8429,12 +8463,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>lundbyakse.opter.cloud</t>
+          <t>ltsjonkopingse.opter.cloud</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>lundbyakse</t>
+          <t>ltsjonkopingse</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8444,27 +8478,37 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F199" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>74.241.233.90</t>
+        </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>passive_dns</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>lundgrense.opter.cloud</t>
+          <t>lundbyakse.opter.cloud</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>lundgrense</t>
+          <t>lundbyakse</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8474,37 +8518,27 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F200" t="b">
-        <v>1</v>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>74.241.233.90</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>passive_dns</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>lundintransportse.opter.cloud</t>
+          <t>lundgrense.opter.cloud</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>lundintransportse</t>
+          <t>lundgrense</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -8519,7 +8553,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -8539,17 +8573,17 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>maksino.opter.cloud</t>
+          <t>lundintransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>maksino</t>
+          <t>lundintransportse</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -8559,7 +8593,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -8567,7 +8601,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -8579,27 +8613,27 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>malmoflygfraktse.opter.cloud</t>
+          <t>maksino.opter.cloud</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>malmoflygfraktse</t>
+          <t>maksino</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -8607,24 +8641,24 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>maltidsfabrikense.opter.cloud</t>
+          <t>malmoflygfraktse.opter.cloud</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>maltidsfabrikense</t>
+          <t>malmoflygfraktse</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -8634,12 +8668,12 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -8652,19 +8686,19 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>manlogistikse.opter.cloud</t>
+          <t>maltidsfabrikense.opter.cloud</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>manlogistikse</t>
+          <t>maltidsfabrikense</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -8674,12 +8708,12 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -8692,19 +8726,19 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>mantorptrpse.opter.cloud</t>
+          <t>manlogistikse.opter.cloud</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>mantorptrpse</t>
+          <t>manlogistikse</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -8714,12 +8748,12 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -8732,19 +8766,19 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>mantumse.opter.cloud</t>
+          <t>mantorptrpse.opter.cloud</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>mantumse</t>
+          <t>mantorptrpse</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -8754,12 +8788,12 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -8772,19 +8806,19 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>mantumspecialse.opter.cloud</t>
+          <t>mantumse.opter.cloud</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>mantumspecialse</t>
+          <t>mantumse</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -8799,7 +8833,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -8819,87 +8853,87 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>miniexpressdk.opter.cloud</t>
+          <t>mantumspecialse.opter.cloud</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>miniexpressdk</t>
+          <t>mantumspecialse</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>dk</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F209" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>74.241.233.90</t>
+        </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>mixorfi.opter.cloud</t>
+          <t>miniexpressdk.opter.cloud</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>mixorfi</t>
+          <t>miniexpressdk</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>dk</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
           <t>2026-10-02</t>
         </is>
       </c>
       <c r="F210" t="b">
-        <v>1</v>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>74.241.233.90</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>mkrlogistikse.opter.cloud</t>
+          <t>mixorfi.opter.cloud</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>mkrlogistikse</t>
+          <t>mixorfi</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -8909,7 +8943,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -8929,12 +8963,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>mktse.opter.cloud</t>
+          <t>mkrlogistikse.opter.cloud</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>mktse</t>
+          <t>mkrlogistikse</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8944,12 +8978,12 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -8962,34 +8996,34 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>mobeldriftno.opter.cloud</t>
+          <t>mktse.opter.cloud</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>mobeldriftno</t>
+          <t>mktse</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -8997,24 +9031,24 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>mobelfraktno.opter.cloud</t>
+          <t>mobeldriftno.opter.cloud</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>mobelfraktno</t>
+          <t>mobeldriftno</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9029,7 +9063,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9049,12 +9083,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>mokkenhaugtransportno.opter.cloud</t>
+          <t>mobelfraktno.opter.cloud</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>mokkenhaugtransportno</t>
+          <t>mobelfraktno</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9069,7 +9103,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9089,12 +9123,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>mordaltransportno.opter.cloud</t>
+          <t>mokkenhaugtransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>mordaltransportno</t>
+          <t>mokkenhaugtransportno</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9109,7 +9143,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9129,17 +9163,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>movatorse.opter.cloud</t>
+          <t>mordaltransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>movatorse</t>
+          <t>mordaltransportno</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -9149,7 +9183,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9157,7 +9191,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -9169,12 +9203,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>mpcargose.opter.cloud</t>
+          <t>movatorse.opter.cloud</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>mpcargose</t>
+          <t>movatorse</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -9184,12 +9218,12 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9202,19 +9236,19 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>mrexpressse.opter.cloud</t>
+          <t>mpcargose.opter.cloud</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>mrexpressse</t>
+          <t>mpcargose</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -9224,12 +9258,12 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9242,19 +9276,19 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>mrlogistikse.opter.cloud</t>
+          <t>mrexpressse.opter.cloud</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>mrlogistikse</t>
+          <t>mrexpressse</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -9269,7 +9303,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9289,17 +9323,17 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>namdaltransportno.opter.cloud</t>
+          <t>mrlogistikse.opter.cloud</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>namdaltransportno</t>
+          <t>mrlogistikse</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -9309,7 +9343,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9317,7 +9351,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -9329,17 +9363,17 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>nausakerise.opter.cloud</t>
+          <t>namdaltransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>nausakerise</t>
+          <t>namdaltransportno</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -9349,7 +9383,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9357,7 +9391,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -9369,17 +9403,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>nemotransportno.opter.cloud</t>
+          <t>nausakerise.opter.cloud</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>nemotransportno</t>
+          <t>nausakerise</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -9389,7 +9423,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9397,7 +9431,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -9409,17 +9443,17 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>nipfraktse.opter.cloud</t>
+          <t>nemotransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>nipfraktse</t>
+          <t>nemotransportno</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -9429,7 +9463,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9437,7 +9471,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -9449,27 +9483,27 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>nnspedno.opter.cloud</t>
+          <t>nipfraktse.opter.cloud</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>nnspedno</t>
+          <t>nipfraktse</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9477,24 +9511,24 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>norbaseno.opter.cloud</t>
+          <t>nnspedno.opter.cloud</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>norbaseno</t>
+          <t>nnspedno</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -9504,12 +9538,12 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9522,34 +9556,34 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>nordicontruckingse.opter.cloud</t>
+          <t>norbaseno.opter.cloud</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>nordicontruckingse</t>
+          <t>norbaseno</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -9557,39 +9591,39 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>nordicthermofi.opter.cloud</t>
+          <t>nordicontruckingse.opter.cloud</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>nordicthermofi</t>
+          <t>nordicontruckingse</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -9602,24 +9636,24 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>nordlysno.opter.cloud</t>
+          <t>nordicthermofi.opter.cloud</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>nordlysno</t>
+          <t>nordicthermofi</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -9629,7 +9663,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -9637,7 +9671,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -9649,17 +9683,17 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>nordstromsse.opter.cloud</t>
+          <t>nordlysno.opter.cloud</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>nordstromsse</t>
+          <t>nordlysno</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -9669,7 +9703,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -9677,7 +9711,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -9689,17 +9723,17 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>nordtrafikkno.opter.cloud</t>
+          <t>nordstromsse.opter.cloud</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>nordtrafikkno</t>
+          <t>nordstromsse</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -9709,7 +9743,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -9717,7 +9751,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -9729,17 +9763,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>norense.opter.cloud</t>
+          <t>nordtrafikkno.opter.cloud</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>norense</t>
+          <t>nordtrafikkno</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -9749,7 +9783,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -9757,7 +9791,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -9769,17 +9803,17 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>norfragtdk.opter.cloud</t>
+          <t>norense.opter.cloud</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>norfragtdk</t>
+          <t>norense</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>dk</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -9789,7 +9823,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -9809,17 +9843,17 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>norfraktno.opter.cloud</t>
+          <t>norfragtdk.opter.cloud</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>norfraktno</t>
+          <t>norfragtdk</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dk</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -9829,7 +9863,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -9837,7 +9871,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -9849,17 +9883,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>norrbudetexpressse.opter.cloud</t>
+          <t>norfraktno.opter.cloud</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>norrbudetexpressse</t>
+          <t>norfraktno</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -9869,20 +9903,15 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F235" t="b">
-        <v>0</v>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -9894,12 +9923,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>norrsjose.opter.cloud</t>
+          <t>norrbudetexpressse.opter.cloud</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>norrsjose</t>
+          <t>norrbudetexpressse</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -9909,17 +9938,22 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="F236" t="b">
+        <v>0</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="F236" t="b">
-        <v>1</v>
-      </c>
       <c r="H236" t="inlineStr">
         <is>
           <t>74.241.233.90</t>
@@ -9927,34 +9961,34 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>norspeedno.opter.cloud</t>
+          <t>norrsjose.opter.cloud</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>norspeedno</t>
+          <t>norrsjose</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -9962,24 +9996,24 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>norsteveno.opter.cloud</t>
+          <t>norspeedno.opter.cloud</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>norsteveno</t>
+          <t>norspeedno</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -9994,7 +10028,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10014,22 +10048,27 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>nwtsweden.opter.cloud</t>
+          <t>norsteveno.opter.cloud</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>nwtsweden</t>
+          <t>norsteveno</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10037,39 +10076,34 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>oalogistikse.opter.cloud</t>
+          <t>nwtsweden.opter.cloud</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>oalogistikse</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>se</t>
+          <t>nwtsweden</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10082,19 +10116,19 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ohrlundsse.opter.cloud</t>
+          <t>oalogistikse.opter.cloud</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>ohrlundsse</t>
+          <t>oalogistikse</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -10109,7 +10143,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10129,17 +10163,17 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>okjtransportno.opter.cloud</t>
+          <t>ohrlundsse.opter.cloud</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>okjtransportno</t>
+          <t>ohrlundsse</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -10149,7 +10183,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10157,7 +10191,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -10169,17 +10203,17 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ollepsakerise.opter.cloud</t>
+          <t>okjtransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>ollepsakerise</t>
+          <t>okjtransportno</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -10189,7 +10223,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10197,7 +10231,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -10209,12 +10243,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>olssonsse.opter.cloud</t>
+          <t>ollepsakerise.opter.cloud</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>olssonsse</t>
+          <t>ollepsakerise</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -10229,7 +10263,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10249,17 +10283,17 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>omdaltransportno.opter.cloud</t>
+          <t>olssonsse.opter.cloud</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>omdaltransportno</t>
+          <t>olssonsse</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -10269,7 +10303,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10277,7 +10311,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -10289,17 +10323,17 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>orebroflyttse.opter.cloud</t>
+          <t>omdaltransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>orebroflyttse</t>
+          <t>omdaltransportno</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -10309,7 +10343,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10317,7 +10351,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -10329,17 +10363,17 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>orlandno.opter.cloud</t>
+          <t>orebroflyttse.opter.cloud</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>orlandno</t>
+          <t>orebroflyttse</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -10349,7 +10383,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10357,7 +10391,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -10369,27 +10403,27 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ostervallsse.opter.cloud</t>
+          <t>orlandno.opter.cloud</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ostervallsse</t>
+          <t>orlandno</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10397,39 +10431,39 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ostkranno.opter.cloud</t>
+          <t>ostervallsse.opter.cloud</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ostkranno</t>
+          <t>ostervallsse</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10437,24 +10471,24 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>otransno.opter.cloud</t>
+          <t>ostkranno.opter.cloud</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>otransno</t>
+          <t>ostkranno</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -10469,7 +10503,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10489,27 +10523,27 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ottenbyse.opter.cloud</t>
+          <t>otransno.opter.cloud</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ottenbyse</t>
+          <t>otransno</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10517,39 +10551,39 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>overhallatransportno.opter.cloud</t>
+          <t>ottenbyse.opter.cloud</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>overhallatransportno</t>
+          <t>ottenbyse</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -10557,29 +10591,29 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>pallcargose.opter.cloud</t>
+          <t>overhallatransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>pallcargose</t>
+          <t>overhallatransportno</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -10589,7 +10623,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -10597,7 +10631,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -10609,12 +10643,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>pantraxxse.opter.cloud</t>
+          <t>pallcargose.opter.cloud</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>pantraxxse</t>
+          <t>pallcargose</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -10629,7 +10663,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -10649,12 +10683,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>partillekyltransportse.opter.cloud</t>
+          <t>pantraxxse.opter.cloud</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>partillekyltransportse</t>
+          <t>pantraxxse</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -10664,72 +10698,72 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F255" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>74.241.233.90</t>
+        </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>pedersentransportno.opter.cloud</t>
+          <t>partillekyltransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>pedersentransportno</t>
+          <t>partillekyltransportse</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
           <t>2026-10-02</t>
         </is>
       </c>
       <c r="F256" t="b">
-        <v>1</v>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>20.251.106.235</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>perftransse.opter.cloud</t>
+          <t>pedersentransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>perftransse</t>
+          <t>pedersentransportno</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -10739,7 +10773,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -10747,7 +10781,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -10759,12 +10793,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>pgtransportse.opter.cloud</t>
+          <t>perftransse.opter.cloud</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>pgtransportse</t>
+          <t>perftransse</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -10779,7 +10813,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -10799,17 +10833,17 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>piccolofi.opter.cloud</t>
+          <t>pgtransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>piccolofi</t>
+          <t>pgtransportse</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -10819,7 +10853,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -10839,17 +10873,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>pleymstransportno.opter.cloud</t>
+          <t>piccolofi.opter.cloud</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>pleymstransportno</t>
+          <t>piccolofi</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -10859,7 +10893,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -10867,7 +10901,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -10879,17 +10913,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>pohjolalogfi.opter.cloud</t>
+          <t>pleymstransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>pohjolalogfi</t>
+          <t>pleymstransportno</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -10899,7 +10933,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -10907,7 +10941,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -10919,17 +10953,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>prolineno.opter.cloud</t>
+          <t>pohjolalogfi.opter.cloud</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>prolineno</t>
+          <t>pohjolalogfi</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -10939,7 +10973,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -10947,7 +10981,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -10959,12 +10993,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>quickno.opter.cloud</t>
+          <t>prolineno.opter.cloud</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>quickno</t>
+          <t>prolineno</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -10979,7 +11013,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -10999,17 +11033,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>rbfraktse.opter.cloud</t>
+          <t>quickno.opter.cloud</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>rbfraktse</t>
+          <t>quickno</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -11019,7 +11053,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11027,7 +11061,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -11039,12 +11073,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>rbftransportse.opter.cloud</t>
+          <t>rbfraktse.opter.cloud</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>rbftransportse</t>
+          <t>rbfraktse</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -11059,7 +11093,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11079,12 +11113,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>rblogistikse.opter.cloud</t>
+          <t>rbftransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>rblogistikse</t>
+          <t>rbftransportse</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -11099,7 +11133,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11119,12 +11153,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>redningsverket.opter.cloud</t>
+          <t>rblogistikse.opter.cloud</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>redningsverket</t>
+          <t>rblogistikse</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>se</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -11134,7 +11173,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11142,7 +11181,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -11154,17 +11193,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>riksbudse.opter.cloud</t>
+          <t>redningsverket.opter.cloud</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>riksbudse</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>se</t>
+          <t>redningsverket</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -11174,7 +11208,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11182,7 +11216,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -11194,12 +11228,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>rologisticsse.opter.cloud</t>
+          <t>riksbudse.opter.cloud</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>rologisticsse</t>
+          <t>riksbudse</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -11214,7 +11248,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11234,12 +11268,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>roxtransse.opter.cloud</t>
+          <t>rologisticsse.opter.cloud</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>roxtransse</t>
+          <t>rologisticsse</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -11254,7 +11288,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11274,17 +11308,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>royaltransportno.opter.cloud</t>
+          <t>roxtransse.opter.cloud</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>royaltransportno</t>
+          <t>roxtransse</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -11294,7 +11328,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11302,7 +11336,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -11314,17 +11348,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ryskapostense.opter.cloud</t>
+          <t>royaltransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>ryskapostense</t>
+          <t>royaltransportno</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -11334,7 +11368,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11342,7 +11376,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -11354,12 +11388,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>sabomsse.opter.cloud</t>
+          <t>ryskapostense.opter.cloud</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>sabomsse</t>
+          <t>ryskapostense</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -11369,12 +11403,12 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11387,34 +11421,34 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>samtransportno.opter.cloud</t>
+          <t>sabomsse.opter.cloud</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>samtransportno</t>
+          <t>sabomsse</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11422,24 +11456,29 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>se247logistics.opter.cloud</t>
+          <t>samtransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>se247logistics</t>
+          <t>samtransportno</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -11449,7 +11488,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11457,7 +11496,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -11469,17 +11508,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>seafoodlogisticsno.opter.cloud</t>
+          <t>se247logistics.opter.cloud</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>seafoodlogisticsno</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>se247logistics</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -11489,7 +11523,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11497,7 +11531,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -11509,12 +11543,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>seafrontno.opter.cloud</t>
+          <t>seafoodlogisticsno.opter.cloud</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>seafrontno</t>
+          <t>seafoodlogisticsno</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -11529,7 +11563,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -11549,27 +11583,27 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>septlogse.opter.cloud</t>
+          <t>seafrontno.opter.cloud</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>septlogse</t>
+          <t>seafrontno</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -11577,39 +11611,39 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>skaugtransportno.opter.cloud</t>
+          <t>septlogse.opter.cloud</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>skaugtransportno</t>
+          <t>septlogse</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -11617,29 +11651,29 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>skubbetse.opter.cloud</t>
+          <t>skaugtransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>skubbetse</t>
+          <t>skaugtransportno</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -11649,7 +11683,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -11657,7 +11691,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -11669,17 +11703,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>slaslettenno.opter.cloud</t>
+          <t>skubbetse.opter.cloud</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>slaslettenno</t>
+          <t>skubbetse</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -11689,7 +11723,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -11697,7 +11731,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -11709,12 +11743,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>slindetransportno.opter.cloud</t>
+          <t>slaslettenno.opter.cloud</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>slindetransportno</t>
+          <t>slaslettenno</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -11729,7 +11763,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -11749,12 +11783,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>smadyrkrematorietno.opter.cloud</t>
+          <t>slindetransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>smadyrkrematorietno</t>
+          <t>slindetransportno</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -11764,12 +11798,12 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -11782,34 +11816,34 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>smafraktse.opter.cloud</t>
+          <t>smadyrkrematorietno.opter.cloud</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>smafraktse</t>
+          <t>smadyrkrematorietno</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -11817,24 +11851,24 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>sodervallsexpressse.opter.cloud</t>
+          <t>smafraktse.opter.cloud</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>sodervallsexpressse</t>
+          <t>smafraktse</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -11844,12 +11878,12 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -11862,34 +11896,34 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>sorumtransportno.opter.cloud</t>
+          <t>sodervallsexpressse.opter.cloud</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>sorumtransportno</t>
+          <t>sodervallsexpressse</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -11897,24 +11931,24 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>speditorenno.opter.cloud</t>
+          <t>sorumtransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>speditorenno</t>
+          <t>sorumtransportno</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -11924,72 +11958,72 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F287" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>20.251.106.235</t>
+        </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>passive_dns</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>sslogse.opter.cloud</t>
+          <t>speditorenno.opter.cloud</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>sslogse</t>
+          <t>speditorenno</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F288" t="b">
-        <v>1</v>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>74.241.233.90</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>passive_dns</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>storemenfi.opter.cloud</t>
+          <t>sslogse.opter.cloud</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>storemenfi</t>
+          <t>sslogse</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -11999,7 +12033,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12019,17 +12053,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>surnflodtno.opter.cloud</t>
+          <t>storemenfi.opter.cloud</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>surnflodtno</t>
+          <t>storemenfi</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -12039,7 +12073,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12047,7 +12081,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -12059,12 +12093,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>sutrano.opter.cloud</t>
+          <t>surnflodtno.opter.cloud</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>sutrano</t>
+          <t>surnflodtno</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -12079,7 +12113,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12099,17 +12133,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>svedalacargose.opter.cloud</t>
+          <t>sutrano.opter.cloud</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>svedalacargose</t>
+          <t>sutrano</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -12119,7 +12153,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12127,7 +12161,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -12139,12 +12173,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>svedalalogabse.opter.cloud</t>
+          <t>svedalacargose.opter.cloud</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>svedalalogabse</t>
+          <t>svedalacargose</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -12154,67 +12188,67 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F293" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>74.241.233.90</t>
+        </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>svippno.opter.cloud</t>
+          <t>svedalalogabse.opter.cloud</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>svippno</t>
+          <t>svedalalogabse</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
-        <is>
           <t>2026-10-02</t>
         </is>
       </c>
       <c r="F294" t="b">
-        <v>1</v>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>20.251.106.235</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>systemtrafikkno.opter.cloud</t>
+          <t>svippno.opter.cloud</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>systemtrafikkno</t>
+          <t>svippno</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -12229,7 +12263,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12249,17 +12283,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>tabergsakerise.opter.cloud</t>
+          <t>systemtrafikkno.opter.cloud</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>tabergsakerise</t>
+          <t>systemtrafikkno</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -12269,7 +12303,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12277,7 +12311,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -12289,17 +12323,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>tavaralahetitfi.opter.cloud</t>
+          <t>tabergsakerise.opter.cloud</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>tavaralahetitfi</t>
+          <t>tabergsakerise</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -12309,7 +12343,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12329,17 +12363,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>tbsno.opter.cloud</t>
+          <t>tavaralahetitfi.opter.cloud</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>tbsno</t>
+          <t>tavaralahetitfi</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -12349,7 +12383,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12357,7 +12391,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -12369,17 +12403,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>tbspecialse.opter.cloud</t>
+          <t>tbsno.opter.cloud</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>tbspecialse</t>
+          <t>tbsno</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -12389,7 +12423,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12397,7 +12431,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -12409,17 +12443,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>tctasno.opter.cloud</t>
+          <t>tbspecialse.opter.cloud</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>tctasno</t>
+          <t>tbspecialse</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -12429,7 +12463,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12437,7 +12471,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -12449,12 +12483,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>tdi24hno.opter.cloud</t>
+          <t>tctasno.opter.cloud</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>tdi24hno</t>
+          <t>tctasno</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -12469,7 +12503,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12489,12 +12523,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>teatransno.opter.cloud</t>
+          <t>tdi24hno.opter.cloud</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>teatransno</t>
+          <t>tdi24hno</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -12509,7 +12543,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12529,12 +12563,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>teraxno.opter.cloud</t>
+          <t>teatransno.opter.cloud</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>teraxno</t>
+          <t>teatransno</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -12549,7 +12583,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -12569,12 +12603,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>termoxpressno.opter.cloud</t>
+          <t>teraxno.opter.cloud</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>termoxpressno</t>
+          <t>teraxno</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -12589,7 +12623,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -12609,17 +12643,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>thorinsakerise.opter.cloud</t>
+          <t>termoxpressno.opter.cloud</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>thorinsakerise</t>
+          <t>termoxpressno</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -12629,7 +12663,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -12637,7 +12671,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -12649,17 +12683,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>timosalofi.opter.cloud</t>
+          <t>thorinsakerise.opter.cloud</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>timosalofi</t>
+          <t>thorinsakerise</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -12669,7 +12703,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -12689,17 +12723,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>tipptransportno.opter.cloud</t>
+          <t>timosalofi.opter.cloud</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>tipptransportno</t>
+          <t>timosalofi</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -12709,7 +12743,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -12717,7 +12751,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -12729,27 +12763,27 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>tipptransportse.opter.cloud</t>
+          <t>tipptransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>tipptransportse</t>
+          <t>tipptransportno</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -12757,24 +12791,24 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>tklogistikse.opter.cloud</t>
+          <t>tipptransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>tklogistikse</t>
+          <t>tipptransportse</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -12789,7 +12823,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -12809,27 +12843,27 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>tnrspedisjonno.opter.cloud</t>
+          <t>tklogistikse.opter.cloud</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>tnrspedisjonno</t>
+          <t>tklogistikse</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -12837,29 +12871,29 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>tonysbudbilse.opter.cloud</t>
+          <t>tnrspedisjonno.opter.cloud</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>tonysbudbilse</t>
+          <t>tnrspedisjonno</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -12869,7 +12903,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -12877,7 +12911,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -12889,12 +12923,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>tornfraktse.opter.cloud</t>
+          <t>tonysbudbilse.opter.cloud</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>tornfraktse</t>
+          <t>tonysbudbilse</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -12909,7 +12943,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -12929,17 +12963,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>torpabilruterno.opter.cloud</t>
+          <t>tornfraktse.opter.cloud</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>torpabilruterno</t>
+          <t>tornfraktse</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -12949,7 +12983,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -12957,7 +12991,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -12969,12 +13003,12 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>torplogisticsno.opter.cloud</t>
+          <t>torpabilruterno.opter.cloud</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>torplogisticsno</t>
+          <t>torpabilruterno</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -12984,27 +13018,37 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F314" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>20.251.106.235</t>
+        </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>passive_dns</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>totenno.opter.cloud</t>
+          <t>torplogisticsno.opter.cloud</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>totenno</t>
+          <t>torplogisticsno</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -13014,52 +13058,42 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F315" t="b">
-        <v>1</v>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>20.251.106.235</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>passive_dns</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>totentransportse.opter.cloud</t>
+          <t>totenno.opter.cloud</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>totentransportse</t>
+          <t>totenno</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13067,39 +13101,39 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>tothno.opter.cloud</t>
+          <t>totentransportse.opter.cloud</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>tothno</t>
+          <t>totentransportse</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13107,39 +13141,39 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>tpse.opter.cloud</t>
+          <t>tothno.opter.cloud</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>tpse</t>
+          <t>tothno</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13147,24 +13181,24 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>traentse.opter.cloud</t>
+          <t>tpse.opter.cloud</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>traentse</t>
+          <t>tpse</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -13174,12 +13208,12 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13192,19 +13226,19 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>trafraktse.opter.cloud</t>
+          <t>traentse.opter.cloud</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>trafraktse</t>
+          <t>traentse</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -13214,12 +13248,12 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13232,34 +13266,34 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>transmarkee.opter.cloud</t>
+          <t>trafraktse.opter.cloud</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>transmarkee</t>
+          <t>trafraktse</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>ee</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13272,34 +13306,34 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>transportformedlarnase.opter.cloud</t>
+          <t>transmarkee.opter.cloud</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>transportformedlarnase</t>
+          <t>transmarkee</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>ee</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13312,34 +13346,34 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>trondheimtermno.opter.cloud</t>
+          <t>transportformedlarnase.opter.cloud</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>trondheimtermno</t>
+          <t>transportformedlarnase</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13347,24 +13381,24 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>tstromsono.opter.cloud</t>
+          <t>trondheimtermno.opter.cloud</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>tstromsono</t>
+          <t>trondheimtermno</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -13379,7 +13413,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13399,12 +13433,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>tsverdalno.opter.cloud</t>
+          <t>tstromsono.opter.cloud</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>tsverdalno</t>
+          <t>tstromsono</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -13419,7 +13453,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13439,17 +13473,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>tuomifi.opter.cloud</t>
+          <t>tsverdalno.opter.cloud</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>tuomifi</t>
+          <t>tsverdalno</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -13459,7 +13493,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13467,7 +13501,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -13479,12 +13513,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>tupekufi.opter.cloud</t>
+          <t>tuomifi.opter.cloud</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>tupekufi</t>
+          <t>tuomifi</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -13499,7 +13533,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13519,17 +13553,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ulviktransportutleieno.opter.cloud</t>
+          <t>tupekufi.opter.cloud</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>ulviktransportutleieno</t>
+          <t>tupekufi</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -13539,7 +13573,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -13547,7 +13581,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -13559,17 +13593,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>unilastse.opter.cloud</t>
+          <t>ulviktransportutleieno.opter.cloud</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>unilastse</t>
+          <t>ulviktransportutleieno</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -13579,7 +13613,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -13587,7 +13621,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -13599,12 +13633,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>uppdragetse.opter.cloud</t>
+          <t>unilastse.opter.cloud</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>uppdragetse</t>
+          <t>unilastse</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -13619,7 +13653,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -13639,12 +13673,12 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>uppsalaakerise.opter.cloud</t>
+          <t>uppdragetse.opter.cloud</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>uppsalaakerise</t>
+          <t>uppdragetse</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -13654,82 +13688,82 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F331" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>74.241.233.90</t>
+        </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>utengenno.opter.cloud</t>
+          <t>uppsalaakerise.opter.cloud</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>utengenno</t>
+          <t>uppsalaakerise</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="E332" t="inlineStr">
-        <is>
           <t>2026-10-02</t>
         </is>
       </c>
       <c r="F332" t="b">
-        <v>1</v>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>20.251.106.235</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>uttse.opter.cloud</t>
+          <t>utengenno.opter.cloud</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>uttse</t>
+          <t>utengenno</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -13737,39 +13771,39 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>uudenmaanfi.opter.cloud</t>
+          <t>uttse.opter.cloud</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>uudenmaanfi</t>
+          <t>uttse</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>fi</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -13782,24 +13816,24 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>valdrestransportno.opter.cloud</t>
+          <t>uudenmaanfi.opter.cloud</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>valdrestransportno</t>
+          <t>uudenmaanfi</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>fi</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -13809,7 +13843,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -13817,7 +13851,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -13829,17 +13863,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>varubudse.opter.cloud</t>
+          <t>valdrestransportno.opter.cloud</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>varubudse</t>
+          <t>valdrestransportno</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -13849,7 +13883,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -13857,7 +13891,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -13869,27 +13903,27 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>vegaspeditiondk.opter.cloud</t>
+          <t>varubudse.opter.cloud</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>vegaspeditiondk</t>
+          <t>varubudse</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>dk</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -13902,34 +13936,34 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>verdalkranno.opter.cloud</t>
+          <t>vegaspeditiondk.opter.cloud</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>verdalkranno</t>
+          <t>vegaspeditiondk</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dk</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -13937,29 +13971,29 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>vgtse.opter.cloud</t>
+          <t>verdalkranno.opter.cloud</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>vgtse</t>
+          <t>verdalkranno</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -13969,7 +14003,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -13977,7 +14011,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -13989,42 +14023,52 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>vialogisticsno.opter.cloud</t>
+          <t>vgtse.opter.cloud</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>vialogisticsno</t>
+          <t>vgtse</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F340" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>74.241.233.90</t>
+        </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>passive_dns</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>vikencargono.opter.cloud</t>
+          <t>vialogisticsno.opter.cloud</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>vikencargono</t>
+          <t>vialogisticsno</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -14034,37 +14078,27 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F341" t="b">
-        <v>1</v>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>20.251.106.235</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>passive_dns</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>vikingspedno.opter.cloud</t>
+          <t>vikencargono.opter.cloud</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>vikingspedno</t>
+          <t>vikencargono</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -14074,37 +14108,47 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F342" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>20.251.106.235</t>
+        </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>wayback_cdx</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>vinstaakerise.opter.cloud</t>
+          <t>vikingspedno.opter.cloud</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>vinstaakerise</t>
+          <t>vikingspedno</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F343" t="b">
@@ -14112,19 +14156,19 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>passive_dns</t>
+          <t>wayback_cdx</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>vivaldise.opter.cloud</t>
+          <t>vinstaakerise.opter.cloud</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>vivaldise</t>
+          <t>vinstaakerise</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -14134,42 +14178,32 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="E344" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F344" t="b">
-        <v>1</v>
-      </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>74.241.233.90</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>passive_dns</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>vtsno.opter.cloud</t>
+          <t>vivaldise.opter.cloud</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>vtsno</t>
+          <t>vivaldise</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>se</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -14179,7 +14213,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14187,7 +14221,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>20.251.106.235</t>
+          <t>74.241.233.90</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -14199,17 +14233,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>wansse.opter.cloud</t>
+          <t>vtsno.opter.cloud</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>wansse</t>
+          <t>vtsno</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>se</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -14219,7 +14253,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14227,7 +14261,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>74.241.233.90</t>
+          <t>20.251.106.235</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -14239,12 +14273,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>westerlundsse.opter.cloud</t>
+          <t>wansse.opter.cloud</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>westerlundsse</t>
+          <t>wansse</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -14254,12 +14288,12 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14272,19 +14306,19 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>register_se</t>
+          <t>seed</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>wibeckerse.opter.cloud</t>
+          <t>westerlundsse.opter.cloud</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>wibeckerse</t>
+          <t>westerlundsse</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -14294,12 +14328,12 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14312,19 +14346,19 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>seed</t>
+          <t>register_se</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>wirensakerise.opter.cloud</t>
+          <t>wibeckerse.opter.cloud</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>wirensakerise</t>
+          <t>wibeckerse</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -14339,7 +14373,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14359,12 +14393,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>wohlinsse.opter.cloud</t>
+          <t>wirensakerise.opter.cloud</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>wohlinsse</t>
+          <t>wirensakerise</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -14379,7 +14413,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14399,12 +14433,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>xpressfraktse.opter.cloud</t>
+          <t>wohlinsse.opter.cloud</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>xpressfraktse</t>
+          <t>wohlinsse</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -14419,7 +14453,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14439,12 +14473,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>xtraresursse.opter.cloud</t>
+          <t>xpressfraktse.opter.cloud</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>xtraresursse</t>
+          <t>xpressfraktse</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -14459,7 +14493,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14479,12 +14513,12 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>xxltransportse.opter.cloud</t>
+          <t>xtraresursse.opter.cloud</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>xxltransportse</t>
+          <t>xtraresursse</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -14499,7 +14533,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14519,38 +14553,78 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
+          <t>xxltransportse.opter.cloud</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>xxltransportse</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F354" t="b">
+        <v>1</v>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>74.241.233.90</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
           <t>zerologisticse.opter.cloud</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
+      <c r="B355" t="inlineStr">
         <is>
           <t>zerologisticse</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>se</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>2026-09-19</t>
-        </is>
-      </c>
-      <c r="E354" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="F354" t="b">
-        <v>1</v>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>74.241.233.90</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="F355" t="b">
+        <v>1</v>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>74.241.233.90</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
         <is>
           <t>seed</t>
         </is>

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,6 +606,40 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>335</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>176</v>
+      </c>
+      <c r="F6" t="n">
+        <v>119</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -693,7 +727,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -733,7 +767,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -773,7 +807,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -813,7 +847,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -853,7 +887,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -893,7 +927,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -933,7 +967,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -973,7 +1007,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1013,7 +1047,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1053,7 +1087,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1093,7 +1127,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1133,7 +1167,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1173,7 +1207,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1213,7 +1247,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1253,7 +1287,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1293,7 +1327,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1333,7 +1367,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1373,7 +1407,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1413,7 +1447,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1453,7 +1487,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1523,7 +1557,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1563,7 +1597,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1603,7 +1637,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1643,7 +1677,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -1683,7 +1717,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -1723,7 +1757,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -1763,7 +1797,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -1803,7 +1837,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -1843,7 +1877,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -1883,7 +1917,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -1948,7 +1982,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -1988,7 +2022,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2028,7 +2062,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2068,7 +2102,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2108,7 +2142,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2148,7 +2182,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2188,7 +2222,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2228,7 +2262,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2268,7 +2302,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2308,7 +2342,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2348,7 +2382,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2388,7 +2422,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2428,7 +2462,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2468,7 +2502,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2508,7 +2542,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2548,7 +2582,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2588,7 +2622,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -2628,7 +2662,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -2668,7 +2702,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -2708,7 +2742,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -2748,7 +2782,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -2818,7 +2852,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -2858,7 +2892,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -2898,7 +2932,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -2938,7 +2972,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -2978,7 +3012,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3018,7 +3052,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3058,7 +3092,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3098,7 +3132,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3138,7 +3172,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3178,7 +3212,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3218,7 +3252,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3258,7 +3292,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3298,7 +3332,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3338,7 +3372,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3378,7 +3412,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3418,7 +3452,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3458,7 +3492,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3498,7 +3532,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3538,7 +3572,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3578,7 +3612,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -3618,7 +3652,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -3658,7 +3692,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -3698,7 +3732,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -3738,7 +3772,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -3778,7 +3812,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -3818,7 +3852,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -3858,7 +3892,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -3898,7 +3932,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -3933,7 +3967,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -3968,7 +4002,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4008,7 +4042,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4048,7 +4082,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4088,7 +4122,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4128,7 +4162,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4168,7 +4202,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4208,7 +4242,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4248,7 +4282,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4288,7 +4322,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4328,7 +4362,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4368,7 +4402,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4408,7 +4442,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4448,7 +4482,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4488,7 +4522,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4528,7 +4562,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4568,7 +4602,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -4608,7 +4642,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -4648,7 +4682,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -4688,7 +4722,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -4728,7 +4762,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -4768,7 +4802,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -4808,7 +4842,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -4848,7 +4882,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -4888,7 +4922,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -4928,7 +4962,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -4968,7 +5002,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5038,7 +5072,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5078,7 +5112,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5118,7 +5152,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5158,7 +5192,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5198,7 +5232,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5238,7 +5272,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5278,7 +5312,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5318,7 +5352,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5358,7 +5392,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5398,7 +5432,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5438,7 +5472,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5478,7 +5512,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5518,7 +5552,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5558,7 +5592,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5598,7 +5632,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -5638,7 +5672,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -5678,7 +5712,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -5718,7 +5752,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -5758,7 +5792,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -5798,7 +5832,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -5838,7 +5872,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -5878,7 +5912,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -5918,7 +5952,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -5958,7 +5992,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -5998,7 +6032,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6038,7 +6072,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6078,7 +6112,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6118,7 +6152,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6158,7 +6192,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6228,7 +6262,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6268,7 +6302,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6308,7 +6342,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6348,7 +6382,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6388,7 +6422,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6428,7 +6462,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6468,7 +6502,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6508,7 +6542,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6548,7 +6582,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6588,7 +6622,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -6628,7 +6662,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -6668,7 +6702,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -6708,7 +6742,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -6748,7 +6782,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -6788,7 +6822,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -6828,7 +6862,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -6868,7 +6902,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -6908,7 +6942,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -6948,7 +6982,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -6988,7 +7022,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7028,7 +7062,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7068,7 +7102,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7108,7 +7142,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7148,7 +7182,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7188,7 +7222,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7228,7 +7262,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7268,7 +7302,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7308,7 +7342,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7343,7 +7377,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7383,7 +7417,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7423,7 +7457,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7463,7 +7497,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7503,7 +7537,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7543,7 +7577,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7583,7 +7617,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -7623,7 +7657,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -7663,7 +7697,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -7703,7 +7737,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -7743,7 +7777,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -7783,7 +7817,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -7853,7 +7887,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -7893,7 +7927,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -7933,7 +7967,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -7973,7 +8007,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8013,7 +8047,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8053,7 +8087,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8093,7 +8127,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8158,7 +8192,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8198,7 +8232,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8238,7 +8272,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8278,7 +8312,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8318,7 +8352,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8403,7 +8437,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8443,7 +8477,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8483,7 +8517,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8553,7 +8587,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -8593,7 +8627,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -8633,7 +8667,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -8673,7 +8707,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -8713,7 +8747,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -8753,7 +8787,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -8793,7 +8827,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -8833,7 +8867,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -8873,7 +8907,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -8943,7 +8977,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -8983,7 +9017,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9023,7 +9057,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9063,7 +9097,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9103,7 +9137,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9143,7 +9177,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9183,7 +9217,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9223,7 +9257,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9263,7 +9297,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9303,7 +9337,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9343,7 +9377,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9383,7 +9417,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9423,7 +9457,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9463,7 +9497,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9503,7 +9537,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9543,7 +9577,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9583,7 +9617,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -9623,7 +9657,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -9663,7 +9697,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -9703,7 +9737,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -9743,7 +9777,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -9783,7 +9817,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -9823,7 +9857,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -9863,7 +9897,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -9903,7 +9937,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -9988,7 +10022,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10028,7 +10062,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10068,7 +10102,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10103,7 +10137,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10143,7 +10177,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10183,7 +10217,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10223,7 +10257,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10263,7 +10297,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10303,7 +10337,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10343,7 +10377,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10383,7 +10417,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10423,7 +10457,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10463,7 +10497,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10503,7 +10537,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10543,7 +10577,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10583,7 +10617,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -10623,7 +10657,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -10663,7 +10697,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -10703,7 +10737,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -10773,7 +10807,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -10813,7 +10847,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -10853,7 +10887,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -10893,7 +10927,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -10933,7 +10967,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -10973,7 +11007,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11013,7 +11047,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11053,7 +11087,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11093,7 +11127,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11133,7 +11167,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11173,7 +11207,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11208,7 +11242,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11248,7 +11282,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11288,7 +11322,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11328,7 +11362,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11368,7 +11402,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11408,7 +11442,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11448,7 +11482,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11488,7 +11522,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11523,7 +11557,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11563,7 +11597,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -11603,7 +11637,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -11643,7 +11677,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -11683,7 +11717,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -11723,7 +11757,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -11763,7 +11797,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -11803,7 +11837,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -11843,7 +11877,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -11883,7 +11917,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -11923,7 +11957,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -11963,7 +11997,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12033,7 +12067,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12073,7 +12107,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12113,7 +12147,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12153,7 +12187,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12193,7 +12227,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12263,7 +12297,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12303,7 +12337,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12343,7 +12377,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12383,7 +12417,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12423,7 +12457,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12463,7 +12497,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12503,7 +12537,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12543,7 +12577,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12583,7 +12617,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -12623,7 +12657,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -12663,7 +12697,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -12703,7 +12737,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -12743,7 +12777,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -12783,7 +12817,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -12823,7 +12857,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -12863,7 +12897,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -12903,7 +12937,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -12943,7 +12977,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -12983,7 +13017,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13023,7 +13057,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13093,7 +13127,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13133,7 +13167,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13173,7 +13207,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13213,7 +13247,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13253,7 +13287,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13293,7 +13327,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13333,7 +13367,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13373,7 +13407,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13413,7 +13447,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13453,7 +13487,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13493,7 +13527,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13533,7 +13567,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13573,7 +13607,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -13613,7 +13647,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -13653,7 +13687,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -13693,7 +13727,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -13763,7 +13797,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -13803,7 +13837,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -13843,7 +13877,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -13883,7 +13917,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -13923,7 +13957,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -13963,7 +13997,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14003,7 +14037,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14043,7 +14077,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14113,7 +14147,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14213,7 +14247,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14253,7 +14287,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14293,7 +14327,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14333,7 +14367,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14373,7 +14407,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14413,7 +14447,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14453,7 +14487,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14493,7 +14527,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14533,7 +14567,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14573,7 +14607,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -14613,7 +14647,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -640,6 +640,40 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>335</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>176</v>
+      </c>
+      <c r="F7" t="n">
+        <v>119</v>
+      </c>
+      <c r="G7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -727,7 +761,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -767,7 +801,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -807,7 +841,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -847,7 +881,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -887,7 +921,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -927,7 +961,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -967,7 +1001,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1007,7 +1041,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1047,7 +1081,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1087,7 +1121,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1127,7 +1161,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1167,7 +1201,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1207,7 +1241,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1247,7 +1281,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1287,7 +1321,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1327,7 +1361,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1367,7 +1401,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1407,7 +1441,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1447,7 +1481,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1487,7 +1521,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1557,7 +1591,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1597,7 +1631,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1637,7 +1671,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1677,7 +1711,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -1717,7 +1751,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -1757,7 +1791,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -1797,7 +1831,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -1837,7 +1871,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -1877,7 +1911,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -1917,7 +1951,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -1982,7 +2016,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2022,7 +2056,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2062,7 +2096,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2102,7 +2136,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2142,7 +2176,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2182,7 +2216,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2222,7 +2256,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2262,7 +2296,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2302,7 +2336,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2342,7 +2376,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2382,7 +2416,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2422,7 +2456,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2462,7 +2496,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2502,7 +2536,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2542,7 +2576,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2582,7 +2616,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2622,7 +2656,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -2662,7 +2696,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -2702,7 +2736,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -2742,7 +2776,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -2782,7 +2816,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -2852,7 +2886,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -2892,7 +2926,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -2932,7 +2966,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -2972,7 +3006,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3012,7 +3046,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3052,7 +3086,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3092,7 +3126,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3132,7 +3166,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3172,7 +3206,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3212,7 +3246,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3252,7 +3286,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3292,7 +3326,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3332,7 +3366,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3372,7 +3406,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3412,7 +3446,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3452,7 +3486,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3492,7 +3526,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3532,7 +3566,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3572,7 +3606,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3612,7 +3646,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -3652,7 +3686,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -3692,7 +3726,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -3732,7 +3766,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -3772,7 +3806,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -3812,7 +3846,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -3852,7 +3886,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -3892,7 +3926,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -3932,7 +3966,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -3967,7 +4001,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4002,7 +4036,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4042,7 +4076,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4082,7 +4116,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4122,7 +4156,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4162,7 +4196,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4202,7 +4236,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4242,7 +4276,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4282,7 +4316,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4322,7 +4356,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4362,7 +4396,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4402,7 +4436,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4442,7 +4476,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4482,7 +4516,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4522,7 +4556,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4562,7 +4596,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4602,7 +4636,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -4642,7 +4676,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -4682,7 +4716,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -4722,7 +4756,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -4762,7 +4796,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -4802,7 +4836,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -4842,7 +4876,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -4882,7 +4916,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -4922,7 +4956,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -4962,7 +4996,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5002,7 +5036,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5072,7 +5106,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5112,7 +5146,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5152,7 +5186,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5192,7 +5226,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5232,7 +5266,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5272,7 +5306,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5312,7 +5346,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5352,7 +5386,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5392,7 +5426,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5432,7 +5466,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5472,7 +5506,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5512,7 +5546,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5552,7 +5586,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5592,7 +5626,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5632,7 +5666,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -5672,7 +5706,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -5712,7 +5746,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -5752,7 +5786,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -5792,7 +5826,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -5832,7 +5866,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -5872,7 +5906,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -5912,7 +5946,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -5952,7 +5986,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -5992,7 +6026,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6032,7 +6066,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6072,7 +6106,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6112,7 +6146,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6152,7 +6186,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6192,7 +6226,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6262,7 +6296,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6302,7 +6336,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6342,7 +6376,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6382,7 +6416,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6422,7 +6456,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6462,7 +6496,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6502,7 +6536,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6542,7 +6576,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6582,7 +6616,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6622,7 +6656,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -6662,7 +6696,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -6702,7 +6736,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -6742,7 +6776,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -6782,7 +6816,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -6822,7 +6856,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -6862,7 +6896,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -6902,7 +6936,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -6942,7 +6976,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -6982,7 +7016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7022,7 +7056,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7062,7 +7096,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7102,7 +7136,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7142,7 +7176,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7182,7 +7216,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7222,7 +7256,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7262,7 +7296,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7302,7 +7336,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7342,7 +7376,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7377,7 +7411,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7417,7 +7451,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7457,7 +7491,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7497,7 +7531,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7537,7 +7571,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7577,7 +7611,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7617,7 +7651,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -7657,7 +7691,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -7697,7 +7731,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -7737,7 +7771,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -7777,7 +7811,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -7817,7 +7851,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -7887,7 +7921,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -7927,7 +7961,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -7967,7 +8001,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8007,7 +8041,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8047,7 +8081,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8087,7 +8121,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8127,7 +8161,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8192,7 +8226,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8232,7 +8266,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8272,7 +8306,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8312,7 +8346,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8352,7 +8386,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8437,7 +8471,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8477,7 +8511,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8517,7 +8551,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8587,7 +8621,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -8627,7 +8661,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -8667,7 +8701,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -8707,7 +8741,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -8747,7 +8781,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -8787,7 +8821,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -8827,7 +8861,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -8867,7 +8901,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -8907,7 +8941,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -8977,7 +9011,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9017,7 +9051,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9057,7 +9091,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9097,7 +9131,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9137,7 +9171,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9177,7 +9211,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9217,7 +9251,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9257,7 +9291,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9297,7 +9331,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9337,7 +9371,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9377,7 +9411,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9417,7 +9451,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9457,7 +9491,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9497,7 +9531,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9537,7 +9571,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9577,7 +9611,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9617,7 +9651,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -9657,7 +9691,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -9697,7 +9731,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -9737,7 +9771,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -9777,7 +9811,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -9817,7 +9851,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -9857,7 +9891,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -9897,7 +9931,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -9937,7 +9971,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10022,7 +10056,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10062,7 +10096,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10102,7 +10136,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10137,7 +10171,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10177,7 +10211,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10217,7 +10251,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10257,7 +10291,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10297,7 +10331,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10337,7 +10371,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10377,7 +10411,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10417,7 +10451,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10457,7 +10491,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10497,7 +10531,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10537,7 +10571,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10577,7 +10611,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10617,7 +10651,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -10657,7 +10691,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -10697,7 +10731,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -10737,7 +10771,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -10807,7 +10841,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -10847,7 +10881,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -10887,7 +10921,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -10927,7 +10961,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -10967,7 +11001,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11007,7 +11041,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11047,7 +11081,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11087,7 +11121,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11127,7 +11161,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11167,7 +11201,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11207,7 +11241,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11242,7 +11276,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11282,7 +11316,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11322,7 +11356,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11362,7 +11396,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11402,7 +11436,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11442,7 +11476,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11482,7 +11516,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11522,7 +11556,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11557,7 +11591,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11597,7 +11631,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -11637,7 +11671,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -11677,7 +11711,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -11717,7 +11751,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -11757,7 +11791,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -11797,7 +11831,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -11837,7 +11871,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -11877,7 +11911,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -11917,7 +11951,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -11957,7 +11991,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -11997,7 +12031,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12067,7 +12101,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12107,7 +12141,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12147,7 +12181,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12187,7 +12221,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12227,7 +12261,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12297,7 +12331,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12337,7 +12371,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12377,7 +12411,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12417,7 +12451,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12457,7 +12491,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12497,7 +12531,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12537,7 +12571,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12577,7 +12611,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12617,7 +12651,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -12657,7 +12691,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -12697,7 +12731,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -12737,7 +12771,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -12777,7 +12811,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -12817,7 +12851,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -12857,7 +12891,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -12897,7 +12931,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -12937,7 +12971,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -12977,7 +13011,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13017,7 +13051,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13057,7 +13091,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13127,7 +13161,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13167,7 +13201,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13207,7 +13241,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13247,7 +13281,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13287,7 +13321,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13327,7 +13361,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13367,7 +13401,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13407,7 +13441,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13447,7 +13481,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13487,7 +13521,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13527,7 +13561,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13567,7 +13601,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13607,7 +13641,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -13647,7 +13681,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -13687,7 +13721,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -13727,7 +13761,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -13797,7 +13831,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -13837,7 +13871,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -13877,7 +13911,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -13917,7 +13951,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -13957,7 +13991,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -13997,7 +14031,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14037,7 +14071,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14077,7 +14111,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14147,7 +14181,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14247,7 +14281,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14287,7 +14321,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14327,7 +14361,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14367,7 +14401,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14407,7 +14441,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14447,7 +14481,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14487,7 +14521,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14527,7 +14561,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14567,7 +14601,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14607,7 +14641,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -14647,7 +14681,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,6 +674,40 @@
         <v>4</v>
       </c>
       <c r="J7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>335</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>176</v>
+      </c>
+      <c r="F8" t="n">
+        <v>119</v>
+      </c>
+      <c r="G8" t="n">
+        <v>24</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -761,7 +795,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -801,7 +835,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -841,7 +875,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -881,7 +915,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -921,7 +955,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -961,7 +995,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1001,7 +1035,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1041,7 +1075,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1081,7 +1115,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1121,7 +1155,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1161,7 +1195,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1201,7 +1235,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1241,7 +1275,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1281,7 +1315,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1321,7 +1355,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1361,7 +1395,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1401,7 +1435,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1441,7 +1475,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1481,7 +1515,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1521,7 +1555,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1591,7 +1625,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1631,7 +1665,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1671,7 +1705,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1711,7 +1745,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -1751,7 +1785,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -1791,7 +1825,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -1831,7 +1865,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -1871,7 +1905,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -1911,7 +1945,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -1951,7 +1985,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2016,7 +2050,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2056,7 +2090,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2096,7 +2130,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2136,7 +2170,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2176,7 +2210,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2216,7 +2250,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2256,7 +2290,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2296,7 +2330,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2336,7 +2370,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2376,7 +2410,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2416,7 +2450,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2456,7 +2490,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2496,7 +2530,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2536,7 +2570,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2576,7 +2610,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2616,7 +2650,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2656,7 +2690,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -2696,7 +2730,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -2736,7 +2770,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -2776,7 +2810,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -2816,7 +2850,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -2886,7 +2920,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -2926,7 +2960,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -2966,7 +3000,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3006,7 +3040,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3046,7 +3080,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3086,7 +3120,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3126,7 +3160,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3166,7 +3200,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3206,7 +3240,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3246,7 +3280,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3286,7 +3320,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3326,7 +3360,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3366,7 +3400,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3406,7 +3440,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3446,7 +3480,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3486,7 +3520,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3526,7 +3560,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3566,7 +3600,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3606,7 +3640,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3646,7 +3680,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -3686,7 +3720,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -3726,7 +3760,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -3766,7 +3800,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -3806,7 +3840,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -3846,7 +3880,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -3886,7 +3920,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -3926,7 +3960,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -3966,7 +4000,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4001,7 +4035,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4036,7 +4070,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4076,7 +4110,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4116,7 +4150,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4156,7 +4190,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4196,7 +4230,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4236,7 +4270,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4276,7 +4310,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4316,7 +4350,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4356,7 +4390,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4396,7 +4430,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4436,7 +4470,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4476,7 +4510,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4516,7 +4550,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4556,7 +4590,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4596,7 +4630,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4636,7 +4670,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -4676,7 +4710,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -4716,7 +4750,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -4756,7 +4790,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -4796,7 +4830,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -4836,7 +4870,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -4876,7 +4910,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -4916,7 +4950,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -4956,7 +4990,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -4996,7 +5030,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5036,7 +5070,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5106,7 +5140,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5146,7 +5180,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5186,7 +5220,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5226,7 +5260,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5266,7 +5300,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5306,7 +5340,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5346,7 +5380,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5386,7 +5420,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5426,7 +5460,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5466,7 +5500,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5506,7 +5540,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5546,7 +5580,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5586,7 +5620,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5626,7 +5660,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5666,7 +5700,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -5706,7 +5740,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -5746,7 +5780,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -5786,7 +5820,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -5826,7 +5860,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -5866,7 +5900,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -5906,7 +5940,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -5946,7 +5980,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -5986,7 +6020,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6026,7 +6060,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6066,7 +6100,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6106,7 +6140,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6146,7 +6180,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6186,7 +6220,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6226,7 +6260,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6296,7 +6330,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6336,7 +6370,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6376,7 +6410,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6416,7 +6450,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6456,7 +6490,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6496,7 +6530,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6536,7 +6570,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6576,7 +6610,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6616,7 +6650,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6656,7 +6690,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -6696,7 +6730,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -6736,7 +6770,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -6776,7 +6810,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -6816,7 +6850,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -6856,7 +6890,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -6896,7 +6930,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -6936,7 +6970,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -6976,7 +7010,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7016,7 +7050,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7056,7 +7090,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7096,7 +7130,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7136,7 +7170,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7176,7 +7210,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7216,7 +7250,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7256,7 +7290,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7296,7 +7330,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7336,7 +7370,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7376,7 +7410,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7411,7 +7445,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7451,7 +7485,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7491,7 +7525,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7531,7 +7565,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7571,7 +7605,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7611,7 +7645,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7651,7 +7685,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -7691,7 +7725,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -7731,7 +7765,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -7771,7 +7805,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -7811,7 +7845,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -7851,7 +7885,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -7921,7 +7955,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -7961,7 +7995,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8001,7 +8035,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8041,7 +8075,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8081,7 +8115,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8121,7 +8155,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8161,7 +8195,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8226,7 +8260,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8266,7 +8300,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8306,7 +8340,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8346,7 +8380,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8386,7 +8420,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8471,7 +8505,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8511,7 +8545,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8551,7 +8585,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8621,7 +8655,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -8661,7 +8695,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -8701,7 +8735,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -8741,7 +8775,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -8781,7 +8815,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -8821,7 +8855,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -8861,7 +8895,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -8901,7 +8935,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -8941,7 +8975,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9011,7 +9045,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9051,7 +9085,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9091,7 +9125,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9131,7 +9165,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9171,7 +9205,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9211,7 +9245,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9251,7 +9285,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9291,7 +9325,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9331,7 +9365,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9371,7 +9405,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9411,7 +9445,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9451,7 +9485,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9491,7 +9525,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9531,7 +9565,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9571,7 +9605,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9611,7 +9645,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9651,7 +9685,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -9691,7 +9725,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -9731,7 +9765,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -9771,7 +9805,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -9811,7 +9845,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -9851,7 +9885,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -9891,7 +9925,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -9931,7 +9965,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -9971,7 +10005,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10056,7 +10090,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10096,7 +10130,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10136,7 +10170,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10171,7 +10205,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10211,7 +10245,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10251,7 +10285,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10291,7 +10325,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10331,7 +10365,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10371,7 +10405,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10411,7 +10445,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10451,7 +10485,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10491,7 +10525,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10531,7 +10565,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10571,7 +10605,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10611,7 +10645,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10651,7 +10685,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -10691,7 +10725,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -10731,7 +10765,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -10771,7 +10805,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -10841,7 +10875,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -10881,7 +10915,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -10921,7 +10955,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -10961,7 +10995,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11001,7 +11035,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11041,7 +11075,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11081,7 +11115,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11121,7 +11155,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11161,7 +11195,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11201,7 +11235,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11241,7 +11275,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11276,7 +11310,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11316,7 +11350,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11356,7 +11390,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11396,7 +11430,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11436,7 +11470,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11476,7 +11510,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11516,7 +11550,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11556,7 +11590,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11591,7 +11625,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11631,7 +11665,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -11671,7 +11705,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -11711,7 +11745,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -11751,7 +11785,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -11791,7 +11825,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -11831,7 +11865,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -11871,7 +11905,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -11911,7 +11945,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -11951,7 +11985,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -11991,7 +12025,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12031,7 +12065,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12101,7 +12135,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12141,7 +12175,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12181,7 +12215,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12221,7 +12255,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12261,7 +12295,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12331,7 +12365,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12371,7 +12405,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12411,7 +12445,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12451,7 +12485,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12491,7 +12525,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12531,7 +12565,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12571,7 +12605,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12611,7 +12645,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12651,7 +12685,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -12691,7 +12725,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -12731,7 +12765,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -12771,7 +12805,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -12811,7 +12845,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -12851,7 +12885,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -12891,7 +12925,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -12931,7 +12965,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -12971,7 +13005,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13011,7 +13045,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13051,7 +13085,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13091,7 +13125,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13161,7 +13195,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13201,7 +13235,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13241,7 +13275,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13281,7 +13315,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13321,7 +13355,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13361,7 +13395,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13401,7 +13435,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13441,7 +13475,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13481,7 +13515,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13521,7 +13555,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13561,7 +13595,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13601,7 +13635,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13641,7 +13675,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -13681,7 +13715,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -13721,7 +13755,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -13761,7 +13795,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -13831,7 +13865,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -13871,7 +13905,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -13911,7 +13945,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -13951,7 +13985,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -13991,7 +14025,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14031,7 +14065,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14071,7 +14105,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14111,7 +14145,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14181,7 +14215,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14281,7 +14315,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14321,7 +14355,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14361,7 +14395,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14401,7 +14435,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14441,7 +14475,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14481,7 +14515,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14521,7 +14555,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14561,7 +14595,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14601,7 +14635,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14641,7 +14675,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -14681,7 +14715,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,6 +708,40 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>335</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>176</v>
+      </c>
+      <c r="F9" t="n">
+        <v>119</v>
+      </c>
+      <c r="G9" t="n">
+        <v>24</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
         <v>6</v>
       </c>
     </row>
@@ -795,7 +829,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -835,7 +869,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -875,7 +909,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -915,7 +949,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -955,7 +989,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -995,7 +1029,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1035,7 +1069,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1075,7 +1109,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1115,7 +1149,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1155,7 +1189,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1195,7 +1229,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1235,7 +1269,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1275,7 +1309,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1315,7 +1349,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1355,7 +1389,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1395,7 +1429,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1435,7 +1469,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1475,7 +1509,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1515,7 +1549,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1555,7 +1589,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1625,7 +1659,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1665,7 +1699,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1705,7 +1739,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1745,7 +1779,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -1785,7 +1819,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -1825,7 +1859,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -1865,7 +1899,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -1905,7 +1939,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -1945,7 +1979,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -1985,7 +2019,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2050,7 +2084,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2090,7 +2124,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2130,7 +2164,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2170,7 +2204,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2210,7 +2244,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2250,7 +2284,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2290,7 +2324,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2330,7 +2364,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2370,7 +2404,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2410,7 +2444,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2450,7 +2484,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2490,7 +2524,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2530,7 +2564,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2570,7 +2604,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2610,7 +2644,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2650,7 +2684,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2690,7 +2724,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -2730,7 +2764,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -2770,7 +2804,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -2810,7 +2844,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -2850,7 +2884,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -2920,7 +2954,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -2960,7 +2994,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3000,7 +3034,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3040,7 +3074,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3080,7 +3114,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3120,7 +3154,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3160,7 +3194,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3200,7 +3234,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3240,7 +3274,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3280,7 +3314,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3320,7 +3354,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3360,7 +3394,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3400,7 +3434,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3440,7 +3474,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3480,7 +3514,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3520,7 +3554,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3560,7 +3594,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3600,7 +3634,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3640,7 +3674,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3680,7 +3714,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -3720,7 +3754,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -3760,7 +3794,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -3800,7 +3834,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -3840,7 +3874,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -3880,7 +3914,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -3920,7 +3954,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -3960,7 +3994,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4000,7 +4034,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4035,7 +4069,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4070,7 +4104,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4110,7 +4144,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4150,7 +4184,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4190,7 +4224,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4230,7 +4264,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4270,7 +4304,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4310,7 +4344,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4350,7 +4384,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4390,7 +4424,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4430,7 +4464,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4470,7 +4504,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4510,7 +4544,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4550,7 +4584,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4590,7 +4624,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4630,7 +4664,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4670,7 +4704,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -4710,7 +4744,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -4750,7 +4784,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -4790,7 +4824,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -4830,7 +4864,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -4870,7 +4904,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -4910,7 +4944,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -4950,7 +4984,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -4990,7 +5024,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5030,7 +5064,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5070,7 +5104,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5140,7 +5174,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5180,7 +5214,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5220,7 +5254,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5260,7 +5294,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5300,7 +5334,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5340,7 +5374,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5380,7 +5414,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5420,7 +5454,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5460,7 +5494,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5500,7 +5534,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5540,7 +5574,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5580,7 +5614,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5620,7 +5654,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5660,7 +5694,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5700,7 +5734,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -5740,7 +5774,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -5780,7 +5814,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -5820,7 +5854,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -5860,7 +5894,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -5900,7 +5934,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -5940,7 +5974,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -5980,7 +6014,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6020,7 +6054,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6060,7 +6094,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6100,7 +6134,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6140,7 +6174,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6180,7 +6214,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6220,7 +6254,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6260,7 +6294,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6330,7 +6364,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6370,7 +6404,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6410,7 +6444,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6450,7 +6484,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6490,7 +6524,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6530,7 +6564,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6570,7 +6604,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6610,7 +6644,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6650,7 +6684,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6690,7 +6724,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -6730,7 +6764,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -6770,7 +6804,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -6810,7 +6844,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -6850,7 +6884,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -6890,7 +6924,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -6930,7 +6964,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -6970,7 +7004,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7010,7 +7044,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7050,7 +7084,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7090,7 +7124,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7130,7 +7164,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7170,7 +7204,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7210,7 +7244,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7250,7 +7284,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7290,7 +7324,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7330,7 +7364,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7370,7 +7404,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7410,7 +7444,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7445,7 +7479,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7485,7 +7519,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7525,7 +7559,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7565,7 +7599,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7605,7 +7639,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7645,7 +7679,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7685,7 +7719,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -7725,7 +7759,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -7765,7 +7799,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -7805,7 +7839,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -7845,7 +7879,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -7885,7 +7919,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -7955,7 +7989,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -7995,7 +8029,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8035,7 +8069,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8075,7 +8109,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8115,7 +8149,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8155,7 +8189,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8195,7 +8229,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8260,7 +8294,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8300,7 +8334,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8340,7 +8374,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8380,7 +8414,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8420,7 +8454,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8505,7 +8539,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8545,7 +8579,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8585,7 +8619,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8655,7 +8689,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -8695,7 +8729,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -8735,7 +8769,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -8775,7 +8809,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -8815,7 +8849,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -8855,7 +8889,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -8895,7 +8929,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -8935,7 +8969,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -8975,7 +9009,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9045,7 +9079,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9085,7 +9119,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9125,7 +9159,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9165,7 +9199,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9205,7 +9239,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9245,7 +9279,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9285,7 +9319,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9325,7 +9359,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9365,7 +9399,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9405,7 +9439,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9445,7 +9479,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9485,7 +9519,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9525,7 +9559,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9565,7 +9599,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9605,7 +9639,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9645,7 +9679,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9685,7 +9719,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -9725,7 +9759,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -9765,7 +9799,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -9805,7 +9839,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -9845,7 +9879,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -9885,7 +9919,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -9925,7 +9959,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -9965,7 +9999,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10005,7 +10039,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10090,7 +10124,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10130,7 +10164,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10170,7 +10204,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10205,7 +10239,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10245,7 +10279,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10285,7 +10319,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10325,7 +10359,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10365,7 +10399,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10405,7 +10439,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10445,7 +10479,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10485,7 +10519,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10525,7 +10559,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10565,7 +10599,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10605,7 +10639,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10645,7 +10679,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10685,7 +10719,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -10725,7 +10759,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -10765,7 +10799,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -10805,7 +10839,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -10875,7 +10909,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -10915,7 +10949,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -10955,7 +10989,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -10995,7 +11029,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11035,7 +11069,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11075,7 +11109,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11115,7 +11149,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11155,7 +11189,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11195,7 +11229,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11235,7 +11269,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11275,7 +11309,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11310,7 +11344,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11350,7 +11384,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11390,7 +11424,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11430,7 +11464,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11470,7 +11504,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11510,7 +11544,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11550,7 +11584,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11590,7 +11624,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11625,7 +11659,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11665,7 +11699,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -11705,7 +11739,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -11745,7 +11779,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -11785,7 +11819,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -11825,7 +11859,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -11865,7 +11899,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -11905,7 +11939,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -11945,7 +11979,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -11985,7 +12019,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12025,7 +12059,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12065,7 +12099,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12135,7 +12169,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12175,7 +12209,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12215,7 +12249,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12255,7 +12289,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12295,7 +12329,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12365,7 +12399,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12405,7 +12439,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12445,7 +12479,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12485,7 +12519,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12525,7 +12559,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12565,7 +12599,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12605,7 +12639,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12645,7 +12679,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12685,7 +12719,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -12725,7 +12759,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -12765,7 +12799,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -12805,7 +12839,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -12845,7 +12879,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -12885,7 +12919,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -12925,7 +12959,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -12965,7 +12999,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13005,7 +13039,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13045,7 +13079,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13085,7 +13119,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13125,7 +13159,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13195,7 +13229,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13235,7 +13269,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13275,7 +13309,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13315,7 +13349,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13355,7 +13389,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13395,7 +13429,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13435,7 +13469,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13475,7 +13509,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13515,7 +13549,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13555,7 +13589,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13595,7 +13629,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13635,7 +13669,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13675,7 +13709,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -13715,7 +13749,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -13755,7 +13789,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -13795,7 +13829,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -13865,7 +13899,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -13905,7 +13939,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -13945,7 +13979,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -13985,7 +14019,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14025,7 +14059,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14065,7 +14099,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14105,7 +14139,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14145,7 +14179,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14215,7 +14249,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14315,7 +14349,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14355,7 +14389,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14395,7 +14429,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14435,7 +14469,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14475,7 +14509,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14515,7 +14549,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14555,7 +14589,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14595,7 +14629,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14635,7 +14669,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14675,7 +14709,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -14715,7 +14749,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,6 +742,40 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>335</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>176</v>
+      </c>
+      <c r="F10" t="n">
+        <v>119</v>
+      </c>
+      <c r="G10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -829,7 +863,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -869,7 +903,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -909,7 +943,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -949,7 +983,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -989,7 +1023,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1029,7 +1063,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1069,7 +1103,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1109,7 +1143,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1149,7 +1183,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1189,7 +1223,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1229,7 +1263,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1269,7 +1303,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1309,7 +1343,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1349,7 +1383,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1389,7 +1423,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1429,7 +1463,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1469,7 +1503,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1509,7 +1543,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1549,7 +1583,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1589,7 +1623,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1659,7 +1693,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1699,7 +1733,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1739,7 +1773,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1779,7 +1813,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -1819,7 +1853,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -1859,7 +1893,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -1899,7 +1933,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -1939,7 +1973,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -1979,7 +2013,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2019,7 +2053,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2084,7 +2118,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2124,7 +2158,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2164,7 +2198,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2204,7 +2238,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2244,7 +2278,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2284,7 +2318,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2324,7 +2358,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2364,7 +2398,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2404,7 +2438,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2444,7 +2478,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2484,7 +2518,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2524,7 +2558,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2564,7 +2598,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2604,7 +2638,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2644,7 +2678,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2684,7 +2718,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2724,7 +2758,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -2764,7 +2798,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -2804,7 +2838,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -2844,7 +2878,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -2884,7 +2918,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -2954,7 +2988,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -2994,7 +3028,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3034,7 +3068,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3074,7 +3108,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3114,7 +3148,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3154,7 +3188,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3194,7 +3228,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3234,7 +3268,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3274,7 +3308,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3314,7 +3348,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3354,7 +3388,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3394,7 +3428,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3434,7 +3468,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3474,7 +3508,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3514,7 +3548,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3554,7 +3588,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3594,7 +3628,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3634,7 +3668,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3674,7 +3708,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3714,7 +3748,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -3754,7 +3788,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -3794,7 +3828,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -3834,7 +3868,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -3874,7 +3908,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -3914,7 +3948,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -3954,7 +3988,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -3994,7 +4028,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4034,7 +4068,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4069,7 +4103,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4104,7 +4138,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4144,7 +4178,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4184,7 +4218,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4224,7 +4258,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4264,7 +4298,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4304,7 +4338,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4344,7 +4378,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4384,7 +4418,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4424,7 +4458,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4464,7 +4498,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4504,7 +4538,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4544,7 +4578,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4584,7 +4618,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4624,7 +4658,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4664,7 +4698,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4704,7 +4738,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -4744,7 +4778,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -4784,7 +4818,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -4824,7 +4858,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -4864,7 +4898,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -4904,7 +4938,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -4944,7 +4978,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -4984,7 +5018,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5024,7 +5058,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5064,7 +5098,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5104,7 +5138,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5174,7 +5208,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5214,7 +5248,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5254,7 +5288,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5294,7 +5328,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5334,7 +5368,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5374,7 +5408,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5414,7 +5448,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5454,7 +5488,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5494,7 +5528,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5534,7 +5568,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5574,7 +5608,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5614,7 +5648,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5654,7 +5688,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5694,7 +5728,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5734,7 +5768,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -5774,7 +5808,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -5814,7 +5848,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -5854,7 +5888,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -5894,7 +5928,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -5934,7 +5968,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -5974,7 +6008,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6014,7 +6048,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6054,7 +6088,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6094,7 +6128,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6134,7 +6168,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6174,7 +6208,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6214,7 +6248,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6254,7 +6288,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6294,7 +6328,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6364,7 +6398,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6404,7 +6438,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6444,7 +6478,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6484,7 +6518,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6524,7 +6558,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6564,7 +6598,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6604,7 +6638,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6644,7 +6678,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6684,7 +6718,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6724,7 +6758,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -6764,7 +6798,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -6804,7 +6838,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -6844,7 +6878,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -6884,7 +6918,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -6924,7 +6958,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -6964,7 +6998,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7004,7 +7038,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7044,7 +7078,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7084,7 +7118,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7124,7 +7158,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7164,7 +7198,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7204,7 +7238,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7244,7 +7278,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7284,7 +7318,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7324,7 +7358,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7364,7 +7398,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7404,7 +7438,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7444,7 +7478,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7479,7 +7513,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7519,7 +7553,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7559,7 +7593,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7599,7 +7633,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7639,7 +7673,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7679,7 +7713,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7719,7 +7753,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -7759,7 +7793,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -7799,7 +7833,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -7839,7 +7873,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -7879,7 +7913,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -7919,7 +7953,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -7989,7 +8023,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8029,7 +8063,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8069,7 +8103,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8109,7 +8143,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8149,7 +8183,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8189,7 +8223,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8229,7 +8263,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8294,7 +8328,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8334,7 +8368,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8374,7 +8408,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8414,7 +8448,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8454,7 +8488,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8539,7 +8573,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8579,7 +8613,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8619,7 +8653,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8689,7 +8723,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -8729,7 +8763,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -8769,7 +8803,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -8809,7 +8843,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -8849,7 +8883,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -8889,7 +8923,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -8929,7 +8963,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -8969,7 +9003,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9009,7 +9043,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9079,7 +9113,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9119,7 +9153,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9159,7 +9193,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9199,7 +9233,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9239,7 +9273,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9279,7 +9313,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9319,7 +9353,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9359,7 +9393,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9399,7 +9433,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9439,7 +9473,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9479,7 +9513,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9519,7 +9553,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9559,7 +9593,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9599,7 +9633,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9639,7 +9673,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9679,7 +9713,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9719,7 +9753,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -9759,7 +9793,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -9799,7 +9833,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -9839,7 +9873,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -9879,7 +9913,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -9919,7 +9953,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -9959,7 +9993,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -9999,7 +10033,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10039,7 +10073,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10124,7 +10158,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10164,7 +10198,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10204,7 +10238,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10239,7 +10273,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10279,7 +10313,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10319,7 +10353,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10359,7 +10393,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10399,7 +10433,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10439,7 +10473,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10479,7 +10513,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10519,7 +10553,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10559,7 +10593,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10599,7 +10633,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10639,7 +10673,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10679,7 +10713,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10719,7 +10753,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -10759,7 +10793,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -10799,7 +10833,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -10839,7 +10873,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -10909,7 +10943,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -10949,7 +10983,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -10989,7 +11023,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11029,7 +11063,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11069,7 +11103,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11109,7 +11143,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11149,7 +11183,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11189,7 +11223,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11229,7 +11263,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11269,7 +11303,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11309,7 +11343,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11344,7 +11378,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11384,7 +11418,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11424,7 +11458,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11464,7 +11498,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11504,7 +11538,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11544,7 +11578,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11584,7 +11618,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11624,7 +11658,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11659,7 +11693,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11699,7 +11733,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -11739,7 +11773,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -11779,7 +11813,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -11819,7 +11853,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -11859,7 +11893,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -11899,7 +11933,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -11939,7 +11973,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -11979,7 +12013,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12019,7 +12053,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12059,7 +12093,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12099,7 +12133,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12169,7 +12203,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12209,7 +12243,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12249,7 +12283,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12289,7 +12323,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12329,7 +12363,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12399,7 +12433,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12439,7 +12473,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12479,7 +12513,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12519,7 +12553,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12559,7 +12593,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12599,7 +12633,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12639,7 +12673,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12679,7 +12713,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12719,7 +12753,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -12759,7 +12793,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -12799,7 +12833,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -12839,7 +12873,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -12879,7 +12913,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -12919,7 +12953,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -12959,7 +12993,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -12999,7 +13033,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13039,7 +13073,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13079,7 +13113,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13119,7 +13153,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13159,7 +13193,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13229,7 +13263,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13269,7 +13303,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13309,7 +13343,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13349,7 +13383,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13389,7 +13423,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13429,7 +13463,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13469,7 +13503,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13509,7 +13543,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13549,7 +13583,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13589,7 +13623,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13629,7 +13663,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13669,7 +13703,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13709,7 +13743,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -13749,7 +13783,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -13789,7 +13823,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -13829,7 +13863,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -13899,7 +13933,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -13939,7 +13973,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -13979,7 +14013,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14019,7 +14053,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14059,7 +14093,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14099,7 +14133,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14139,7 +14173,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14179,7 +14213,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14249,7 +14283,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14349,7 +14383,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14389,7 +14423,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14429,7 +14463,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14469,7 +14503,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14509,7 +14543,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14549,7 +14583,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14589,7 +14623,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14629,7 +14663,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14669,7 +14703,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14709,7 +14743,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -14749,7 +14783,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,6 +776,40 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>335</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>176</v>
+      </c>
+      <c r="F11" t="n">
+        <v>119</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="n">
         <v>6</v>
       </c>
     </row>
@@ -863,7 +897,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -903,7 +937,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -943,7 +977,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -983,7 +1017,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1023,7 +1057,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1063,7 +1097,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1103,7 +1137,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1143,7 +1177,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1183,7 +1217,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1223,7 +1257,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1263,7 +1297,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1303,7 +1337,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1343,7 +1377,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1383,7 +1417,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1423,7 +1457,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1463,7 +1497,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1503,7 +1537,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1543,7 +1577,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1583,7 +1617,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1623,7 +1657,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1693,7 +1727,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1733,7 +1767,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1773,7 +1807,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1813,7 +1847,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -1853,7 +1887,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -1893,7 +1927,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -1933,7 +1967,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -1973,7 +2007,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2013,7 +2047,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2053,7 +2087,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2118,7 +2152,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2158,7 +2192,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2198,7 +2232,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2238,7 +2272,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2278,7 +2312,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2318,7 +2352,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2358,7 +2392,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2398,7 +2432,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2438,7 +2472,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2478,7 +2512,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2518,7 +2552,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2558,7 +2592,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2598,7 +2632,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2638,7 +2672,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2678,7 +2712,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2718,7 +2752,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2758,7 +2792,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -2798,7 +2832,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -2838,7 +2872,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -2878,7 +2912,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -2918,7 +2952,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -2988,7 +3022,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3028,7 +3062,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3068,7 +3102,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3108,7 +3142,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3148,7 +3182,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3188,7 +3222,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3228,7 +3262,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3268,7 +3302,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3308,7 +3342,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3348,7 +3382,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3388,7 +3422,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3428,7 +3462,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3468,7 +3502,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3508,7 +3542,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3548,7 +3582,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3588,7 +3622,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3628,7 +3662,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3668,7 +3702,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3708,7 +3742,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3748,7 +3782,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -3788,7 +3822,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -3828,7 +3862,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -3868,7 +3902,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -3908,7 +3942,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -3948,7 +3982,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -3988,7 +4022,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4028,7 +4062,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4068,7 +4102,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4103,7 +4137,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4138,7 +4172,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4178,7 +4212,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4218,7 +4252,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4258,7 +4292,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4298,7 +4332,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4338,7 +4372,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4378,7 +4412,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4418,7 +4452,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4458,7 +4492,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4498,7 +4532,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4538,7 +4572,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4578,7 +4612,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4618,7 +4652,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4658,7 +4692,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4698,7 +4732,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4738,7 +4772,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -4778,7 +4812,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -4818,7 +4852,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -4858,7 +4892,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -4898,7 +4932,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -4938,7 +4972,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -4978,7 +5012,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5018,7 +5052,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5058,7 +5092,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5098,7 +5132,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5138,7 +5172,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5208,7 +5242,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5248,7 +5282,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5288,7 +5322,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5328,7 +5362,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5368,7 +5402,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5408,7 +5442,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5448,7 +5482,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5488,7 +5522,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5528,7 +5562,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5568,7 +5602,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5608,7 +5642,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5648,7 +5682,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5688,7 +5722,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5728,7 +5762,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5768,7 +5802,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -5808,7 +5842,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -5848,7 +5882,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -5888,7 +5922,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -5928,7 +5962,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -5968,7 +6002,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6008,7 +6042,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6048,7 +6082,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6088,7 +6122,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6128,7 +6162,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6168,7 +6202,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6208,7 +6242,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6248,7 +6282,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6288,7 +6322,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6328,7 +6362,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6398,7 +6432,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6438,7 +6472,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6478,7 +6512,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6518,7 +6552,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6558,7 +6592,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6598,7 +6632,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6638,7 +6672,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6678,7 +6712,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6718,7 +6752,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6758,7 +6792,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -6798,7 +6832,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -6838,7 +6872,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -6878,7 +6912,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -6918,7 +6952,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -6958,7 +6992,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -6998,7 +7032,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7038,7 +7072,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7078,7 +7112,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7118,7 +7152,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7158,7 +7192,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7198,7 +7232,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7238,7 +7272,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7278,7 +7312,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7318,7 +7352,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7358,7 +7392,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7398,7 +7432,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7438,7 +7472,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7478,7 +7512,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7513,7 +7547,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7553,7 +7587,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7593,7 +7627,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7633,7 +7667,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7673,7 +7707,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7713,7 +7747,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7753,7 +7787,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -7793,7 +7827,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -7833,7 +7867,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -7873,7 +7907,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -7913,7 +7947,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -7953,7 +7987,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8023,7 +8057,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8063,7 +8097,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8103,7 +8137,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8143,7 +8177,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8183,7 +8217,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8223,7 +8257,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8263,7 +8297,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8328,7 +8362,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8368,7 +8402,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8408,7 +8442,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8448,7 +8482,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8488,7 +8522,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8573,7 +8607,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8613,7 +8647,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8653,7 +8687,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8723,7 +8757,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -8763,7 +8797,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -8803,7 +8837,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -8843,7 +8877,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -8883,7 +8917,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -8923,7 +8957,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -8963,7 +8997,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9003,7 +9037,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9043,7 +9077,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9113,7 +9147,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9153,7 +9187,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9193,7 +9227,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9233,7 +9267,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9273,7 +9307,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9313,7 +9347,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9353,7 +9387,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9393,7 +9427,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9433,7 +9467,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9473,7 +9507,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9513,7 +9547,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9553,7 +9587,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9593,7 +9627,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9633,7 +9667,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9673,7 +9707,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9713,7 +9747,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9753,7 +9787,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -9793,7 +9827,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -9833,7 +9867,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -9873,7 +9907,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -9913,7 +9947,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -9953,7 +9987,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -9993,7 +10027,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10033,7 +10067,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10073,7 +10107,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10158,7 +10192,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10198,7 +10232,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10238,7 +10272,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10273,7 +10307,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10313,7 +10347,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10353,7 +10387,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10393,7 +10427,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10433,7 +10467,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10473,7 +10507,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10513,7 +10547,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10553,7 +10587,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10593,7 +10627,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10633,7 +10667,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10673,7 +10707,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10713,7 +10747,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10753,7 +10787,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -10793,7 +10827,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -10833,7 +10867,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -10873,7 +10907,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -10943,7 +10977,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -10983,7 +11017,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11023,7 +11057,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11063,7 +11097,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11103,7 +11137,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11143,7 +11177,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11183,7 +11217,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11223,7 +11257,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11263,7 +11297,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11303,7 +11337,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11343,7 +11377,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11378,7 +11412,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11418,7 +11452,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11458,7 +11492,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11498,7 +11532,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11538,7 +11572,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11578,7 +11612,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11618,7 +11652,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11658,7 +11692,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11693,7 +11727,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11733,7 +11767,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -11773,7 +11807,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -11813,7 +11847,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -11853,7 +11887,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -11893,7 +11927,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -11933,7 +11967,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -11973,7 +12007,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12013,7 +12047,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12053,7 +12087,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12093,7 +12127,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12133,7 +12167,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12203,7 +12237,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12243,7 +12277,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12283,7 +12317,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12323,7 +12357,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12363,7 +12397,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12433,7 +12467,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12473,7 +12507,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12513,7 +12547,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12553,7 +12587,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12593,7 +12627,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12633,7 +12667,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12673,7 +12707,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12713,7 +12747,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12753,7 +12787,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -12793,7 +12827,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -12833,7 +12867,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -12873,7 +12907,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -12913,7 +12947,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -12953,7 +12987,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -12993,7 +13027,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13033,7 +13067,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13073,7 +13107,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13113,7 +13147,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13153,7 +13187,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13193,7 +13227,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13263,7 +13297,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13303,7 +13337,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13343,7 +13377,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13383,7 +13417,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13423,7 +13457,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13463,7 +13497,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13503,7 +13537,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13543,7 +13577,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13583,7 +13617,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13623,7 +13657,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13663,7 +13697,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13703,7 +13737,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13743,7 +13777,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -13783,7 +13817,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -13823,7 +13857,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -13863,7 +13897,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -13933,7 +13967,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -13973,7 +14007,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14013,7 +14047,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14053,7 +14087,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14093,7 +14127,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14133,7 +14167,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14173,7 +14207,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14213,7 +14247,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14283,7 +14317,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14383,7 +14417,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14423,7 +14457,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14463,7 +14497,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14503,7 +14537,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14543,7 +14577,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14583,7 +14617,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14623,7 +14657,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14663,7 +14697,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14703,7 +14737,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14743,7 +14777,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -14783,7 +14817,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -810,6 +810,40 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>335</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>176</v>
+      </c>
+      <c r="F12" t="n">
+        <v>119</v>
+      </c>
+      <c r="G12" t="n">
+        <v>24</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="n">
         <v>6</v>
       </c>
     </row>
@@ -897,7 +931,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -937,7 +971,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -977,7 +1011,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1017,7 +1051,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1057,7 +1091,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1097,7 +1131,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1137,7 +1171,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1177,7 +1211,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1217,7 +1251,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1257,7 +1291,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1297,7 +1331,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1337,7 +1371,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1377,7 +1411,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1417,7 +1451,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1457,7 +1491,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1497,7 +1531,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1537,7 +1571,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1577,7 +1611,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1617,7 +1651,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1657,7 +1691,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1727,7 +1761,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1767,7 +1801,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1807,7 +1841,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1847,7 +1881,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -1887,7 +1921,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -1927,7 +1961,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -1967,7 +2001,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2007,7 +2041,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2047,7 +2081,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2087,7 +2121,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2152,7 +2186,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2192,7 +2226,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2232,7 +2266,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2272,7 +2306,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2312,7 +2346,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2352,7 +2386,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2392,7 +2426,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2432,7 +2466,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2472,7 +2506,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2512,7 +2546,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2552,7 +2586,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2592,7 +2626,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2632,7 +2666,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2672,7 +2706,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2712,7 +2746,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2752,7 +2786,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2792,7 +2826,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -2832,7 +2866,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -2872,7 +2906,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -2912,7 +2946,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -2952,7 +2986,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3022,7 +3056,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3062,7 +3096,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3102,7 +3136,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3142,7 +3176,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3182,7 +3216,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3222,7 +3256,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3262,7 +3296,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3302,7 +3336,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3342,7 +3376,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3382,7 +3416,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3422,7 +3456,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3462,7 +3496,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3502,7 +3536,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3542,7 +3576,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3582,7 +3616,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3622,7 +3656,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3662,7 +3696,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3702,7 +3736,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3742,7 +3776,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3782,7 +3816,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -3822,7 +3856,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -3862,7 +3896,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -3902,7 +3936,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -3942,7 +3976,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -3982,7 +4016,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4022,7 +4056,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4062,7 +4096,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4102,7 +4136,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4137,7 +4171,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4172,7 +4206,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4212,7 +4246,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4252,7 +4286,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4292,7 +4326,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4332,7 +4366,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4372,7 +4406,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4412,7 +4446,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4452,7 +4486,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4492,7 +4526,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4532,7 +4566,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4572,7 +4606,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4612,7 +4646,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4652,7 +4686,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4692,7 +4726,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4732,7 +4766,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4772,7 +4806,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -4812,7 +4846,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -4852,7 +4886,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -4892,7 +4926,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -4932,7 +4966,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -4972,7 +5006,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5012,7 +5046,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5052,7 +5086,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5092,7 +5126,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5132,7 +5166,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5172,7 +5206,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5242,7 +5276,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5282,7 +5316,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5322,7 +5356,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5362,7 +5396,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5402,7 +5436,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5442,7 +5476,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5482,7 +5516,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5522,7 +5556,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5562,7 +5596,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5602,7 +5636,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5642,7 +5676,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5682,7 +5716,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5722,7 +5756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5762,7 +5796,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5802,7 +5836,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -5842,7 +5876,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -5882,7 +5916,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -5922,7 +5956,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -5962,7 +5996,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6002,7 +6036,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6042,7 +6076,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6082,7 +6116,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6122,7 +6156,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6162,7 +6196,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6202,7 +6236,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6242,7 +6276,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6282,7 +6316,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6322,7 +6356,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6362,7 +6396,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6432,7 +6466,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6472,7 +6506,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6512,7 +6546,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6552,7 +6586,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6592,7 +6626,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6632,7 +6666,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6672,7 +6706,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6712,7 +6746,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6752,7 +6786,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6792,7 +6826,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -6832,7 +6866,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -6872,7 +6906,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -6912,7 +6946,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -6952,7 +6986,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -6992,7 +7026,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7032,7 +7066,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7072,7 +7106,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7112,7 +7146,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7152,7 +7186,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7192,7 +7226,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7232,7 +7266,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7272,7 +7306,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7312,7 +7346,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7352,7 +7386,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7392,7 +7426,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7432,7 +7466,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7472,7 +7506,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7512,7 +7546,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7547,7 +7581,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7587,7 +7621,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7627,7 +7661,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7667,7 +7701,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7707,7 +7741,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7747,7 +7781,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7787,7 +7821,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -7827,7 +7861,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -7867,7 +7901,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -7907,7 +7941,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -7947,7 +7981,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -7987,7 +8021,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8057,7 +8091,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8097,7 +8131,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8137,7 +8171,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8177,7 +8211,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8217,7 +8251,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8257,7 +8291,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8297,7 +8331,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8362,7 +8396,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8402,7 +8436,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8442,7 +8476,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8482,7 +8516,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8522,7 +8556,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8607,7 +8641,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8647,7 +8681,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8687,7 +8721,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8757,7 +8791,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -8797,7 +8831,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -8837,7 +8871,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -8877,7 +8911,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -8917,7 +8951,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -8957,7 +8991,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -8997,7 +9031,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9037,7 +9071,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9077,7 +9111,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9147,7 +9181,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9187,7 +9221,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9227,7 +9261,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9267,7 +9301,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9307,7 +9341,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9347,7 +9381,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9387,7 +9421,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9427,7 +9461,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9467,7 +9501,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9507,7 +9541,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9547,7 +9581,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9587,7 +9621,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9627,7 +9661,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9667,7 +9701,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9707,7 +9741,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9747,7 +9781,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9787,7 +9821,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -9827,7 +9861,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -9867,7 +9901,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -9907,7 +9941,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -9947,7 +9981,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -9987,7 +10021,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10027,7 +10061,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10067,7 +10101,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10107,7 +10141,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10192,7 +10226,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10232,7 +10266,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10272,7 +10306,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10307,7 +10341,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10347,7 +10381,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10387,7 +10421,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10427,7 +10461,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10467,7 +10501,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10507,7 +10541,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10547,7 +10581,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10587,7 +10621,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10627,7 +10661,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10667,7 +10701,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10707,7 +10741,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10747,7 +10781,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10787,7 +10821,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -10827,7 +10861,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -10867,7 +10901,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -10907,7 +10941,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -10977,7 +11011,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11017,7 +11051,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11057,7 +11091,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11097,7 +11131,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11137,7 +11171,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11177,7 +11211,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11217,7 +11251,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11257,7 +11291,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11297,7 +11331,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11337,7 +11371,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11377,7 +11411,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11412,7 +11446,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11452,7 +11486,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11492,7 +11526,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11532,7 +11566,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11572,7 +11606,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11612,7 +11646,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11652,7 +11686,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11692,7 +11726,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11727,7 +11761,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11767,7 +11801,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -11807,7 +11841,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -11847,7 +11881,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -11887,7 +11921,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -11927,7 +11961,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -11967,7 +12001,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12007,7 +12041,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12047,7 +12081,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12087,7 +12121,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12127,7 +12161,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12167,7 +12201,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12237,7 +12271,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12277,7 +12311,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12317,7 +12351,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12357,7 +12391,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12397,7 +12431,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12467,7 +12501,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12507,7 +12541,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12547,7 +12581,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12587,7 +12621,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12627,7 +12661,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12667,7 +12701,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12707,7 +12741,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12747,7 +12781,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12787,7 +12821,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -12827,7 +12861,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -12867,7 +12901,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -12907,7 +12941,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -12947,7 +12981,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -12987,7 +13021,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13027,7 +13061,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13067,7 +13101,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13107,7 +13141,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13147,7 +13181,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13187,7 +13221,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13227,7 +13261,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13297,7 +13331,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13337,7 +13371,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13377,7 +13411,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13417,7 +13451,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13457,7 +13491,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13497,7 +13531,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13537,7 +13571,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13577,7 +13611,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13617,7 +13651,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13657,7 +13691,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13697,7 +13731,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13737,7 +13771,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13777,7 +13811,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -13817,7 +13851,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -13857,7 +13891,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -13897,7 +13931,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -13967,7 +14001,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14007,7 +14041,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14047,7 +14081,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14087,7 +14121,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14127,7 +14161,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14167,7 +14201,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14207,7 +14241,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14247,7 +14281,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14317,7 +14351,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14417,7 +14451,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14457,7 +14491,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14497,7 +14531,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14537,7 +14571,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14577,7 +14611,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14617,7 +14651,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14657,7 +14691,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14697,7 +14731,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14737,7 +14771,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14777,7 +14811,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -14817,7 +14851,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,6 +844,40 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>335</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>176</v>
+      </c>
+      <c r="F13" t="n">
+        <v>119</v>
+      </c>
+      <c r="G13" t="n">
+        <v>24</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="n">
         <v>6</v>
       </c>
     </row>
@@ -931,7 +965,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -971,7 +1005,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1011,7 +1045,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1051,7 +1085,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1091,7 +1125,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1131,7 +1165,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1171,7 +1205,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1211,7 +1245,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1251,7 +1285,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1291,7 +1325,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1331,7 +1365,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1371,7 +1405,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1411,7 +1445,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1451,7 +1485,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1491,7 +1525,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1531,7 +1565,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1571,7 +1605,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1611,7 +1645,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1651,7 +1685,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1691,7 +1725,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1761,7 +1795,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1801,7 +1835,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1841,7 +1875,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1881,7 +1915,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -1921,7 +1955,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -1961,7 +1995,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2001,7 +2035,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2041,7 +2075,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2081,7 +2115,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2121,7 +2155,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2186,7 +2220,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2226,7 +2260,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2266,7 +2300,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2306,7 +2340,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2346,7 +2380,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2386,7 +2420,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2426,7 +2460,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2466,7 +2500,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2506,7 +2540,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2546,7 +2580,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2586,7 +2620,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2626,7 +2660,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2666,7 +2700,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2706,7 +2740,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2746,7 +2780,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2786,7 +2820,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2826,7 +2860,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -2866,7 +2900,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -2906,7 +2940,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -2946,7 +2980,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -2986,7 +3020,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3056,7 +3090,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3096,7 +3130,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3136,7 +3170,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3176,7 +3210,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3216,7 +3250,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3256,7 +3290,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3296,7 +3330,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3336,7 +3370,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3376,7 +3410,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3416,7 +3450,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3456,7 +3490,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3496,7 +3530,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3536,7 +3570,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3576,7 +3610,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3616,7 +3650,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3656,7 +3690,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3696,7 +3730,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3736,7 +3770,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3776,7 +3810,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3816,7 +3850,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -3856,7 +3890,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -3896,7 +3930,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -3936,7 +3970,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -3976,7 +4010,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4016,7 +4050,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4056,7 +4090,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4096,7 +4130,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4136,7 +4170,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4171,7 +4205,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4206,7 +4240,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4246,7 +4280,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4286,7 +4320,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4326,7 +4360,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4366,7 +4400,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4406,7 +4440,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4446,7 +4480,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4486,7 +4520,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4526,7 +4560,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4566,7 +4600,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4606,7 +4640,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4646,7 +4680,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4686,7 +4720,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4726,7 +4760,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4766,7 +4800,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4806,7 +4840,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -4846,7 +4880,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -4886,7 +4920,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -4926,7 +4960,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -4966,7 +5000,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5006,7 +5040,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5046,7 +5080,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5086,7 +5120,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5126,7 +5160,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5166,7 +5200,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5206,7 +5240,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5276,7 +5310,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5316,7 +5350,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5356,7 +5390,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5396,7 +5430,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5436,7 +5470,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5476,7 +5510,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5516,7 +5550,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5556,7 +5590,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5596,7 +5630,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5636,7 +5670,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5676,7 +5710,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5716,7 +5750,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5756,7 +5790,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5796,7 +5830,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5836,7 +5870,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -5876,7 +5910,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -5916,7 +5950,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -5956,7 +5990,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -5996,7 +6030,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6036,7 +6070,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6076,7 +6110,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6116,7 +6150,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6156,7 +6190,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6196,7 +6230,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6236,7 +6270,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6276,7 +6310,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6316,7 +6350,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6356,7 +6390,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6396,7 +6430,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6466,7 +6500,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6506,7 +6540,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6546,7 +6580,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6586,7 +6620,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6626,7 +6660,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6666,7 +6700,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6706,7 +6740,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6746,7 +6780,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6786,7 +6820,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6826,7 +6860,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -6866,7 +6900,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -6906,7 +6940,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -6946,7 +6980,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -6986,7 +7020,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7026,7 +7060,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7066,7 +7100,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7106,7 +7140,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7146,7 +7180,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7186,7 +7220,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7226,7 +7260,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7266,7 +7300,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7306,7 +7340,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7346,7 +7380,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7386,7 +7420,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7426,7 +7460,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7466,7 +7500,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7506,7 +7540,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7546,7 +7580,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7581,7 +7615,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7621,7 +7655,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7661,7 +7695,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7701,7 +7735,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7741,7 +7775,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7781,7 +7815,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7821,7 +7855,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -7861,7 +7895,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -7901,7 +7935,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -7941,7 +7975,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -7981,7 +8015,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8021,7 +8055,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8091,7 +8125,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8131,7 +8165,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8171,7 +8205,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8211,7 +8245,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8251,7 +8285,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8291,7 +8325,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8331,7 +8365,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8396,7 +8430,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8436,7 +8470,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8476,7 +8510,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8516,7 +8550,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8556,7 +8590,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8641,7 +8675,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8681,7 +8715,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8721,7 +8755,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8791,7 +8825,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -8831,7 +8865,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -8871,7 +8905,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -8911,7 +8945,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -8951,7 +8985,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -8991,7 +9025,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9031,7 +9065,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9071,7 +9105,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9111,7 +9145,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9181,7 +9215,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9221,7 +9255,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9261,7 +9295,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9301,7 +9335,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9341,7 +9375,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9381,7 +9415,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9421,7 +9455,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9461,7 +9495,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9501,7 +9535,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9541,7 +9575,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9581,7 +9615,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9621,7 +9655,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9661,7 +9695,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9701,7 +9735,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9741,7 +9775,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9781,7 +9815,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9821,7 +9855,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -9861,7 +9895,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -9901,7 +9935,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -9941,7 +9975,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -9981,7 +10015,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10021,7 +10055,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10061,7 +10095,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10101,7 +10135,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10141,7 +10175,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10226,7 +10260,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10266,7 +10300,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10306,7 +10340,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10341,7 +10375,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10381,7 +10415,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10421,7 +10455,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10461,7 +10495,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10501,7 +10535,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10541,7 +10575,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10581,7 +10615,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10621,7 +10655,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10661,7 +10695,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10701,7 +10735,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10741,7 +10775,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10781,7 +10815,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10821,7 +10855,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -10861,7 +10895,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -10901,7 +10935,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -10941,7 +10975,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11011,7 +11045,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11051,7 +11085,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11091,7 +11125,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11131,7 +11165,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11171,7 +11205,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11211,7 +11245,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11251,7 +11285,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11291,7 +11325,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11331,7 +11365,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11371,7 +11405,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11411,7 +11445,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11446,7 +11480,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11486,7 +11520,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11526,7 +11560,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11566,7 +11600,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11606,7 +11640,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11646,7 +11680,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11686,7 +11720,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11726,7 +11760,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11761,7 +11795,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11801,7 +11835,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -11841,7 +11875,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -11881,7 +11915,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -11921,7 +11955,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -11961,7 +11995,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12001,7 +12035,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12041,7 +12075,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12081,7 +12115,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12121,7 +12155,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12161,7 +12195,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12201,7 +12235,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12271,7 +12305,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12311,7 +12345,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12351,7 +12385,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12391,7 +12425,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12431,7 +12465,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12501,7 +12535,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12541,7 +12575,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12581,7 +12615,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12621,7 +12655,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12661,7 +12695,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12701,7 +12735,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12741,7 +12775,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12781,7 +12815,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12821,7 +12855,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -12861,7 +12895,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -12901,7 +12935,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -12941,7 +12975,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -12981,7 +13015,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13021,7 +13055,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13061,7 +13095,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13101,7 +13135,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13141,7 +13175,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13181,7 +13215,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13221,7 +13255,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13261,7 +13295,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13331,7 +13365,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13371,7 +13405,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13411,7 +13445,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13451,7 +13485,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13491,7 +13525,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13531,7 +13565,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13571,7 +13605,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13611,7 +13645,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13651,7 +13685,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13691,7 +13725,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13731,7 +13765,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13771,7 +13805,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13811,7 +13845,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -13851,7 +13885,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -13891,7 +13925,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -13931,7 +13965,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14001,7 +14035,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14041,7 +14075,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14081,7 +14115,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14121,7 +14155,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14161,7 +14195,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14201,7 +14235,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14241,7 +14275,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14281,7 +14315,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14351,7 +14385,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14451,7 +14485,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14491,7 +14525,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14531,7 +14565,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14571,7 +14605,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14611,7 +14645,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14651,7 +14685,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14691,7 +14725,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14731,7 +14765,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14771,7 +14805,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14811,7 +14845,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -14851,7 +14885,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,6 +878,40 @@
         <v>4</v>
       </c>
       <c r="J13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>335</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>176</v>
+      </c>
+      <c r="F14" t="n">
+        <v>119</v>
+      </c>
+      <c r="G14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
         <v>6</v>
       </c>
     </row>
@@ -965,7 +999,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1005,7 +1039,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1045,7 +1079,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1085,7 +1119,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1125,7 +1159,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1165,7 +1199,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1205,7 +1239,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1245,7 +1279,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1285,7 +1319,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1325,7 +1359,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1365,7 +1399,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1405,7 +1439,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1445,7 +1479,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1485,7 +1519,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1525,7 +1559,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1565,7 +1599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1605,7 +1639,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1645,7 +1679,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1685,7 +1719,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1725,7 +1759,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1795,7 +1829,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1835,7 +1869,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1875,7 +1909,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1915,7 +1949,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -1955,7 +1989,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -1995,7 +2029,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2035,7 +2069,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2075,7 +2109,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2115,7 +2149,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2155,7 +2189,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2220,7 +2254,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2260,7 +2294,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2300,7 +2334,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2340,7 +2374,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2380,7 +2414,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2420,7 +2454,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2460,7 +2494,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2500,7 +2534,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2540,7 +2574,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2580,7 +2614,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2620,7 +2654,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2660,7 +2694,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2700,7 +2734,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2740,7 +2774,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2780,7 +2814,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2820,7 +2854,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2860,7 +2894,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -2900,7 +2934,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -2940,7 +2974,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -2980,7 +3014,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3020,7 +3054,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3090,7 +3124,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3130,7 +3164,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3170,7 +3204,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3210,7 +3244,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3250,7 +3284,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3290,7 +3324,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3330,7 +3364,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3370,7 +3404,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3410,7 +3444,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3450,7 +3484,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3490,7 +3524,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3530,7 +3564,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3570,7 +3604,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3610,7 +3644,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3650,7 +3684,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3690,7 +3724,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3730,7 +3764,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3770,7 +3804,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3810,7 +3844,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3850,7 +3884,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -3890,7 +3924,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -3930,7 +3964,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -3970,7 +4004,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4010,7 +4044,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4050,7 +4084,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4090,7 +4124,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4130,7 +4164,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4170,7 +4204,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4205,7 +4239,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4240,7 +4274,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4280,7 +4314,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4320,7 +4354,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4360,7 +4394,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4400,7 +4434,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4440,7 +4474,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4480,7 +4514,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4520,7 +4554,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4560,7 +4594,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4600,7 +4634,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4640,7 +4674,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4680,7 +4714,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4720,7 +4754,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4760,7 +4794,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4800,7 +4834,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4840,7 +4874,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -4880,7 +4914,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -4920,7 +4954,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -4960,7 +4994,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5000,7 +5034,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5040,7 +5074,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5080,7 +5114,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5120,7 +5154,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5160,7 +5194,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5200,7 +5234,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5240,7 +5274,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5310,7 +5344,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5350,7 +5384,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5390,7 +5424,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5430,7 +5464,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5470,7 +5504,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5510,7 +5544,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5550,7 +5584,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5590,7 +5624,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5630,7 +5664,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5670,7 +5704,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5710,7 +5744,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5750,7 +5784,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5790,7 +5824,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5830,7 +5864,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5870,7 +5904,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -5910,7 +5944,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -5950,7 +5984,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -5990,7 +6024,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6030,7 +6064,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6070,7 +6104,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6110,7 +6144,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6150,7 +6184,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6190,7 +6224,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6230,7 +6264,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6270,7 +6304,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6310,7 +6344,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6350,7 +6384,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6390,7 +6424,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6430,7 +6464,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6500,7 +6534,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6540,7 +6574,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6580,7 +6614,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6620,7 +6654,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6660,7 +6694,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6700,7 +6734,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6740,7 +6774,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6780,7 +6814,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6820,7 +6854,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6860,7 +6894,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -6900,7 +6934,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -6940,7 +6974,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -6980,7 +7014,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7020,7 +7054,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7060,7 +7094,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7100,7 +7134,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7140,7 +7174,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7180,7 +7214,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7220,7 +7254,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7260,7 +7294,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7300,7 +7334,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7340,7 +7374,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7380,7 +7414,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7420,7 +7454,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7460,7 +7494,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7500,7 +7534,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7540,7 +7574,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7580,7 +7614,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7615,7 +7649,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7655,7 +7689,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7695,7 +7729,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7735,7 +7769,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7775,7 +7809,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7815,7 +7849,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7855,7 +7889,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -7895,7 +7929,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -7935,7 +7969,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -7975,7 +8009,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8015,7 +8049,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8055,7 +8089,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8125,7 +8159,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8165,7 +8199,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8205,7 +8239,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8245,7 +8279,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8285,7 +8319,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8325,7 +8359,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8365,7 +8399,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8430,7 +8464,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8470,7 +8504,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8510,7 +8544,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8550,7 +8584,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8590,7 +8624,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8675,7 +8709,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8715,7 +8749,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8755,7 +8789,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8825,7 +8859,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -8865,7 +8899,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -8905,7 +8939,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -8945,7 +8979,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -8985,7 +9019,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9025,7 +9059,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9065,7 +9099,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9105,7 +9139,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9145,7 +9179,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9215,7 +9249,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9255,7 +9289,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9295,7 +9329,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9335,7 +9369,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9375,7 +9409,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9415,7 +9449,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9455,7 +9489,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9495,7 +9529,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9535,7 +9569,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9575,7 +9609,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9615,7 +9649,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9655,7 +9689,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9695,7 +9729,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9735,7 +9769,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9775,7 +9809,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9815,7 +9849,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9855,7 +9889,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -9895,7 +9929,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -9935,7 +9969,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -9975,7 +10009,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10015,7 +10049,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10055,7 +10089,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10095,7 +10129,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10135,7 +10169,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10175,7 +10209,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10260,7 +10294,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10300,7 +10334,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10340,7 +10374,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10375,7 +10409,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10415,7 +10449,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10455,7 +10489,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10495,7 +10529,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10535,7 +10569,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10575,7 +10609,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10615,7 +10649,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10655,7 +10689,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10695,7 +10729,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10735,7 +10769,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10775,7 +10809,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10815,7 +10849,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10855,7 +10889,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -10895,7 +10929,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -10935,7 +10969,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -10975,7 +11009,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11045,7 +11079,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11085,7 +11119,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11125,7 +11159,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11165,7 +11199,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11205,7 +11239,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11245,7 +11279,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11285,7 +11319,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11325,7 +11359,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11365,7 +11399,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11405,7 +11439,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11445,7 +11479,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11480,7 +11514,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11520,7 +11554,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11560,7 +11594,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11600,7 +11634,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11640,7 +11674,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11680,7 +11714,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11720,7 +11754,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11760,7 +11794,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11795,7 +11829,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11835,7 +11869,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -11875,7 +11909,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -11915,7 +11949,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -11955,7 +11989,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -11995,7 +12029,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12035,7 +12069,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12075,7 +12109,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12115,7 +12149,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12155,7 +12189,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12195,7 +12229,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12235,7 +12269,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12305,7 +12339,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12345,7 +12379,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12385,7 +12419,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12425,7 +12459,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12465,7 +12499,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12535,7 +12569,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12575,7 +12609,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12615,7 +12649,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12655,7 +12689,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12695,7 +12729,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12735,7 +12769,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12775,7 +12809,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12815,7 +12849,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12855,7 +12889,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -12895,7 +12929,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -12935,7 +12969,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -12975,7 +13009,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13015,7 +13049,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13055,7 +13089,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13095,7 +13129,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13135,7 +13169,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13175,7 +13209,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13215,7 +13249,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13255,7 +13289,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13295,7 +13329,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13365,7 +13399,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13405,7 +13439,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13445,7 +13479,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13485,7 +13519,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13525,7 +13559,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13565,7 +13599,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13605,7 +13639,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13645,7 +13679,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13685,7 +13719,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13725,7 +13759,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13765,7 +13799,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13805,7 +13839,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13845,7 +13879,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -13885,7 +13919,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -13925,7 +13959,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -13965,7 +13999,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14035,7 +14069,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14075,7 +14109,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14115,7 +14149,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14155,7 +14189,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14195,7 +14229,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14235,7 +14269,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14275,7 +14309,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14315,7 +14349,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14385,7 +14419,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14485,7 +14519,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14525,7 +14559,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14565,7 +14599,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14605,7 +14639,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14645,7 +14679,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14685,7 +14719,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14725,7 +14759,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14765,7 +14799,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14805,7 +14839,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14845,7 +14879,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -14885,7 +14919,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +912,40 @@
         <v>4</v>
       </c>
       <c r="J14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>335</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>176</v>
+      </c>
+      <c r="F15" t="n">
+        <v>119</v>
+      </c>
+      <c r="G15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -999,7 +1033,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1039,7 +1073,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1079,7 +1113,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1119,7 +1153,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1159,7 +1193,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1199,7 +1233,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1239,7 +1273,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1279,7 +1313,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1319,7 +1353,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1359,7 +1393,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1399,7 +1433,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1439,7 +1473,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1479,7 +1513,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1519,7 +1553,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1559,7 +1593,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1599,7 +1633,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1639,7 +1673,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1679,7 +1713,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1719,7 +1753,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1759,7 +1793,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1829,7 +1863,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1869,7 +1903,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1909,7 +1943,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1949,7 +1983,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -1989,7 +2023,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2029,7 +2063,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2069,7 +2103,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2109,7 +2143,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2149,7 +2183,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2189,7 +2223,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2254,7 +2288,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2294,7 +2328,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2334,7 +2368,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2374,7 +2408,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2414,7 +2448,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2454,7 +2488,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2494,7 +2528,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2534,7 +2568,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2574,7 +2608,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2614,7 +2648,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2654,7 +2688,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2694,7 +2728,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2734,7 +2768,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2774,7 +2808,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2814,7 +2848,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2854,7 +2888,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2894,7 +2928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -2934,7 +2968,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -2974,7 +3008,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3014,7 +3048,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3054,7 +3088,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3124,7 +3158,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3164,7 +3198,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3204,7 +3238,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3244,7 +3278,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3284,7 +3318,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3324,7 +3358,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3364,7 +3398,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3404,7 +3438,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3444,7 +3478,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3484,7 +3518,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3524,7 +3558,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3564,7 +3598,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3604,7 +3638,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3644,7 +3678,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3684,7 +3718,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3724,7 +3758,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3764,7 +3798,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3804,7 +3838,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3844,7 +3878,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3884,7 +3918,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -3924,7 +3958,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -3964,7 +3998,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4004,7 +4038,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4044,7 +4078,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4084,7 +4118,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4124,7 +4158,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4164,7 +4198,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4204,7 +4238,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4239,7 +4273,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4274,7 +4308,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4314,7 +4348,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4354,7 +4388,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4394,7 +4428,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4434,7 +4468,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4474,7 +4508,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4514,7 +4548,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4554,7 +4588,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4594,7 +4628,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4634,7 +4668,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4674,7 +4708,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4714,7 +4748,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4754,7 +4788,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4794,7 +4828,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4834,7 +4868,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4874,7 +4908,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -4914,7 +4948,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -4954,7 +4988,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -4994,7 +5028,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5034,7 +5068,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5074,7 +5108,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5114,7 +5148,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5154,7 +5188,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5194,7 +5228,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5234,7 +5268,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5274,7 +5308,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5344,7 +5378,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5384,7 +5418,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5424,7 +5458,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5464,7 +5498,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5504,7 +5538,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5544,7 +5578,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5584,7 +5618,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5624,7 +5658,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5664,7 +5698,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5704,7 +5738,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5744,7 +5778,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5784,7 +5818,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5824,7 +5858,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5864,7 +5898,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5904,7 +5938,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -5944,7 +5978,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -5984,7 +6018,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6024,7 +6058,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6064,7 +6098,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6104,7 +6138,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6144,7 +6178,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6184,7 +6218,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6224,7 +6258,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6264,7 +6298,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6304,7 +6338,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6344,7 +6378,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6384,7 +6418,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6424,7 +6458,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6464,7 +6498,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6534,7 +6568,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6574,7 +6608,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6614,7 +6648,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6654,7 +6688,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6694,7 +6728,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6734,7 +6768,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6774,7 +6808,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6814,7 +6848,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6854,7 +6888,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6894,7 +6928,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -6934,7 +6968,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -6974,7 +7008,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7014,7 +7048,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7054,7 +7088,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7094,7 +7128,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7134,7 +7168,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7174,7 +7208,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7214,7 +7248,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7254,7 +7288,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7294,7 +7328,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7334,7 +7368,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7374,7 +7408,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7414,7 +7448,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7454,7 +7488,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7494,7 +7528,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7534,7 +7568,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7574,7 +7608,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7614,7 +7648,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7649,7 +7683,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7689,7 +7723,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7729,7 +7763,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7769,7 +7803,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7809,7 +7843,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7849,7 +7883,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7889,7 +7923,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -7929,7 +7963,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -7969,7 +8003,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8009,7 +8043,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8049,7 +8083,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8089,7 +8123,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8159,7 +8193,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8199,7 +8233,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8239,7 +8273,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8279,7 +8313,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8319,7 +8353,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8359,7 +8393,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8399,7 +8433,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8464,7 +8498,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8504,7 +8538,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8544,7 +8578,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8584,7 +8618,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8624,7 +8658,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8709,7 +8743,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8749,7 +8783,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8789,7 +8823,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8859,7 +8893,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -8899,7 +8933,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -8939,7 +8973,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -8979,7 +9013,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9019,7 +9053,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9059,7 +9093,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9099,7 +9133,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9139,7 +9173,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9179,7 +9213,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9249,7 +9283,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9289,7 +9323,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9329,7 +9363,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9369,7 +9403,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9409,7 +9443,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9449,7 +9483,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9489,7 +9523,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9529,7 +9563,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9569,7 +9603,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9609,7 +9643,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9649,7 +9683,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9689,7 +9723,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9729,7 +9763,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9769,7 +9803,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9809,7 +9843,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9849,7 +9883,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9889,7 +9923,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -9929,7 +9963,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -9969,7 +10003,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10009,7 +10043,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10049,7 +10083,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10089,7 +10123,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10129,7 +10163,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10169,7 +10203,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10209,7 +10243,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10294,7 +10328,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10334,7 +10368,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10374,7 +10408,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10409,7 +10443,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10449,7 +10483,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10489,7 +10523,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10529,7 +10563,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10569,7 +10603,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10609,7 +10643,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10649,7 +10683,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10689,7 +10723,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10729,7 +10763,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10769,7 +10803,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10809,7 +10843,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10849,7 +10883,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10889,7 +10923,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -10929,7 +10963,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -10969,7 +11003,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11009,7 +11043,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11079,7 +11113,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11119,7 +11153,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11159,7 +11193,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11199,7 +11233,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11239,7 +11273,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11279,7 +11313,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11319,7 +11353,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11359,7 +11393,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11399,7 +11433,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11439,7 +11473,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11479,7 +11513,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11514,7 +11548,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11554,7 +11588,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11594,7 +11628,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11634,7 +11668,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11674,7 +11708,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11714,7 +11748,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11754,7 +11788,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11794,7 +11828,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11829,7 +11863,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11869,7 +11903,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -11909,7 +11943,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -11949,7 +11983,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -11989,7 +12023,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12029,7 +12063,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12069,7 +12103,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12109,7 +12143,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12149,7 +12183,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12189,7 +12223,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12229,7 +12263,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12269,7 +12303,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12339,7 +12373,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12379,7 +12413,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12419,7 +12453,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12459,7 +12493,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12499,7 +12533,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12569,7 +12603,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12609,7 +12643,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12649,7 +12683,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12689,7 +12723,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12729,7 +12763,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12769,7 +12803,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12809,7 +12843,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12849,7 +12883,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12889,7 +12923,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -12929,7 +12963,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -12969,7 +13003,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13009,7 +13043,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13049,7 +13083,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13089,7 +13123,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13129,7 +13163,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13169,7 +13203,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13209,7 +13243,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13249,7 +13283,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13289,7 +13323,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13329,7 +13363,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13399,7 +13433,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13439,7 +13473,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13479,7 +13513,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13519,7 +13553,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13559,7 +13593,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13599,7 +13633,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13639,7 +13673,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13679,7 +13713,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13719,7 +13753,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13759,7 +13793,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13799,7 +13833,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13839,7 +13873,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13879,7 +13913,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -13919,7 +13953,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -13959,7 +13993,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -13999,7 +14033,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14069,7 +14103,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14109,7 +14143,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14149,7 +14183,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14189,7 +14223,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14229,7 +14263,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14269,7 +14303,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14309,7 +14343,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14349,7 +14383,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14419,7 +14453,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14519,7 +14553,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14559,7 +14593,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14599,7 +14633,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14639,7 +14673,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14679,7 +14713,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14719,7 +14753,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14759,7 +14793,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14799,7 +14833,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14839,7 +14873,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14879,7 +14913,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -14919,7 +14953,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,6 +946,40 @@
         <v>4</v>
       </c>
       <c r="J15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>335</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>176</v>
+      </c>
+      <c r="F16" t="n">
+        <v>119</v>
+      </c>
+      <c r="G16" t="n">
+        <v>24</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1033,7 +1067,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1073,7 +1107,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1113,7 +1147,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1153,7 +1187,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1193,7 +1227,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1233,7 +1267,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1273,7 +1307,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1313,7 +1347,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1353,7 +1387,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1393,7 +1427,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1433,7 +1467,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1473,7 +1507,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1513,7 +1547,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1553,7 +1587,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1593,7 +1627,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1633,7 +1667,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1673,7 +1707,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1713,7 +1747,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1753,7 +1787,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1793,7 +1827,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1863,7 +1897,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1903,7 +1937,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1943,7 +1977,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -1983,7 +2017,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2023,7 +2057,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2063,7 +2097,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2103,7 +2137,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2143,7 +2177,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2183,7 +2217,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2223,7 +2257,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2288,7 +2322,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2328,7 +2362,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2368,7 +2402,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2408,7 +2442,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2448,7 +2482,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2488,7 +2522,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2528,7 +2562,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2568,7 +2602,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2608,7 +2642,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2648,7 +2682,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2688,7 +2722,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2728,7 +2762,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2768,7 +2802,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2808,7 +2842,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2848,7 +2882,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2888,7 +2922,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2928,7 +2962,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -2968,7 +3002,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3008,7 +3042,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3048,7 +3082,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3088,7 +3122,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3158,7 +3192,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3198,7 +3232,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3238,7 +3272,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3278,7 +3312,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3318,7 +3352,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3358,7 +3392,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3398,7 +3432,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3438,7 +3472,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3478,7 +3512,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3518,7 +3552,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3558,7 +3592,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3598,7 +3632,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3638,7 +3672,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3678,7 +3712,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3718,7 +3752,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3758,7 +3792,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3798,7 +3832,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3838,7 +3872,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3878,7 +3912,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3918,7 +3952,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -3958,7 +3992,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -3998,7 +4032,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4038,7 +4072,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4078,7 +4112,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4118,7 +4152,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4158,7 +4192,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4198,7 +4232,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4238,7 +4272,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4273,7 +4307,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4308,7 +4342,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4348,7 +4382,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4388,7 +4422,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4428,7 +4462,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4468,7 +4502,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4508,7 +4542,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4548,7 +4582,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4588,7 +4622,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4628,7 +4662,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4668,7 +4702,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4708,7 +4742,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4748,7 +4782,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4788,7 +4822,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4828,7 +4862,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4868,7 +4902,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4908,7 +4942,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -4948,7 +4982,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -4988,7 +5022,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -5028,7 +5062,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5068,7 +5102,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5108,7 +5142,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5148,7 +5182,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5188,7 +5222,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5228,7 +5262,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5268,7 +5302,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5308,7 +5342,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5378,7 +5412,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5418,7 +5452,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5458,7 +5492,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5498,7 +5532,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5538,7 +5572,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5578,7 +5612,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5618,7 +5652,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5658,7 +5692,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5698,7 +5732,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5738,7 +5772,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5778,7 +5812,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5818,7 +5852,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5858,7 +5892,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5898,7 +5932,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5938,7 +5972,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -5978,7 +6012,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6018,7 +6052,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6058,7 +6092,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6098,7 +6132,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6138,7 +6172,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6178,7 +6212,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6218,7 +6252,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6258,7 +6292,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6298,7 +6332,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6338,7 +6372,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6378,7 +6412,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6418,7 +6452,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6458,7 +6492,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6498,7 +6532,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6568,7 +6602,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6608,7 +6642,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6648,7 +6682,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6688,7 +6722,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6728,7 +6762,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6768,7 +6802,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6808,7 +6842,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6848,7 +6882,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6888,7 +6922,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6928,7 +6962,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -6968,7 +7002,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7008,7 +7042,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7048,7 +7082,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7088,7 +7122,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7128,7 +7162,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7168,7 +7202,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7208,7 +7242,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7248,7 +7282,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7288,7 +7322,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7328,7 +7362,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7368,7 +7402,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7408,7 +7442,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7448,7 +7482,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7488,7 +7522,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7528,7 +7562,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7568,7 +7602,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7608,7 +7642,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7648,7 +7682,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7683,7 +7717,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7723,7 +7757,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7763,7 +7797,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7803,7 +7837,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7843,7 +7877,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7883,7 +7917,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7923,7 +7957,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -7963,7 +7997,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8003,7 +8037,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8043,7 +8077,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8083,7 +8117,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8123,7 +8157,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8193,7 +8227,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8233,7 +8267,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8273,7 +8307,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8313,7 +8347,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8353,7 +8387,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8393,7 +8427,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8433,7 +8467,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8498,7 +8532,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8538,7 +8572,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8578,7 +8612,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8618,7 +8652,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8658,7 +8692,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8743,7 +8777,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8783,7 +8817,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8823,7 +8857,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8893,7 +8927,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -8933,7 +8967,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -8973,7 +9007,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -9013,7 +9047,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9053,7 +9087,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9093,7 +9127,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9133,7 +9167,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9173,7 +9207,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9213,7 +9247,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9283,7 +9317,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9323,7 +9357,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9363,7 +9397,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9403,7 +9437,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9443,7 +9477,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9483,7 +9517,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9523,7 +9557,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9563,7 +9597,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9603,7 +9637,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9643,7 +9677,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9683,7 +9717,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9723,7 +9757,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9763,7 +9797,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9803,7 +9837,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9843,7 +9877,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9883,7 +9917,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9923,7 +9957,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -9963,7 +9997,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10003,7 +10037,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10043,7 +10077,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10083,7 +10117,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10123,7 +10157,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10163,7 +10197,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10203,7 +10237,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10243,7 +10277,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10328,7 +10362,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10368,7 +10402,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10408,7 +10442,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10443,7 +10477,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10483,7 +10517,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10523,7 +10557,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10563,7 +10597,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10603,7 +10637,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10643,7 +10677,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10683,7 +10717,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10723,7 +10757,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10763,7 +10797,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10803,7 +10837,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10843,7 +10877,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10883,7 +10917,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10923,7 +10957,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -10963,7 +10997,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11003,7 +11037,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11043,7 +11077,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11113,7 +11147,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11153,7 +11187,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11193,7 +11227,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11233,7 +11267,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11273,7 +11307,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11313,7 +11347,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11353,7 +11387,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11393,7 +11427,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11433,7 +11467,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11473,7 +11507,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11513,7 +11547,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11548,7 +11582,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11588,7 +11622,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11628,7 +11662,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11668,7 +11702,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11708,7 +11742,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11748,7 +11782,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11788,7 +11822,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11828,7 +11862,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11863,7 +11897,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11903,7 +11937,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -11943,7 +11977,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -11983,7 +12017,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12023,7 +12057,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12063,7 +12097,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12103,7 +12137,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12143,7 +12177,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12183,7 +12217,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12223,7 +12257,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12263,7 +12297,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12303,7 +12337,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12373,7 +12407,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12413,7 +12447,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12453,7 +12487,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12493,7 +12527,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12533,7 +12567,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12603,7 +12637,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12643,7 +12677,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12683,7 +12717,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12723,7 +12757,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12763,7 +12797,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12803,7 +12837,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12843,7 +12877,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12883,7 +12917,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12923,7 +12957,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -12963,7 +12997,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13003,7 +13037,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13043,7 +13077,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13083,7 +13117,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13123,7 +13157,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13163,7 +13197,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13203,7 +13237,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13243,7 +13277,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13283,7 +13317,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13323,7 +13357,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13363,7 +13397,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13433,7 +13467,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13473,7 +13507,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13513,7 +13547,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13553,7 +13587,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13593,7 +13627,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13633,7 +13667,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13673,7 +13707,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13713,7 +13747,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13753,7 +13787,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13793,7 +13827,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13833,7 +13867,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13873,7 +13907,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13913,7 +13947,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -13953,7 +13987,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -13993,7 +14027,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14033,7 +14067,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14103,7 +14137,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14143,7 +14177,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14183,7 +14217,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14223,7 +14257,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14263,7 +14297,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14303,7 +14337,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14343,7 +14377,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14383,7 +14417,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14453,7 +14487,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14553,7 +14587,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14593,7 +14627,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14633,7 +14667,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14673,7 +14707,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14713,7 +14747,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14753,7 +14787,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14793,7 +14827,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14833,7 +14867,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14873,7 +14907,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14913,7 +14947,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -14953,7 +14987,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,6 +980,40 @@
         <v>4</v>
       </c>
       <c r="J16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>335</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>176</v>
+      </c>
+      <c r="F17" t="n">
+        <v>119</v>
+      </c>
+      <c r="G17" t="n">
+        <v>24</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1067,7 +1101,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1107,7 +1141,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1147,7 +1181,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1187,7 +1221,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1227,7 +1261,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1267,7 +1301,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1307,7 +1341,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1347,7 +1381,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1387,7 +1421,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1427,7 +1461,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1467,7 +1501,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1507,7 +1541,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1547,7 +1581,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1587,7 +1621,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1627,7 +1661,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1667,7 +1701,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1707,7 +1741,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1747,7 +1781,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1787,7 +1821,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1827,7 +1861,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1897,7 +1931,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1937,7 +1971,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -1977,7 +2011,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2017,7 +2051,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2057,7 +2091,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2097,7 +2131,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2137,7 +2171,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2177,7 +2211,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2217,7 +2251,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2257,7 +2291,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2322,7 +2356,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2362,7 +2396,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2402,7 +2436,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2442,7 +2476,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2482,7 +2516,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2522,7 +2556,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2562,7 +2596,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2602,7 +2636,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2642,7 +2676,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2682,7 +2716,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2722,7 +2756,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2762,7 +2796,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2802,7 +2836,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2842,7 +2876,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2882,7 +2916,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2922,7 +2956,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2962,7 +2996,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -3002,7 +3036,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3042,7 +3076,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3082,7 +3116,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3122,7 +3156,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3192,7 +3226,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3232,7 +3266,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3272,7 +3306,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3312,7 +3346,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3352,7 +3386,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3392,7 +3426,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3432,7 +3466,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3472,7 +3506,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3512,7 +3546,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3552,7 +3586,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3592,7 +3626,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3632,7 +3666,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3672,7 +3706,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3712,7 +3746,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3752,7 +3786,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3792,7 +3826,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3832,7 +3866,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3872,7 +3906,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3912,7 +3946,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3952,7 +3986,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -3992,7 +4026,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -4032,7 +4066,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4072,7 +4106,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4112,7 +4146,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4152,7 +4186,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4192,7 +4226,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4232,7 +4266,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4272,7 +4306,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4307,7 +4341,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4342,7 +4376,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4382,7 +4416,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4422,7 +4456,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4462,7 +4496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4502,7 +4536,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4542,7 +4576,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4582,7 +4616,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4622,7 +4656,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4662,7 +4696,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4702,7 +4736,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4742,7 +4776,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4782,7 +4816,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4822,7 +4856,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4862,7 +4896,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4902,7 +4936,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4942,7 +4976,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -4982,7 +5016,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -5022,7 +5056,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -5062,7 +5096,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5102,7 +5136,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5142,7 +5176,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5182,7 +5216,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5222,7 +5256,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5262,7 +5296,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5302,7 +5336,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5342,7 +5376,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5412,7 +5446,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5452,7 +5486,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5492,7 +5526,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5532,7 +5566,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5572,7 +5606,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5612,7 +5646,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5652,7 +5686,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5692,7 +5726,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5732,7 +5766,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5772,7 +5806,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5812,7 +5846,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5852,7 +5886,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5892,7 +5926,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5932,7 +5966,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -5972,7 +6006,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -6012,7 +6046,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6052,7 +6086,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6092,7 +6126,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6132,7 +6166,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6172,7 +6206,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6212,7 +6246,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6252,7 +6286,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6292,7 +6326,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6332,7 +6366,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6372,7 +6406,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6412,7 +6446,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6452,7 +6486,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6492,7 +6526,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6532,7 +6566,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6602,7 +6636,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6642,7 +6676,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6682,7 +6716,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6722,7 +6756,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6762,7 +6796,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6802,7 +6836,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6842,7 +6876,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6882,7 +6916,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6922,7 +6956,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6962,7 +6996,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -7002,7 +7036,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7042,7 +7076,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7082,7 +7116,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7122,7 +7156,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7162,7 +7196,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7202,7 +7236,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7242,7 +7276,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7282,7 +7316,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7322,7 +7356,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7362,7 +7396,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7402,7 +7436,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7442,7 +7476,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7482,7 +7516,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7522,7 +7556,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7562,7 +7596,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7602,7 +7636,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7642,7 +7676,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7682,7 +7716,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7717,7 +7751,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7757,7 +7791,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7797,7 +7831,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7837,7 +7871,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7877,7 +7911,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7917,7 +7951,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7957,7 +7991,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -7997,7 +8031,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8037,7 +8071,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8077,7 +8111,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8117,7 +8151,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8157,7 +8191,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8227,7 +8261,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8267,7 +8301,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8307,7 +8341,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8347,7 +8381,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8387,7 +8421,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8427,7 +8461,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8467,7 +8501,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8532,7 +8566,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8572,7 +8606,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8612,7 +8646,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8652,7 +8686,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8692,7 +8726,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8777,7 +8811,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8817,7 +8851,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8857,7 +8891,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8927,7 +8961,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -8967,7 +9001,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9007,7 +9041,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -9047,7 +9081,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9087,7 +9121,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9127,7 +9161,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9167,7 +9201,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9207,7 +9241,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9247,7 +9281,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9317,7 +9351,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9357,7 +9391,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9397,7 +9431,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9437,7 +9471,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9477,7 +9511,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9517,7 +9551,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9557,7 +9591,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9597,7 +9631,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9637,7 +9671,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9677,7 +9711,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9717,7 +9751,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9757,7 +9791,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9797,7 +9831,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9837,7 +9871,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9877,7 +9911,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9917,7 +9951,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9957,7 +9991,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -9997,7 +10031,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10037,7 +10071,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10077,7 +10111,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10117,7 +10151,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10157,7 +10191,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10197,7 +10231,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10237,7 +10271,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10277,7 +10311,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10362,7 +10396,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10402,7 +10436,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10442,7 +10476,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10477,7 +10511,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10517,7 +10551,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10557,7 +10591,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10597,7 +10631,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10637,7 +10671,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10677,7 +10711,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10717,7 +10751,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10757,7 +10791,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10797,7 +10831,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10837,7 +10871,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10877,7 +10911,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10917,7 +10951,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10957,7 +10991,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -10997,7 +11031,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11037,7 +11071,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11077,7 +11111,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11147,7 +11181,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11187,7 +11221,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11227,7 +11261,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11267,7 +11301,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11307,7 +11341,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11347,7 +11381,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11387,7 +11421,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11427,7 +11461,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11467,7 +11501,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11507,7 +11541,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11547,7 +11581,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11582,7 +11616,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11622,7 +11656,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11662,7 +11696,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11702,7 +11736,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11742,7 +11776,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11782,7 +11816,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11822,7 +11856,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11862,7 +11896,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11897,7 +11931,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11937,7 +11971,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -11977,7 +12011,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -12017,7 +12051,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12057,7 +12091,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12097,7 +12131,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12137,7 +12171,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12177,7 +12211,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12217,7 +12251,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12257,7 +12291,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12297,7 +12331,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12337,7 +12371,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12407,7 +12441,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12447,7 +12481,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12487,7 +12521,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12527,7 +12561,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12567,7 +12601,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12637,7 +12671,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12677,7 +12711,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12717,7 +12751,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12757,7 +12791,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12797,7 +12831,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12837,7 +12871,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12877,7 +12911,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12917,7 +12951,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12957,7 +12991,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -12997,7 +13031,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13037,7 +13071,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13077,7 +13111,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13117,7 +13151,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13157,7 +13191,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13197,7 +13231,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13237,7 +13271,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13277,7 +13311,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13317,7 +13351,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13357,7 +13391,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13397,7 +13431,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13467,7 +13501,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13507,7 +13541,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13547,7 +13581,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13587,7 +13621,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13627,7 +13661,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13667,7 +13701,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13707,7 +13741,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13747,7 +13781,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13787,7 +13821,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13827,7 +13861,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13867,7 +13901,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13907,7 +13941,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13947,7 +13981,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -13987,7 +14021,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -14027,7 +14061,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14067,7 +14101,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14137,7 +14171,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14177,7 +14211,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14217,7 +14251,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14257,7 +14291,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14297,7 +14331,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14337,7 +14371,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14377,7 +14411,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14417,7 +14451,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14487,7 +14521,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14587,7 +14621,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14627,7 +14661,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14667,7 +14701,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14707,7 +14741,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14747,7 +14781,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14787,7 +14821,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14827,7 +14861,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14867,7 +14901,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14907,7 +14941,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14947,7 +14981,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -14987,7 +15021,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,6 +1014,40 @@
         <v>4</v>
       </c>
       <c r="J17" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>335</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>176</v>
+      </c>
+      <c r="F18" t="n">
+        <v>119</v>
+      </c>
+      <c r="G18" t="n">
+        <v>24</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1101,7 +1135,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1141,7 +1175,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1181,7 +1215,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1221,7 +1255,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1261,7 +1295,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1301,7 +1335,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1341,7 +1375,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1381,7 +1415,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1421,7 +1455,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1461,7 +1495,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1501,7 +1535,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1541,7 +1575,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1581,7 +1615,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1621,7 +1655,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1661,7 +1695,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1701,7 +1735,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1741,7 +1775,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1781,7 +1815,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1821,7 +1855,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1861,7 +1895,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1931,7 +1965,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -1971,7 +2005,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2011,7 +2045,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2051,7 +2085,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2091,7 +2125,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2131,7 +2165,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2171,7 +2205,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2211,7 +2245,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2251,7 +2285,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2291,7 +2325,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2356,7 +2390,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2396,7 +2430,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2436,7 +2470,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2476,7 +2510,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2516,7 +2550,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2556,7 +2590,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2596,7 +2630,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2636,7 +2670,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2676,7 +2710,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2716,7 +2750,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2756,7 +2790,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2796,7 +2830,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2836,7 +2870,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2876,7 +2910,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2916,7 +2950,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2956,7 +2990,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -2996,7 +3030,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -3036,7 +3070,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3076,7 +3110,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3116,7 +3150,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3156,7 +3190,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3226,7 +3260,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3266,7 +3300,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3306,7 +3340,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3346,7 +3380,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3386,7 +3420,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3426,7 +3460,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3466,7 +3500,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3506,7 +3540,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3546,7 +3580,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3586,7 +3620,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3626,7 +3660,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3666,7 +3700,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3706,7 +3740,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3746,7 +3780,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3786,7 +3820,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3826,7 +3860,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3866,7 +3900,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3906,7 +3940,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3946,7 +3980,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -3986,7 +4020,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -4026,7 +4060,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -4066,7 +4100,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4106,7 +4140,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4146,7 +4180,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4186,7 +4220,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4226,7 +4260,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4266,7 +4300,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4306,7 +4340,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4341,7 +4375,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4376,7 +4410,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4416,7 +4450,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4456,7 +4490,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4496,7 +4530,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4536,7 +4570,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4576,7 +4610,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4616,7 +4650,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4656,7 +4690,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4696,7 +4730,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4736,7 +4770,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4776,7 +4810,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4816,7 +4850,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4856,7 +4890,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4896,7 +4930,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4936,7 +4970,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -4976,7 +5010,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -5016,7 +5050,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -5056,7 +5090,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -5096,7 +5130,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5136,7 +5170,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5176,7 +5210,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5216,7 +5250,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5256,7 +5290,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5296,7 +5330,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5336,7 +5370,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5376,7 +5410,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5446,7 +5480,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5486,7 +5520,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5526,7 +5560,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5566,7 +5600,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5606,7 +5640,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5646,7 +5680,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5686,7 +5720,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5726,7 +5760,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5766,7 +5800,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5806,7 +5840,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5846,7 +5880,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5886,7 +5920,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5926,7 +5960,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -5966,7 +6000,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -6006,7 +6040,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -6046,7 +6080,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6086,7 +6120,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6126,7 +6160,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6166,7 +6200,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6206,7 +6240,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6246,7 +6280,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6286,7 +6320,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6326,7 +6360,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6366,7 +6400,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6406,7 +6440,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6446,7 +6480,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6486,7 +6520,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6526,7 +6560,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6566,7 +6600,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6636,7 +6670,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6676,7 +6710,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6716,7 +6750,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6756,7 +6790,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6796,7 +6830,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6836,7 +6870,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6876,7 +6910,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6916,7 +6950,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6956,7 +6990,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -6996,7 +7030,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -7036,7 +7070,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7076,7 +7110,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7116,7 +7150,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7156,7 +7190,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7196,7 +7230,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7236,7 +7270,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7276,7 +7310,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7316,7 +7350,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7356,7 +7390,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7396,7 +7430,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7436,7 +7470,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7476,7 +7510,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7516,7 +7550,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7556,7 +7590,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7596,7 +7630,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7636,7 +7670,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7676,7 +7710,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7716,7 +7750,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7751,7 +7785,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7791,7 +7825,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7831,7 +7865,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7871,7 +7905,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7911,7 +7945,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7951,7 +7985,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -7991,7 +8025,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -8031,7 +8065,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8071,7 +8105,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8111,7 +8145,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8151,7 +8185,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8191,7 +8225,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8261,7 +8295,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8301,7 +8335,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8341,7 +8375,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8381,7 +8415,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8421,7 +8455,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8461,7 +8495,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8501,7 +8535,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8566,7 +8600,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8606,7 +8640,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8646,7 +8680,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8686,7 +8720,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8726,7 +8760,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8811,7 +8845,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8851,7 +8885,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8891,7 +8925,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8961,7 +8995,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -9001,7 +9035,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9041,7 +9075,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -9081,7 +9115,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9121,7 +9155,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9161,7 +9195,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9201,7 +9235,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9241,7 +9275,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9281,7 +9315,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9351,7 +9385,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9391,7 +9425,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9431,7 +9465,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9471,7 +9505,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9511,7 +9545,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9551,7 +9585,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9591,7 +9625,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9631,7 +9665,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9671,7 +9705,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9711,7 +9745,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9751,7 +9785,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9791,7 +9825,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9831,7 +9865,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9871,7 +9905,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9911,7 +9945,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9951,7 +9985,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -9991,7 +10025,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -10031,7 +10065,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10071,7 +10105,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10111,7 +10145,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10151,7 +10185,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10191,7 +10225,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10231,7 +10265,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10271,7 +10305,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10311,7 +10345,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10396,7 +10430,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10436,7 +10470,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10476,7 +10510,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10511,7 +10545,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10551,7 +10585,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10591,7 +10625,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10631,7 +10665,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10671,7 +10705,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10711,7 +10745,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10751,7 +10785,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10791,7 +10825,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10831,7 +10865,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10871,7 +10905,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10911,7 +10945,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10951,7 +10985,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -10991,7 +11025,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -11031,7 +11065,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11071,7 +11105,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11111,7 +11145,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11181,7 +11215,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11221,7 +11255,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11261,7 +11295,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11301,7 +11335,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11341,7 +11375,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11381,7 +11415,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11421,7 +11455,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11461,7 +11495,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11501,7 +11535,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11541,7 +11575,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11581,7 +11615,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11616,7 +11650,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11656,7 +11690,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11696,7 +11730,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11736,7 +11770,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11776,7 +11810,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11816,7 +11850,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11856,7 +11890,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11896,7 +11930,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11931,7 +11965,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -11971,7 +12005,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -12011,7 +12045,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -12051,7 +12085,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12091,7 +12125,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12131,7 +12165,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12171,7 +12205,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12211,7 +12245,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12251,7 +12285,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12291,7 +12325,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12331,7 +12365,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12371,7 +12405,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12441,7 +12475,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12481,7 +12515,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12521,7 +12555,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12561,7 +12595,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12601,7 +12635,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12671,7 +12705,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12711,7 +12745,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12751,7 +12785,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12791,7 +12825,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12831,7 +12865,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12871,7 +12905,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12911,7 +12945,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12951,7 +12985,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -12991,7 +13025,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -13031,7 +13065,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13071,7 +13105,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13111,7 +13145,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13151,7 +13185,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13191,7 +13225,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13231,7 +13265,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13271,7 +13305,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13311,7 +13345,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13351,7 +13385,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13391,7 +13425,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13431,7 +13465,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13501,7 +13535,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13541,7 +13575,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13581,7 +13615,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13621,7 +13655,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13661,7 +13695,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13701,7 +13735,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13741,7 +13775,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13781,7 +13815,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13821,7 +13855,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13861,7 +13895,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13901,7 +13935,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13941,7 +13975,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -13981,7 +14015,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -14021,7 +14055,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -14061,7 +14095,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14101,7 +14135,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14171,7 +14205,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14211,7 +14245,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14251,7 +14285,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14291,7 +14325,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14331,7 +14365,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14371,7 +14405,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14411,7 +14445,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14451,7 +14485,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14521,7 +14555,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14621,7 +14655,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14661,7 +14695,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14701,7 +14735,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14741,7 +14775,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14781,7 +14815,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14821,7 +14855,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14861,7 +14895,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14901,7 +14935,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14941,7 +14975,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -14981,7 +15015,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -15021,7 +15055,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1048,40 @@
         <v>4</v>
       </c>
       <c r="J18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>334</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>175</v>
+      </c>
+      <c r="F19" t="n">
+        <v>119</v>
+      </c>
+      <c r="G19" t="n">
+        <v>24</v>
+      </c>
+      <c r="H19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1135,7 +1169,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1175,7 +1209,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1215,7 +1249,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1255,7 +1289,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1295,7 +1329,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1335,7 +1369,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1375,7 +1409,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1415,7 +1449,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1455,7 +1489,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1495,7 +1529,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1535,7 +1569,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1575,7 +1609,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1615,7 +1649,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1655,7 +1689,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1695,7 +1729,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1735,7 +1769,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1775,7 +1809,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1815,7 +1849,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1855,7 +1889,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1895,7 +1929,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1965,7 +1999,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -2005,7 +2039,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2045,7 +2079,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2085,7 +2119,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2125,7 +2159,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2165,7 +2199,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2205,7 +2239,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2245,7 +2279,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2285,7 +2319,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2325,7 +2359,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2390,7 +2424,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2430,7 +2464,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2470,7 +2504,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2510,7 +2544,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2550,7 +2584,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2590,7 +2624,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2630,7 +2664,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2670,7 +2704,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2710,7 +2744,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2750,7 +2784,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2790,7 +2824,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2830,7 +2864,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2870,7 +2904,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2910,7 +2944,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2950,7 +2984,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -2990,7 +3024,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -3030,7 +3064,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -3070,7 +3104,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3110,7 +3144,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3150,7 +3184,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3190,7 +3224,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3260,7 +3294,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3300,7 +3334,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3340,7 +3374,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3380,7 +3414,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3420,7 +3454,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3460,7 +3494,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3500,7 +3534,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3540,7 +3574,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3580,7 +3614,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3620,7 +3654,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3660,7 +3694,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3700,7 +3734,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3740,7 +3774,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3780,7 +3814,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3820,7 +3854,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3860,7 +3894,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3900,7 +3934,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3940,7 +3974,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -3980,7 +4014,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -4020,7 +4054,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -4060,7 +4094,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -4100,7 +4134,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4140,7 +4174,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4180,7 +4214,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4220,7 +4254,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4260,7 +4294,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4300,7 +4334,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4340,7 +4374,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4375,7 +4409,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4410,7 +4444,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4450,7 +4484,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4490,7 +4524,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4530,7 +4564,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4570,7 +4604,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4610,7 +4644,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4650,7 +4684,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4690,7 +4724,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4730,7 +4764,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4770,7 +4804,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4810,7 +4844,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4850,7 +4884,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4890,7 +4924,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4930,7 +4964,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -4974,7 +5008,12 @@
         </is>
       </c>
       <c r="F99" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -5010,7 +5049,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -5050,7 +5089,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -5090,7 +5129,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -5130,7 +5169,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5170,7 +5209,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5210,7 +5249,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5250,7 +5289,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5290,7 +5329,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5330,7 +5369,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5370,7 +5409,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5410,7 +5449,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5480,7 +5519,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5520,7 +5559,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5560,7 +5599,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5600,7 +5639,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5640,7 +5679,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5680,7 +5719,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5720,7 +5759,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5760,7 +5799,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5800,7 +5839,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5840,7 +5879,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5880,7 +5919,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5920,7 +5959,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5960,7 +5999,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -6000,7 +6039,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -6040,7 +6079,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -6080,7 +6119,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6120,7 +6159,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6160,7 +6199,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6200,7 +6239,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6240,7 +6279,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6280,7 +6319,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6320,7 +6359,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6360,7 +6399,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6400,7 +6439,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6440,7 +6479,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6480,7 +6519,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6520,7 +6559,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6560,7 +6599,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6600,7 +6639,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6670,7 +6709,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6710,7 +6749,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6750,7 +6789,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6790,7 +6829,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6830,7 +6869,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6870,7 +6909,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6910,7 +6949,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6950,7 +6989,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -6990,7 +7029,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -7030,7 +7069,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -7070,7 +7109,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7110,7 +7149,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7150,7 +7189,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7190,7 +7229,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7230,7 +7269,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7270,7 +7309,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7310,7 +7349,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7350,7 +7389,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7390,7 +7429,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7430,7 +7469,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7470,7 +7509,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7510,7 +7549,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7550,7 +7589,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7590,7 +7629,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7630,7 +7669,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7670,7 +7709,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7710,7 +7749,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7750,7 +7789,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7785,7 +7824,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7825,7 +7864,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7865,7 +7904,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7905,7 +7944,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7945,7 +7984,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -7985,7 +8024,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -8025,7 +8064,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -8065,7 +8104,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8105,7 +8144,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8145,7 +8184,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8185,7 +8224,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8225,7 +8264,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8295,7 +8334,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8335,7 +8374,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8375,7 +8414,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8415,7 +8454,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8455,7 +8494,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8495,7 +8534,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8535,7 +8574,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8600,7 +8639,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8640,7 +8679,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8680,7 +8719,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8720,7 +8759,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8760,7 +8799,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8845,7 +8884,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8885,7 +8924,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8925,7 +8964,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -8995,7 +9034,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -9035,7 +9074,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9075,7 +9114,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -9115,7 +9154,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9155,7 +9194,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9195,7 +9234,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9235,7 +9274,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9275,7 +9314,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9315,7 +9354,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9385,7 +9424,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9425,7 +9464,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9465,7 +9504,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9505,7 +9544,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9545,7 +9584,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9585,7 +9624,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9625,7 +9664,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9665,7 +9704,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9705,7 +9744,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9745,7 +9784,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9785,7 +9824,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9825,7 +9864,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9865,7 +9904,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9905,7 +9944,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9945,7 +9984,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -9985,7 +10024,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -10025,7 +10064,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -10065,7 +10104,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10105,7 +10144,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10145,7 +10184,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10185,7 +10224,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10225,7 +10264,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10265,7 +10304,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10305,7 +10344,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10345,7 +10384,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10430,7 +10469,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10470,7 +10509,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10510,7 +10549,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10545,7 +10584,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10585,7 +10624,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10625,7 +10664,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10665,7 +10704,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10705,7 +10744,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10745,7 +10784,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10785,7 +10824,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10825,7 +10864,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10865,7 +10904,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10905,7 +10944,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10945,7 +10984,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -10985,7 +11024,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -11025,7 +11064,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -11065,7 +11104,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11105,7 +11144,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11145,7 +11184,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11215,7 +11254,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11255,7 +11294,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11295,7 +11334,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11335,7 +11374,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11375,7 +11414,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11415,7 +11454,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11455,7 +11494,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11495,7 +11534,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11535,7 +11574,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11575,7 +11614,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11615,7 +11654,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11650,7 +11689,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11690,7 +11729,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11730,7 +11769,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11770,7 +11809,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11810,7 +11849,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11850,7 +11889,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11890,7 +11929,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11930,7 +11969,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -11965,7 +12004,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -12005,7 +12044,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -12045,7 +12084,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -12085,7 +12124,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12125,7 +12164,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12165,7 +12204,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12205,7 +12244,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12245,7 +12284,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12285,7 +12324,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12325,7 +12364,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12365,7 +12404,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12405,7 +12444,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12475,7 +12514,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12515,7 +12554,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12555,7 +12594,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12595,7 +12634,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12635,7 +12674,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12705,7 +12744,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12745,7 +12784,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12785,7 +12824,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12825,7 +12864,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12865,7 +12904,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12905,7 +12944,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12945,7 +12984,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -12985,7 +13024,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -13025,7 +13064,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -13065,7 +13104,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13105,7 +13144,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13145,7 +13184,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13185,7 +13224,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13225,7 +13264,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13265,7 +13304,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13305,7 +13344,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13345,7 +13384,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13385,7 +13424,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13425,7 +13464,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13465,7 +13504,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13535,7 +13574,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13575,7 +13614,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13615,7 +13654,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13655,7 +13694,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13695,7 +13734,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13735,7 +13774,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13775,7 +13814,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13815,7 +13854,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13855,7 +13894,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13895,7 +13934,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13935,7 +13974,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -13975,7 +14014,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -14015,7 +14054,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -14055,7 +14094,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -14095,7 +14134,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14135,7 +14174,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14205,7 +14244,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14245,7 +14284,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14285,7 +14324,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14325,7 +14364,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14365,7 +14404,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14405,7 +14444,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14445,7 +14484,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14485,7 +14524,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14555,7 +14594,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14655,7 +14694,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14695,7 +14734,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14735,7 +14774,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14775,7 +14814,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14815,7 +14854,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14855,7 +14894,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14895,7 +14934,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14935,7 +14974,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -14975,7 +15014,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -15015,7 +15054,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -15055,7 +15094,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,6 +1082,40 @@
         <v>4</v>
       </c>
       <c r="J19" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>334</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>175</v>
+      </c>
+      <c r="F20" t="n">
+        <v>119</v>
+      </c>
+      <c r="G20" t="n">
+        <v>24</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1169,7 +1203,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1209,7 +1243,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1249,7 +1283,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1289,7 +1323,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1329,7 +1363,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1369,7 +1403,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1409,7 +1443,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1449,7 +1483,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1489,7 +1523,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1529,7 +1563,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1569,7 +1603,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1609,7 +1643,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1649,7 +1683,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1689,7 +1723,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1729,7 +1763,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1769,7 +1803,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1809,7 +1843,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1849,7 +1883,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1889,7 +1923,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1929,7 +1963,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -1999,7 +2033,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -2039,7 +2073,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2079,7 +2113,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2119,7 +2153,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2159,7 +2193,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2199,7 +2233,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2239,7 +2273,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2279,7 +2313,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2319,7 +2353,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2359,7 +2393,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2424,7 +2458,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2464,7 +2498,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2504,7 +2538,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2544,7 +2578,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2584,7 +2618,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2624,7 +2658,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2664,7 +2698,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2704,7 +2738,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2744,7 +2778,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2784,7 +2818,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2824,7 +2858,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2864,7 +2898,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2904,7 +2938,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2944,7 +2978,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -2984,7 +3018,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -3024,7 +3058,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -3064,7 +3098,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -3104,7 +3138,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3144,7 +3178,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3184,7 +3218,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3224,7 +3258,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3294,7 +3328,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3334,7 +3368,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3374,7 +3408,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3414,7 +3448,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3454,7 +3488,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3494,7 +3528,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3534,7 +3568,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3574,7 +3608,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3614,7 +3648,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3654,7 +3688,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3694,7 +3728,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3734,7 +3768,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3774,7 +3808,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3814,7 +3848,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3854,7 +3888,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3894,7 +3928,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3934,7 +3968,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -3974,7 +4008,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -4014,7 +4048,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -4054,7 +4088,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -4094,7 +4128,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -4134,7 +4168,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4174,7 +4208,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4214,7 +4248,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4254,7 +4288,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4294,7 +4328,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4334,7 +4368,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4374,7 +4408,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4409,7 +4443,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4444,7 +4478,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4484,7 +4518,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4524,7 +4558,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4564,7 +4598,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4604,7 +4638,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4644,7 +4678,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4684,7 +4718,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4724,7 +4758,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4764,7 +4798,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4804,7 +4838,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4844,7 +4878,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4884,7 +4918,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4924,7 +4958,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4964,7 +4998,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -5049,7 +5083,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -5089,7 +5123,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -5129,7 +5163,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -5169,7 +5203,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5209,7 +5243,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5249,7 +5283,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5289,7 +5323,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5329,7 +5363,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5369,7 +5403,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5409,7 +5443,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5449,7 +5483,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5519,7 +5553,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5559,7 +5593,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5599,7 +5633,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5639,7 +5673,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5679,7 +5713,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5719,7 +5753,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5759,7 +5793,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5799,7 +5833,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5839,7 +5873,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5879,7 +5913,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5919,7 +5953,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5959,7 +5993,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -5999,7 +6033,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -6039,7 +6073,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -6079,7 +6113,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -6119,7 +6153,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6159,7 +6193,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6199,7 +6233,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6239,7 +6273,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6279,7 +6313,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6319,7 +6353,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6359,7 +6393,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6399,7 +6433,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6439,7 +6473,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6479,7 +6513,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6519,7 +6553,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6559,7 +6593,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6599,7 +6633,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6639,7 +6673,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6709,7 +6743,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6749,7 +6783,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6789,7 +6823,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6829,7 +6863,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6869,7 +6903,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6909,7 +6943,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6949,7 +6983,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -6989,7 +7023,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -7029,7 +7063,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -7069,7 +7103,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -7109,7 +7143,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7149,7 +7183,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7189,7 +7223,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7229,7 +7263,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7269,7 +7303,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7309,7 +7343,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7349,7 +7383,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7389,7 +7423,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7429,7 +7463,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7469,7 +7503,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7509,7 +7543,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7549,7 +7583,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7589,7 +7623,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7629,7 +7663,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7669,7 +7703,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7709,7 +7743,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7749,7 +7783,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7789,7 +7823,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7824,7 +7858,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7864,7 +7898,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7904,7 +7938,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7944,7 +7978,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -7984,7 +8018,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -8024,7 +8058,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -8064,7 +8098,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -8104,7 +8138,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8144,7 +8178,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8184,7 +8218,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8224,7 +8258,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8264,7 +8298,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8334,7 +8368,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8374,7 +8408,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8414,7 +8448,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8454,7 +8488,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8494,7 +8528,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8534,7 +8568,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8574,7 +8608,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8639,7 +8673,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8679,7 +8713,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8719,7 +8753,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8759,7 +8793,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8799,7 +8833,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8884,7 +8918,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8924,7 +8958,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8964,7 +8998,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -9034,7 +9068,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -9074,7 +9108,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9114,7 +9148,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -9154,7 +9188,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9194,7 +9228,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9234,7 +9268,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9274,7 +9308,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9314,7 +9348,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9354,7 +9388,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9424,7 +9458,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9464,7 +9498,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9504,7 +9538,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9544,7 +9578,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9584,7 +9618,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9624,7 +9658,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9664,7 +9698,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9704,7 +9738,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9744,7 +9778,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9784,7 +9818,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9824,7 +9858,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9864,7 +9898,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9904,7 +9938,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9944,7 +9978,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -9984,7 +10018,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -10024,7 +10058,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -10064,7 +10098,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -10104,7 +10138,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10144,7 +10178,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10184,7 +10218,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10224,7 +10258,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10264,7 +10298,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10304,7 +10338,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10344,7 +10378,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10384,7 +10418,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10469,7 +10503,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10509,7 +10543,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10549,7 +10583,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10584,7 +10618,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10624,7 +10658,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10664,7 +10698,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10704,7 +10738,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10744,7 +10778,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10784,7 +10818,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10824,7 +10858,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10864,7 +10898,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10904,7 +10938,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10944,7 +10978,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -10984,7 +11018,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -11024,7 +11058,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -11064,7 +11098,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -11104,7 +11138,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11144,7 +11178,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11184,7 +11218,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11254,7 +11288,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11294,7 +11328,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11334,7 +11368,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11374,7 +11408,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11414,7 +11448,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11454,7 +11488,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11494,7 +11528,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11534,7 +11568,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11574,7 +11608,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11614,7 +11648,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11654,7 +11688,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11689,7 +11723,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11729,7 +11763,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11769,7 +11803,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11809,7 +11843,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11849,7 +11883,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11889,7 +11923,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11929,7 +11963,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -11969,7 +12003,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -12004,7 +12038,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -12044,7 +12078,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -12084,7 +12118,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -12124,7 +12158,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12164,7 +12198,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12204,7 +12238,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12244,7 +12278,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12284,7 +12318,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12324,7 +12358,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12364,7 +12398,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12404,7 +12438,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12444,7 +12478,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12514,7 +12548,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12554,7 +12588,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12594,7 +12628,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12634,7 +12668,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12674,7 +12708,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12744,7 +12778,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12784,7 +12818,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12824,7 +12858,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12864,7 +12898,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12904,7 +12938,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12944,7 +12978,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -12984,7 +13018,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -13024,7 +13058,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -13064,7 +13098,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -13104,7 +13138,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13144,7 +13178,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13184,7 +13218,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13224,7 +13258,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13264,7 +13298,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13304,7 +13338,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13344,7 +13378,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13384,7 +13418,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13424,7 +13458,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13464,7 +13498,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13504,7 +13538,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13574,7 +13608,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13614,7 +13648,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13654,7 +13688,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13694,7 +13728,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13734,7 +13768,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13774,7 +13808,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13814,7 +13848,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13854,7 +13888,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13894,7 +13928,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13934,7 +13968,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -13974,7 +14008,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -14014,7 +14048,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -14054,7 +14088,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -14094,7 +14128,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -14134,7 +14168,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14174,7 +14208,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14244,7 +14278,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14284,7 +14318,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14324,7 +14358,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14364,7 +14398,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14404,7 +14438,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14444,7 +14478,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14484,7 +14518,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14524,7 +14558,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14594,7 +14628,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14694,7 +14728,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14734,7 +14768,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14774,7 +14808,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14814,7 +14848,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14854,7 +14888,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14894,7 +14928,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14934,7 +14968,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -14974,7 +15008,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -15014,7 +15048,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -15054,7 +15088,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -15094,7 +15128,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,6 +1116,40 @@
         <v>4</v>
       </c>
       <c r="J20" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>334</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>175</v>
+      </c>
+      <c r="F21" t="n">
+        <v>119</v>
+      </c>
+      <c r="G21" t="n">
+        <v>24</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1203,7 +1237,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1243,7 +1277,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1283,7 +1317,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1323,7 +1357,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1363,7 +1397,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1403,7 +1437,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1443,7 +1477,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1483,7 +1517,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1523,7 +1557,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1563,7 +1597,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1603,7 +1637,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1643,7 +1677,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1683,7 +1717,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1723,7 +1757,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1763,7 +1797,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1803,7 +1837,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1843,7 +1877,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1883,7 +1917,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1923,7 +1957,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1963,7 +1997,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2033,7 +2067,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -2073,7 +2107,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2113,7 +2147,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2153,7 +2187,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2193,7 +2227,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2233,7 +2267,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2273,7 +2307,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2313,7 +2347,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2353,7 +2387,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2393,7 +2427,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2458,7 +2492,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2498,7 +2532,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2538,7 +2572,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2578,7 +2612,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2618,7 +2652,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2658,7 +2692,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2698,7 +2732,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2738,7 +2772,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2778,7 +2812,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2818,7 +2852,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2858,7 +2892,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2898,7 +2932,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2938,7 +2972,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -2978,7 +3012,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -3018,7 +3052,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -3058,7 +3092,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -3098,7 +3132,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -3138,7 +3172,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3178,7 +3212,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3218,7 +3252,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3258,7 +3292,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3328,7 +3362,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3368,7 +3402,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3408,7 +3442,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3448,7 +3482,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3488,7 +3522,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3528,7 +3562,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3568,7 +3602,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3608,7 +3642,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3648,7 +3682,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3688,7 +3722,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3728,7 +3762,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3768,7 +3802,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3808,7 +3842,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3848,7 +3882,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3888,7 +3922,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3928,7 +3962,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -3968,7 +4002,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -4008,7 +4042,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -4048,7 +4082,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -4088,7 +4122,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -4128,7 +4162,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -4168,7 +4202,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4208,7 +4242,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4248,7 +4282,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4288,7 +4322,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4328,7 +4362,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4368,7 +4402,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4408,7 +4442,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4443,7 +4477,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4478,7 +4512,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4518,7 +4552,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4558,7 +4592,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4598,7 +4632,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4638,7 +4672,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4678,7 +4712,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4718,7 +4752,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4758,7 +4792,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4798,7 +4832,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4838,7 +4872,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4878,7 +4912,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4918,7 +4952,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4958,7 +4992,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -4998,7 +5032,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -5083,7 +5117,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -5123,7 +5157,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -5163,7 +5197,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -5203,7 +5237,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5243,7 +5277,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5283,7 +5317,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5323,7 +5357,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5363,7 +5397,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5403,7 +5437,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5443,7 +5477,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5483,7 +5517,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5553,7 +5587,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5593,7 +5627,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5633,7 +5667,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5673,7 +5707,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5713,7 +5747,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5753,7 +5787,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5793,7 +5827,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5833,7 +5867,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5873,7 +5907,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5913,7 +5947,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5953,7 +5987,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -5993,7 +6027,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -6033,7 +6067,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -6073,7 +6107,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -6113,7 +6147,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -6153,7 +6187,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6193,7 +6227,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6233,7 +6267,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6273,7 +6307,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6313,7 +6347,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6353,7 +6387,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6393,7 +6427,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6433,7 +6467,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6473,7 +6507,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6513,7 +6547,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6553,7 +6587,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6593,7 +6627,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6633,7 +6667,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6673,7 +6707,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6743,7 +6777,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6783,7 +6817,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6823,7 +6857,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6863,7 +6897,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6903,7 +6937,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6943,7 +6977,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -6983,7 +7017,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -7023,7 +7057,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -7063,7 +7097,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -7103,7 +7137,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -7143,7 +7177,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7183,7 +7217,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7223,7 +7257,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7263,7 +7297,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7303,7 +7337,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7343,7 +7377,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7383,7 +7417,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7423,7 +7457,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7463,7 +7497,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7503,7 +7537,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7543,7 +7577,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7583,7 +7617,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7623,7 +7657,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7663,7 +7697,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7703,7 +7737,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7743,7 +7777,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7783,7 +7817,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7823,7 +7857,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7858,7 +7892,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7898,7 +7932,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7938,7 +7972,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -7978,7 +8012,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -8018,7 +8052,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -8058,7 +8092,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -8098,7 +8132,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -8138,7 +8172,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8178,7 +8212,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8218,7 +8252,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8258,7 +8292,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8298,7 +8332,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8368,7 +8402,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8408,7 +8442,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8448,7 +8482,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8488,7 +8522,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8528,7 +8562,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8568,7 +8602,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8608,7 +8642,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8673,7 +8707,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8713,7 +8747,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8753,7 +8787,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8793,7 +8827,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8833,7 +8867,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8918,7 +8952,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8958,7 +8992,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -8998,7 +9032,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -9068,7 +9102,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -9108,7 +9142,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9148,7 +9182,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -9188,7 +9222,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9228,7 +9262,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9268,7 +9302,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9308,7 +9342,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9348,7 +9382,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9388,7 +9422,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9458,7 +9492,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9498,7 +9532,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9538,7 +9572,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9578,7 +9612,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9618,7 +9652,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9658,7 +9692,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9698,7 +9732,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9738,7 +9772,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9778,7 +9812,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9818,7 +9852,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9858,7 +9892,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9898,7 +9932,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9938,7 +9972,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -9978,7 +10012,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -10018,7 +10052,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -10058,7 +10092,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -10098,7 +10132,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -10138,7 +10172,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10178,7 +10212,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10218,7 +10252,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10258,7 +10292,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10298,7 +10332,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10338,7 +10372,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10378,7 +10412,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10418,7 +10452,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10503,7 +10537,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10543,7 +10577,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10583,7 +10617,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10618,7 +10652,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10658,7 +10692,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10698,7 +10732,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10738,7 +10772,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10778,7 +10812,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10818,7 +10852,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10858,7 +10892,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10898,7 +10932,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10938,7 +10972,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -10978,7 +11012,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -11018,7 +11052,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -11058,7 +11092,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -11098,7 +11132,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -11138,7 +11172,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11178,7 +11212,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11218,7 +11252,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11288,7 +11322,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11328,7 +11362,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11368,7 +11402,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11408,7 +11442,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11448,7 +11482,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11488,7 +11522,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11528,7 +11562,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11568,7 +11602,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11608,7 +11642,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11648,7 +11682,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11688,7 +11722,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11723,7 +11757,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11763,7 +11797,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11803,7 +11837,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11843,7 +11877,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11883,7 +11917,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11923,7 +11957,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11963,7 +11997,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -12003,7 +12037,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -12038,7 +12072,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -12078,7 +12112,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -12118,7 +12152,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -12158,7 +12192,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12198,7 +12232,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12238,7 +12272,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12278,7 +12312,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12318,7 +12352,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12358,7 +12392,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12398,7 +12432,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12438,7 +12472,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12478,7 +12512,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12548,7 +12582,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12588,7 +12622,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12628,7 +12662,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12668,7 +12702,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12708,7 +12742,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12778,7 +12812,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12818,7 +12852,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12858,7 +12892,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12898,7 +12932,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12938,7 +12972,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -12978,7 +13012,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -13018,7 +13052,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -13058,7 +13092,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -13098,7 +13132,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -13138,7 +13172,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13178,7 +13212,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13218,7 +13252,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13258,7 +13292,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13298,7 +13332,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13338,7 +13372,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13378,7 +13412,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13418,7 +13452,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13458,7 +13492,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13498,7 +13532,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13538,7 +13572,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13608,7 +13642,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13648,7 +13682,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13688,7 +13722,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13728,7 +13762,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13768,7 +13802,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13808,7 +13842,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13848,7 +13882,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13888,7 +13922,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13928,7 +13962,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -13968,7 +14002,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -14008,7 +14042,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -14048,7 +14082,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -14088,7 +14122,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -14128,7 +14162,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -14168,7 +14202,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14208,7 +14242,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14278,7 +14312,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14318,7 +14352,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14358,7 +14392,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14398,7 +14432,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14438,7 +14472,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14478,7 +14512,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14518,7 +14552,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14558,7 +14592,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14628,7 +14662,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14728,7 +14762,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14768,7 +14802,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14808,7 +14842,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14848,7 +14882,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14888,7 +14922,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14928,7 +14962,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -14968,7 +15002,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -15008,7 +15042,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -15048,7 +15082,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -15088,7 +15122,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -15128,7 +15162,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1150,6 +1150,40 @@
         <v>4</v>
       </c>
       <c r="J21" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>334</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>175</v>
+      </c>
+      <c r="F22" t="n">
+        <v>119</v>
+      </c>
+      <c r="G22" t="n">
+        <v>24</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1237,7 +1271,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1277,7 +1311,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1317,7 +1351,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1357,7 +1391,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1397,7 +1431,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1437,7 +1471,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1477,7 +1511,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1517,7 +1551,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1557,7 +1591,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1597,7 +1631,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1637,7 +1671,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1677,7 +1711,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1717,7 +1751,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1757,7 +1791,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1797,7 +1831,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1837,7 +1871,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1877,7 +1911,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1917,7 +1951,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1957,7 +1991,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -1997,7 +2031,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2067,7 +2101,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -2107,7 +2141,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2147,7 +2181,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2187,7 +2221,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2227,7 +2261,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2267,7 +2301,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2307,7 +2341,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2347,7 +2381,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2387,7 +2421,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2427,7 +2461,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2492,7 +2526,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2532,7 +2566,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2572,7 +2606,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2612,7 +2646,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2652,7 +2686,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2692,7 +2726,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2732,7 +2766,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2772,7 +2806,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2812,7 +2846,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2852,7 +2886,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2892,7 +2926,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2932,7 +2966,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -2972,7 +3006,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -3012,7 +3046,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -3052,7 +3086,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -3092,7 +3126,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -3132,7 +3166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -3172,7 +3206,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3212,7 +3246,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3252,7 +3286,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3292,7 +3326,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3362,7 +3396,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3402,7 +3436,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3442,7 +3476,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3482,7 +3516,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3522,7 +3556,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3562,7 +3596,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3602,7 +3636,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3642,7 +3676,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3682,7 +3716,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3722,7 +3756,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3762,7 +3796,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3802,7 +3836,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3842,7 +3876,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3882,7 +3916,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3922,7 +3956,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3962,7 +3996,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -4002,7 +4036,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -4042,7 +4076,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -4082,7 +4116,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -4122,7 +4156,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -4162,7 +4196,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -4202,7 +4236,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4242,7 +4276,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4282,7 +4316,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4322,7 +4356,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4362,7 +4396,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4402,7 +4436,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4442,7 +4476,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4477,7 +4511,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4512,7 +4546,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4552,7 +4586,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4592,7 +4626,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4632,7 +4666,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4672,7 +4706,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4712,7 +4746,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4752,7 +4786,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4792,7 +4826,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4832,7 +4866,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4872,7 +4906,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4912,7 +4946,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4952,7 +4986,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -4992,7 +5026,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -5032,7 +5066,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -5117,7 +5151,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -5157,7 +5191,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -5197,7 +5231,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -5237,7 +5271,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5277,7 +5311,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5317,7 +5351,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5357,7 +5391,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5397,7 +5431,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5437,7 +5471,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5477,7 +5511,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5517,7 +5551,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5587,7 +5621,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5627,7 +5661,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5667,7 +5701,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5707,7 +5741,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5747,7 +5781,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5787,7 +5821,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5827,7 +5861,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5867,7 +5901,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5907,7 +5941,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5947,7 +5981,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -5987,7 +6021,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -6027,7 +6061,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -6067,7 +6101,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -6107,7 +6141,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -6147,7 +6181,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -6187,7 +6221,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6227,7 +6261,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6267,7 +6301,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6307,7 +6341,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6347,7 +6381,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6387,7 +6421,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6427,7 +6461,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6467,7 +6501,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6507,7 +6541,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6547,7 +6581,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6587,7 +6621,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6627,7 +6661,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6667,7 +6701,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6707,7 +6741,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6777,7 +6811,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6817,7 +6851,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6857,7 +6891,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6897,7 +6931,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6937,7 +6971,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -6977,7 +7011,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -7017,7 +7051,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -7057,7 +7091,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -7097,7 +7131,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -7137,7 +7171,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -7177,7 +7211,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7217,7 +7251,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7257,7 +7291,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7297,7 +7331,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7337,7 +7371,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7377,7 +7411,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7417,7 +7451,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7457,7 +7491,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7497,7 +7531,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7537,7 +7571,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7577,7 +7611,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7617,7 +7651,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7657,7 +7691,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7697,7 +7731,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7737,7 +7771,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7777,7 +7811,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7817,7 +7851,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7857,7 +7891,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7892,7 +7926,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7932,7 +7966,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -7972,7 +8006,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -8012,7 +8046,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -8052,7 +8086,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -8092,7 +8126,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -8132,7 +8166,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -8172,7 +8206,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8212,7 +8246,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8252,7 +8286,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8292,7 +8326,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8332,7 +8366,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8402,7 +8436,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8442,7 +8476,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8482,7 +8516,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8522,7 +8556,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8562,7 +8596,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8602,7 +8636,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8642,7 +8676,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8707,7 +8741,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8747,7 +8781,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8787,7 +8821,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8827,7 +8861,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8867,7 +8901,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8952,7 +8986,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -8992,7 +9026,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -9032,7 +9066,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -9102,7 +9136,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -9142,7 +9176,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9182,7 +9216,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -9222,7 +9256,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9262,7 +9296,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9302,7 +9336,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9342,7 +9376,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9382,7 +9416,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9422,7 +9456,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9492,7 +9526,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9532,7 +9566,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9572,7 +9606,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9612,7 +9646,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9652,7 +9686,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9692,7 +9726,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9732,7 +9766,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9772,7 +9806,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9812,7 +9846,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9852,7 +9886,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9892,7 +9926,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9932,7 +9966,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -9972,7 +10006,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -10012,7 +10046,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -10052,7 +10086,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -10092,7 +10126,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -10132,7 +10166,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -10172,7 +10206,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10212,7 +10246,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10252,7 +10286,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10292,7 +10326,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10332,7 +10366,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10372,7 +10406,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10412,7 +10446,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10452,7 +10486,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10537,7 +10571,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10577,7 +10611,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10617,7 +10651,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10652,7 +10686,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10692,7 +10726,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10732,7 +10766,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10772,7 +10806,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10812,7 +10846,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10852,7 +10886,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10892,7 +10926,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10932,7 +10966,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -10972,7 +11006,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -11012,7 +11046,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -11052,7 +11086,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -11092,7 +11126,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -11132,7 +11166,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -11172,7 +11206,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11212,7 +11246,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11252,7 +11286,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11322,7 +11356,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11362,7 +11396,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11402,7 +11436,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11442,7 +11476,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11482,7 +11516,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11522,7 +11556,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11562,7 +11596,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11602,7 +11636,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11642,7 +11676,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11682,7 +11716,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11722,7 +11756,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11757,7 +11791,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11797,7 +11831,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11837,7 +11871,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11877,7 +11911,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11917,7 +11951,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11957,7 +11991,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -11997,7 +12031,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -12037,7 +12071,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -12072,7 +12106,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -12112,7 +12146,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -12152,7 +12186,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -12192,7 +12226,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12232,7 +12266,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12272,7 +12306,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12312,7 +12346,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12352,7 +12386,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12392,7 +12426,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12432,7 +12466,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12472,7 +12506,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12512,7 +12546,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12582,7 +12616,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12622,7 +12656,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12662,7 +12696,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12702,7 +12736,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12742,7 +12776,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12812,7 +12846,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12852,7 +12886,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12892,7 +12926,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12932,7 +12966,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -12972,7 +13006,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -13012,7 +13046,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -13052,7 +13086,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -13092,7 +13126,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -13132,7 +13166,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -13172,7 +13206,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13212,7 +13246,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13252,7 +13286,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13292,7 +13326,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13332,7 +13366,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13372,7 +13406,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13412,7 +13446,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13452,7 +13486,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13492,7 +13526,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13532,7 +13566,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13572,7 +13606,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13642,7 +13676,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13682,7 +13716,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13722,7 +13756,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13762,7 +13796,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13802,7 +13836,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13842,7 +13876,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13882,7 +13916,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13922,7 +13956,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13962,7 +13996,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -14002,7 +14036,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -14042,7 +14076,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -14082,7 +14116,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -14122,7 +14156,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -14162,7 +14196,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -14202,7 +14236,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14242,7 +14276,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14312,7 +14346,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14352,7 +14386,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14392,7 +14426,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14432,7 +14466,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14472,7 +14506,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14512,7 +14546,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14552,7 +14586,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14592,7 +14626,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14662,7 +14696,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14762,7 +14796,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14802,7 +14836,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14842,7 +14876,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14882,7 +14916,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14922,7 +14956,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14962,7 +14996,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -15002,7 +15036,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -15042,7 +15076,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -15082,7 +15116,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -15122,7 +15156,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -15162,7 +15196,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1184,6 +1184,40 @@
         <v>4</v>
       </c>
       <c r="J22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>334</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>175</v>
+      </c>
+      <c r="F23" t="n">
+        <v>119</v>
+      </c>
+      <c r="G23" t="n">
+        <v>24</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1271,7 +1305,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1311,7 +1345,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1351,7 +1385,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1391,7 +1425,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1431,7 +1465,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1471,7 +1505,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1511,7 +1545,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1551,7 +1585,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1591,7 +1625,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1631,7 +1665,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1671,7 +1705,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1711,7 +1745,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1751,7 +1785,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1791,7 +1825,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1831,7 +1865,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1871,7 +1905,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1911,7 +1945,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1951,7 +1985,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -1991,7 +2025,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -2031,7 +2065,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2101,7 +2135,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -2141,7 +2175,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2181,7 +2215,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2221,7 +2255,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2261,7 +2295,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2301,7 +2335,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2341,7 +2375,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2381,7 +2415,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2421,7 +2455,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2461,7 +2495,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2526,7 +2560,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2566,7 +2600,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2606,7 +2640,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2646,7 +2680,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2686,7 +2720,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2726,7 +2760,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2766,7 +2800,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2806,7 +2840,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2846,7 +2880,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2886,7 +2920,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2926,7 +2960,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -2966,7 +3000,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -3006,7 +3040,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -3046,7 +3080,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -3086,7 +3120,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -3126,7 +3160,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -3166,7 +3200,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -3206,7 +3240,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3246,7 +3280,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3286,7 +3320,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3326,7 +3360,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3396,7 +3430,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3436,7 +3470,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3476,7 +3510,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3516,7 +3550,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3556,7 +3590,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3596,7 +3630,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3636,7 +3670,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3676,7 +3710,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3716,7 +3750,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3756,7 +3790,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3796,7 +3830,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3836,7 +3870,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3876,7 +3910,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3916,7 +3950,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3956,7 +3990,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -3996,7 +4030,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -4036,7 +4070,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -4076,7 +4110,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -4116,7 +4150,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -4156,7 +4190,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -4196,7 +4230,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -4236,7 +4270,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4276,7 +4310,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4316,7 +4350,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4356,7 +4390,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4396,7 +4430,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4436,7 +4470,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4476,7 +4510,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4511,7 +4545,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4546,7 +4580,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4586,7 +4620,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4626,7 +4660,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4666,7 +4700,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4706,7 +4740,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4746,7 +4780,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4786,7 +4820,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4826,7 +4860,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4866,7 +4900,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4906,7 +4940,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4946,7 +4980,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -4986,7 +5020,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -5026,7 +5060,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -5066,7 +5100,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -5151,7 +5185,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -5191,7 +5225,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -5231,7 +5265,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -5271,7 +5305,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5311,7 +5345,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5351,7 +5385,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5391,7 +5425,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5431,7 +5465,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5471,7 +5505,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5511,7 +5545,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5551,7 +5585,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5621,7 +5655,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5661,7 +5695,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5701,7 +5735,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5741,7 +5775,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5781,7 +5815,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5821,7 +5855,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5861,7 +5895,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5901,7 +5935,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5941,7 +5975,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -5981,7 +6015,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -6021,7 +6055,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -6061,7 +6095,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -6101,7 +6135,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -6141,7 +6175,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -6181,7 +6215,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -6221,7 +6255,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6261,7 +6295,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6301,7 +6335,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6341,7 +6375,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6381,7 +6415,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6421,7 +6455,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6461,7 +6495,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6501,7 +6535,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6541,7 +6575,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6581,7 +6615,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6621,7 +6655,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6661,7 +6695,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6701,7 +6735,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6741,7 +6775,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6811,7 +6845,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6851,7 +6885,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6891,7 +6925,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6931,7 +6965,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -6971,7 +7005,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -7011,7 +7045,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -7051,7 +7085,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -7091,7 +7125,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -7131,7 +7165,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -7171,7 +7205,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -7211,7 +7245,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7251,7 +7285,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7291,7 +7325,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7331,7 +7365,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7371,7 +7405,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7411,7 +7445,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7451,7 +7485,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7491,7 +7525,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7531,7 +7565,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7571,7 +7605,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7611,7 +7645,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7651,7 +7685,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7691,7 +7725,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7731,7 +7765,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7771,7 +7805,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7811,7 +7845,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7851,7 +7885,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7891,7 +7925,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7926,7 +7960,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -7966,7 +8000,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -8006,7 +8040,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -8046,7 +8080,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -8086,7 +8120,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -8126,7 +8160,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -8166,7 +8200,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -8206,7 +8240,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8246,7 +8280,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8286,7 +8320,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8326,7 +8360,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8366,7 +8400,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8436,7 +8470,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8476,7 +8510,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8516,7 +8550,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8556,7 +8590,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8596,7 +8630,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8636,7 +8670,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8676,7 +8710,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8741,7 +8775,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8781,7 +8815,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8821,7 +8855,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8861,7 +8895,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8901,7 +8935,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -8986,7 +9020,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -9026,7 +9060,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -9066,7 +9100,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -9136,7 +9170,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -9176,7 +9210,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9216,7 +9250,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -9256,7 +9290,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9296,7 +9330,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9336,7 +9370,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9376,7 +9410,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9416,7 +9450,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9456,7 +9490,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9526,7 +9560,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9566,7 +9600,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9606,7 +9640,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9646,7 +9680,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9686,7 +9720,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9726,7 +9760,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9766,7 +9800,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9806,7 +9840,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9846,7 +9880,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9886,7 +9920,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9926,7 +9960,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -9966,7 +10000,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -10006,7 +10040,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -10046,7 +10080,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -10086,7 +10120,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -10126,7 +10160,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -10166,7 +10200,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -10206,7 +10240,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10246,7 +10280,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10286,7 +10320,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10326,7 +10360,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10366,7 +10400,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10406,7 +10440,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10446,7 +10480,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10486,7 +10520,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10571,7 +10605,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10611,7 +10645,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10651,7 +10685,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10686,7 +10720,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10726,7 +10760,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10766,7 +10800,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10806,7 +10840,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10846,7 +10880,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10886,7 +10920,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10926,7 +10960,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -10966,7 +11000,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -11006,7 +11040,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -11046,7 +11080,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -11086,7 +11120,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -11126,7 +11160,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -11166,7 +11200,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -11206,7 +11240,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11246,7 +11280,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11286,7 +11320,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11356,7 +11390,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11396,7 +11430,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11436,7 +11470,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11476,7 +11510,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11516,7 +11550,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11556,7 +11590,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11596,7 +11630,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11636,7 +11670,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11676,7 +11710,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11716,7 +11750,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11756,7 +11790,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11791,7 +11825,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11831,7 +11865,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11871,7 +11905,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11911,7 +11945,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11951,7 +11985,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -11991,7 +12025,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -12031,7 +12065,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -12071,7 +12105,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -12106,7 +12140,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -12146,7 +12180,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -12186,7 +12220,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -12226,7 +12260,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12266,7 +12300,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12306,7 +12340,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12346,7 +12380,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12386,7 +12420,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12426,7 +12460,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12466,7 +12500,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12506,7 +12540,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12546,7 +12580,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12616,7 +12650,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12656,7 +12690,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12696,7 +12730,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12736,7 +12770,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12776,7 +12810,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12846,7 +12880,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12886,7 +12920,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12926,7 +12960,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -12966,7 +13000,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -13006,7 +13040,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -13046,7 +13080,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -13086,7 +13120,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -13126,7 +13160,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -13166,7 +13200,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -13206,7 +13240,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13246,7 +13280,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13286,7 +13320,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13326,7 +13360,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13366,7 +13400,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13406,7 +13440,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13446,7 +13480,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13486,7 +13520,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13526,7 +13560,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13566,7 +13600,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13606,7 +13640,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13676,7 +13710,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13716,7 +13750,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13756,7 +13790,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13796,7 +13830,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13836,7 +13870,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13876,7 +13910,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13916,7 +13950,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13956,7 +13990,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -13996,7 +14030,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -14036,7 +14070,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -14076,7 +14110,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -14116,7 +14150,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -14156,7 +14190,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -14196,7 +14230,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -14236,7 +14270,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14276,7 +14310,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14346,7 +14380,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14386,7 +14420,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14426,7 +14460,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14466,7 +14500,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14506,7 +14540,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14546,7 +14580,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14586,7 +14620,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14626,7 +14660,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14696,7 +14730,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14796,7 +14830,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14836,7 +14870,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14876,7 +14910,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14916,7 +14950,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14956,7 +14990,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -14996,7 +15030,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -15036,7 +15070,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -15076,7 +15110,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -15116,7 +15150,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -15156,7 +15190,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -15196,7 +15230,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,6 +1218,40 @@
         <v>4</v>
       </c>
       <c r="J23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>334</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>175</v>
+      </c>
+      <c r="F24" t="n">
+        <v>119</v>
+      </c>
+      <c r="G24" t="n">
+        <v>24</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1305,7 +1339,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1345,7 +1379,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1385,7 +1419,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1425,7 +1459,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1465,7 +1499,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1505,7 +1539,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1545,7 +1579,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1585,7 +1619,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1625,7 +1659,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1665,7 +1699,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1705,7 +1739,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1745,7 +1779,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1785,7 +1819,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1825,7 +1859,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1865,7 +1899,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1905,7 +1939,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1945,7 +1979,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -1985,7 +2019,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -2025,7 +2059,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -2065,7 +2099,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2135,7 +2169,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -2175,7 +2209,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2215,7 +2249,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2255,7 +2289,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2295,7 +2329,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2335,7 +2369,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2375,7 +2409,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2415,7 +2449,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2455,7 +2489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2495,7 +2529,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2560,7 +2594,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2600,7 +2634,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2640,7 +2674,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2680,7 +2714,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2720,7 +2754,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2760,7 +2794,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2800,7 +2834,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2840,7 +2874,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2880,7 +2914,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2920,7 +2954,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2960,7 +2994,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -3000,7 +3034,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -3040,7 +3074,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -3080,7 +3114,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -3120,7 +3154,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -3160,7 +3194,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -3200,7 +3234,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -3240,7 +3274,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3280,7 +3314,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3320,7 +3354,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3360,7 +3394,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3430,7 +3464,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3470,7 +3504,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3510,7 +3544,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3550,7 +3584,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3590,7 +3624,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3630,7 +3664,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3670,7 +3704,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3710,7 +3744,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3750,7 +3784,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3790,7 +3824,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3830,7 +3864,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3870,7 +3904,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3910,7 +3944,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3950,7 +3984,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -3990,7 +4024,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -4030,7 +4064,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -4070,7 +4104,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -4110,7 +4144,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -4150,7 +4184,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -4190,7 +4224,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -4230,7 +4264,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -4270,7 +4304,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4310,7 +4344,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4350,7 +4384,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4390,7 +4424,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4430,7 +4464,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4470,7 +4504,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4510,7 +4544,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4545,7 +4579,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4580,7 +4614,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4620,7 +4654,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4660,7 +4694,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4700,7 +4734,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4740,7 +4774,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4780,7 +4814,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4820,7 +4854,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4860,7 +4894,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4900,7 +4934,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4940,7 +4974,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -4980,7 +5014,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -5020,7 +5054,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -5060,7 +5094,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -5100,7 +5134,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -5185,7 +5219,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -5225,7 +5259,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -5265,7 +5299,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -5305,7 +5339,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5345,7 +5379,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5385,7 +5419,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5425,7 +5459,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5465,7 +5499,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5505,7 +5539,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5545,7 +5579,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5585,7 +5619,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5655,7 +5689,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5695,7 +5729,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5735,7 +5769,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5775,7 +5809,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5815,7 +5849,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5855,7 +5889,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5895,7 +5929,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5935,7 +5969,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -5975,7 +6009,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -6015,7 +6049,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -6055,7 +6089,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -6095,7 +6129,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -6135,7 +6169,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -6175,7 +6209,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -6215,7 +6249,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -6255,7 +6289,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6295,7 +6329,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6335,7 +6369,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6375,7 +6409,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6415,7 +6449,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6455,7 +6489,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6495,7 +6529,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6535,7 +6569,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6575,7 +6609,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6615,7 +6649,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6655,7 +6689,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6695,7 +6729,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6735,7 +6769,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6775,7 +6809,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6845,7 +6879,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6885,7 +6919,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6925,7 +6959,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6965,7 +6999,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -7005,7 +7039,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -7045,7 +7079,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -7085,7 +7119,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -7125,7 +7159,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -7165,7 +7199,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -7205,7 +7239,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -7245,7 +7279,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7285,7 +7319,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7325,7 +7359,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7365,7 +7399,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7405,7 +7439,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7445,7 +7479,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7485,7 +7519,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7525,7 +7559,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7565,7 +7599,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7605,7 +7639,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7645,7 +7679,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7685,7 +7719,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7725,7 +7759,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7765,7 +7799,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7805,7 +7839,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7845,7 +7879,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7885,7 +7919,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7925,7 +7959,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7960,7 +7994,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -8000,7 +8034,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -8040,7 +8074,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -8080,7 +8114,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -8120,7 +8154,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -8160,7 +8194,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -8200,7 +8234,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -8240,7 +8274,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8280,7 +8314,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8320,7 +8354,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8360,7 +8394,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8400,7 +8434,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8470,7 +8504,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8510,7 +8544,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8550,7 +8584,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8590,7 +8624,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8630,7 +8664,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8670,7 +8704,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8710,7 +8744,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8775,7 +8809,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8815,7 +8849,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8855,7 +8889,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8895,7 +8929,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8935,7 +8969,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -9020,7 +9054,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -9060,7 +9094,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -9100,7 +9134,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -9170,7 +9204,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -9210,7 +9244,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9250,7 +9284,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -9290,7 +9324,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9330,7 +9364,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9370,7 +9404,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9410,7 +9444,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9450,7 +9484,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9490,7 +9524,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9560,7 +9594,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9600,7 +9634,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9640,7 +9674,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9680,7 +9714,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9720,7 +9754,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9760,7 +9794,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9800,7 +9834,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9840,7 +9874,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9880,7 +9914,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9920,7 +9954,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9960,7 +9994,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -10000,7 +10034,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -10040,7 +10074,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -10080,7 +10114,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -10120,7 +10154,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -10160,7 +10194,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -10200,7 +10234,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -10240,7 +10274,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10280,7 +10314,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10320,7 +10354,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10360,7 +10394,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10400,7 +10434,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10440,7 +10474,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10480,7 +10514,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10520,7 +10554,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10605,7 +10639,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10645,7 +10679,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10685,7 +10719,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10720,7 +10754,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10760,7 +10794,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10800,7 +10834,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10840,7 +10874,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10880,7 +10914,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10920,7 +10954,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10960,7 +10994,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -11000,7 +11034,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -11040,7 +11074,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -11080,7 +11114,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -11120,7 +11154,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -11160,7 +11194,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -11200,7 +11234,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -11240,7 +11274,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11280,7 +11314,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11320,7 +11354,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11390,7 +11424,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11430,7 +11464,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11470,7 +11504,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11510,7 +11544,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11550,7 +11584,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11590,7 +11624,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11630,7 +11664,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11670,7 +11704,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11710,7 +11744,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11750,7 +11784,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11790,7 +11824,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11825,7 +11859,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11865,7 +11899,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11905,7 +11939,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11945,7 +11979,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -11985,7 +12019,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -12025,7 +12059,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -12065,7 +12099,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -12105,7 +12139,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -12140,7 +12174,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -12180,7 +12214,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -12220,7 +12254,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -12260,7 +12294,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12300,7 +12334,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12340,7 +12374,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12380,7 +12414,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12420,7 +12454,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12460,7 +12494,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12500,7 +12534,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12540,7 +12574,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12580,7 +12614,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12650,7 +12684,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12690,7 +12724,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12730,7 +12764,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12770,7 +12804,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12810,7 +12844,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12880,7 +12914,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12920,7 +12954,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12960,7 +12994,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -13000,7 +13034,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -13040,7 +13074,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -13080,7 +13114,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -13120,7 +13154,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -13160,7 +13194,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -13200,7 +13234,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -13240,7 +13274,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13280,7 +13314,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13320,7 +13354,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13360,7 +13394,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13400,7 +13434,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13440,7 +13474,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13480,7 +13514,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13520,7 +13554,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13560,7 +13594,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13600,7 +13634,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13640,7 +13674,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13710,7 +13744,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13750,7 +13784,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13790,7 +13824,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13830,7 +13864,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13870,7 +13904,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13910,7 +13944,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13950,7 +13984,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -13990,7 +14024,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -14030,7 +14064,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -14070,7 +14104,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -14110,7 +14144,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -14150,7 +14184,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -14190,7 +14224,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -14230,7 +14264,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -14270,7 +14304,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14310,7 +14344,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14380,7 +14414,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14420,7 +14454,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14460,7 +14494,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14500,7 +14534,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14540,7 +14574,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14580,7 +14614,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14620,7 +14654,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14660,7 +14694,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14730,7 +14764,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14830,7 +14864,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14870,7 +14904,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14910,7 +14944,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14950,7 +14984,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -14990,7 +15024,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -15030,7 +15064,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -15070,7 +15104,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -15110,7 +15144,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -15150,7 +15184,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -15190,7 +15224,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -15230,7 +15264,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1252,6 +1252,40 @@
         <v>4</v>
       </c>
       <c r="J24" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>334</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>175</v>
+      </c>
+      <c r="F25" t="n">
+        <v>119</v>
+      </c>
+      <c r="G25" t="n">
+        <v>24</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1339,7 +1373,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1379,7 +1413,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1419,7 +1453,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1459,7 +1493,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1499,7 +1533,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1539,7 +1573,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1579,7 +1613,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1619,7 +1653,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1659,7 +1693,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1699,7 +1733,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1739,7 +1773,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1779,7 +1813,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1819,7 +1853,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1859,7 +1893,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -1899,7 +1933,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -1939,7 +1973,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -1979,7 +2013,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -2019,7 +2053,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -2059,7 +2093,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -2099,7 +2133,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2169,7 +2203,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -2209,7 +2243,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2249,7 +2283,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2289,7 +2323,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2329,7 +2363,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2369,7 +2403,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2409,7 +2443,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2449,7 +2483,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2489,7 +2523,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2529,7 +2563,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2594,7 +2628,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2634,7 +2668,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2674,7 +2708,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2714,7 +2748,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2754,7 +2788,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2794,7 +2828,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2834,7 +2868,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -2874,7 +2908,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -2914,7 +2948,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -2954,7 +2988,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -2994,7 +3028,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -3034,7 +3068,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -3074,7 +3108,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -3114,7 +3148,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -3154,7 +3188,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -3194,7 +3228,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -3234,7 +3268,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -3274,7 +3308,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3314,7 +3348,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3354,7 +3388,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3394,7 +3428,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3464,7 +3498,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3504,7 +3538,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3544,7 +3578,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3584,7 +3618,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3624,7 +3658,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3664,7 +3698,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3704,7 +3738,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3744,7 +3778,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3784,7 +3818,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3824,7 +3858,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -3864,7 +3898,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -3904,7 +3938,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -3944,7 +3978,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -3984,7 +4018,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -4024,7 +4058,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -4064,7 +4098,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -4104,7 +4138,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -4144,7 +4178,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -4184,7 +4218,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -4224,7 +4258,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -4264,7 +4298,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -4304,7 +4338,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4344,7 +4378,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4384,7 +4418,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4424,7 +4458,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4464,7 +4498,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4504,7 +4538,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4544,7 +4578,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4579,7 +4613,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4614,7 +4648,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4654,7 +4688,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4694,7 +4728,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4734,7 +4768,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4774,7 +4808,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4814,7 +4848,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4854,7 +4888,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -4894,7 +4928,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -4934,7 +4968,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -4974,7 +5008,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -5014,7 +5048,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -5054,7 +5088,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -5094,7 +5128,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -5134,7 +5168,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -5219,7 +5253,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -5259,7 +5293,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -5299,7 +5333,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -5339,7 +5373,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5379,7 +5413,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5419,7 +5453,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5459,7 +5493,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5499,7 +5533,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5539,7 +5573,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5579,7 +5613,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5619,7 +5653,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5689,7 +5723,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5729,7 +5763,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5769,7 +5803,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5809,7 +5843,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5849,7 +5883,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -5889,7 +5923,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -5929,7 +5963,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -5969,7 +6003,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -6009,7 +6043,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -6049,7 +6083,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -6089,7 +6123,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -6129,7 +6163,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -6169,7 +6203,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -6209,7 +6243,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -6249,7 +6283,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -6289,7 +6323,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6329,7 +6363,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6369,7 +6403,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6409,7 +6443,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6449,7 +6483,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6489,7 +6523,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6529,7 +6563,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6569,7 +6603,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6609,7 +6643,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6649,7 +6683,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6689,7 +6723,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6729,7 +6763,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6769,7 +6803,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6809,7 +6843,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6879,7 +6913,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -6919,7 +6953,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -6959,7 +6993,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -6999,7 +7033,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -7039,7 +7073,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -7079,7 +7113,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -7119,7 +7153,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -7159,7 +7193,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -7199,7 +7233,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -7239,7 +7273,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -7279,7 +7313,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7319,7 +7353,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7359,7 +7393,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7399,7 +7433,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7439,7 +7473,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7479,7 +7513,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7519,7 +7553,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7559,7 +7593,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7599,7 +7633,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7639,7 +7673,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7679,7 +7713,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7719,7 +7753,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7759,7 +7793,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7799,7 +7833,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7839,7 +7873,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -7879,7 +7913,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -7919,7 +7953,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -7959,7 +7993,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -7994,7 +8028,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -8034,7 +8068,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -8074,7 +8108,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -8114,7 +8148,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -8154,7 +8188,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -8194,7 +8228,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -8234,7 +8268,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -8274,7 +8308,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8314,7 +8348,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8354,7 +8388,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8394,7 +8428,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8434,7 +8468,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8504,7 +8538,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8544,7 +8578,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8584,7 +8618,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8624,7 +8658,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8664,7 +8698,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8704,7 +8738,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8744,7 +8778,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8809,7 +8843,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -8849,7 +8883,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -8889,7 +8923,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -8929,7 +8963,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -8969,7 +9003,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -9054,7 +9088,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F197" t="b">
@@ -9094,7 +9128,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -9134,7 +9168,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -9204,7 +9238,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -9244,7 +9278,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9284,7 +9318,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -9324,7 +9358,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9364,7 +9398,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9404,7 +9438,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9444,7 +9478,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9484,7 +9518,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9524,7 +9558,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9594,7 +9628,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9634,7 +9668,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9674,7 +9708,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9714,7 +9748,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9754,7 +9788,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9794,7 +9828,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9834,7 +9868,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -9874,7 +9908,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -9914,7 +9948,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -9954,7 +9988,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -9994,7 +10028,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -10034,7 +10068,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -10074,7 +10108,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -10114,7 +10148,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -10154,7 +10188,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -10194,7 +10228,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -10234,7 +10268,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -10274,7 +10308,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10314,7 +10348,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10354,7 +10388,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10394,7 +10428,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10434,7 +10468,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10474,7 +10508,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10514,7 +10548,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10554,7 +10588,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10639,7 +10673,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10679,7 +10713,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10719,7 +10753,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10754,7 +10788,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10794,7 +10828,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10834,7 +10868,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -10874,7 +10908,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -10914,7 +10948,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -10954,7 +10988,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -10994,7 +11028,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -11034,7 +11068,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -11074,7 +11108,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -11114,7 +11148,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -11154,7 +11188,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -11194,7 +11228,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -11234,7 +11268,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -11274,7 +11308,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11314,7 +11348,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11354,7 +11388,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11424,7 +11458,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11464,7 +11498,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11504,7 +11538,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11544,7 +11578,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11584,7 +11618,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11624,7 +11658,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11664,7 +11698,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11704,7 +11738,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11744,7 +11778,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11784,7 +11818,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11824,7 +11858,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -11859,7 +11893,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -11899,7 +11933,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -11939,7 +11973,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -11979,7 +12013,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -12019,7 +12053,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -12059,7 +12093,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -12099,7 +12133,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -12139,7 +12173,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -12174,7 +12208,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -12214,7 +12248,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -12254,7 +12288,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -12294,7 +12328,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12334,7 +12368,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12374,7 +12408,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12414,7 +12448,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12454,7 +12488,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12494,7 +12528,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12534,7 +12568,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12574,7 +12608,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12614,7 +12648,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12684,7 +12718,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12724,7 +12758,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12764,7 +12798,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12804,7 +12838,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12844,7 +12878,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -12914,7 +12948,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -12954,7 +12988,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -12994,7 +13028,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -13034,7 +13068,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -13074,7 +13108,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -13114,7 +13148,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -13154,7 +13188,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -13194,7 +13228,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -13234,7 +13268,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -13274,7 +13308,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13314,7 +13348,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13354,7 +13388,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13394,7 +13428,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13434,7 +13468,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13474,7 +13508,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13514,7 +13548,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13554,7 +13588,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13594,7 +13628,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13634,7 +13668,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13674,7 +13708,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13744,7 +13778,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -13784,7 +13818,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13824,7 +13858,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -13864,7 +13898,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -13904,7 +13938,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -13944,7 +13978,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -13984,7 +14018,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -14024,7 +14058,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -14064,7 +14098,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -14104,7 +14138,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -14144,7 +14178,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -14184,7 +14218,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -14224,7 +14258,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -14264,7 +14298,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -14304,7 +14338,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14344,7 +14378,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14414,7 +14448,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14454,7 +14488,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14494,7 +14528,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14534,7 +14568,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14574,7 +14608,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14614,7 +14648,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14654,7 +14688,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14694,7 +14728,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14764,7 +14798,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -14864,7 +14898,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -14904,7 +14938,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -14944,7 +14978,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -14984,7 +15018,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -15024,7 +15058,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -15064,7 +15098,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -15104,7 +15138,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -15144,7 +15178,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -15184,7 +15218,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -15224,7 +15258,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -15264,7 +15298,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F355" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1388,6 +1388,40 @@
         <v>4</v>
       </c>
       <c r="J28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>335</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>176</v>
+      </c>
+      <c r="F29" t="n">
+        <v>119</v>
+      </c>
+      <c r="G29" t="n">
+        <v>24</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1475,7 +1509,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1515,7 +1549,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1555,7 +1589,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1595,7 +1629,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1635,7 +1669,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1675,7 +1709,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1715,7 +1749,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1755,7 +1789,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1795,7 +1829,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1835,7 +1869,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1875,7 +1909,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1915,7 +1949,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1955,7 +1989,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -1995,7 +2029,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -2035,7 +2069,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -2075,7 +2109,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -2115,7 +2149,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -2155,7 +2189,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -2195,7 +2229,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -2235,7 +2269,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2305,7 +2339,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -2345,7 +2379,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2385,7 +2419,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2425,7 +2459,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2465,7 +2499,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2505,7 +2539,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2545,7 +2579,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2585,7 +2619,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2625,7 +2659,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2665,7 +2699,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2705,7 +2739,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F33" t="b">
@@ -2770,7 +2804,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2810,7 +2844,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2850,7 +2884,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2890,7 +2924,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2930,7 +2964,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -2970,7 +3004,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -3010,7 +3044,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -3050,7 +3084,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -3090,7 +3124,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -3130,7 +3164,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -3170,7 +3204,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -3210,7 +3244,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -3250,7 +3284,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -3290,7 +3324,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -3330,7 +3364,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -3370,7 +3404,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -3410,7 +3444,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3450,7 +3484,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3490,7 +3524,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3530,7 +3564,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3570,7 +3604,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F55" t="b">
@@ -3640,7 +3674,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3680,7 +3714,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3720,7 +3754,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3760,7 +3794,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3800,7 +3834,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3840,7 +3874,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3880,7 +3914,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3920,7 +3954,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3960,7 +3994,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -4000,7 +4034,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -4040,7 +4074,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -4080,7 +4114,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -4120,7 +4154,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -4160,7 +4194,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -4200,7 +4234,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -4240,7 +4274,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -4280,7 +4314,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -4320,7 +4354,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -4360,7 +4394,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -4400,7 +4434,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -4440,7 +4474,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4480,7 +4514,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4520,7 +4554,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4560,7 +4594,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4600,7 +4634,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4640,7 +4674,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4680,7 +4714,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4720,7 +4754,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4755,7 +4789,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4790,7 +4824,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4830,7 +4864,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4870,7 +4904,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4910,7 +4944,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4950,7 +4984,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -4990,7 +5024,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -5030,7 +5064,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -5070,7 +5104,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -5110,7 +5144,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -5150,7 +5184,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -5190,7 +5224,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -5230,7 +5264,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -5270,7 +5304,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -5310,7 +5344,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -5395,7 +5429,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -5435,7 +5469,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -5475,7 +5509,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5515,7 +5549,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5555,7 +5589,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5595,7 +5629,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5635,7 +5669,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5675,7 +5709,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5715,7 +5749,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5755,7 +5789,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5795,7 +5829,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F111" t="b">
@@ -5865,7 +5899,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5905,7 +5939,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5945,7 +5979,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -5985,7 +6019,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -6025,7 +6059,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -6065,7 +6099,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -6105,7 +6139,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -6145,7 +6179,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -6185,7 +6219,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -6225,7 +6259,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -6265,7 +6299,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -6305,7 +6339,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -6345,7 +6379,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -6385,7 +6419,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -6425,7 +6459,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6465,7 +6499,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6505,7 +6539,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6545,7 +6579,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6585,7 +6619,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6625,7 +6659,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6665,7 +6699,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6705,7 +6739,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6745,7 +6779,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6785,7 +6819,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6825,7 +6859,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6865,7 +6899,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6905,7 +6939,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6945,7 +6979,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -6985,7 +7019,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F141" t="b">
@@ -7055,7 +7089,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -7095,7 +7129,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -7135,7 +7169,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -7175,7 +7209,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -7215,7 +7249,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -7255,7 +7289,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -7295,7 +7329,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -7335,7 +7369,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -7375,7 +7409,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -7415,7 +7449,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7455,7 +7489,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7495,7 +7529,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7535,7 +7569,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7575,7 +7609,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7615,7 +7649,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7655,7 +7689,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7695,7 +7729,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7735,7 +7769,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7775,7 +7809,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7815,7 +7849,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7855,7 +7889,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7895,7 +7929,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7935,7 +7969,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -7975,7 +8009,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -8015,7 +8049,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -8055,7 +8089,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -8095,7 +8129,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -8135,7 +8169,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -8170,7 +8204,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -8210,7 +8244,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -8250,7 +8284,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -8290,7 +8324,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -8330,7 +8364,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -8370,7 +8404,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -8410,7 +8444,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8450,7 +8484,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8490,7 +8524,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8530,7 +8564,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8570,7 +8604,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8610,7 +8644,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F182" t="b">
@@ -8680,7 +8714,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8720,7 +8754,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8760,7 +8794,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8800,7 +8834,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8840,7 +8874,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8880,7 +8914,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8920,7 +8954,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F190" t="b">
@@ -8985,7 +9019,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -9025,7 +9059,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -9065,7 +9099,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -9105,7 +9139,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -9145,7 +9179,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F196" t="b">
@@ -9230,7 +9264,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -9270,7 +9304,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -9310,7 +9344,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F200" t="b">
@@ -9380,7 +9414,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9420,7 +9454,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -9460,7 +9494,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9500,7 +9534,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9540,7 +9574,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9580,7 +9614,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9620,7 +9654,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9660,7 +9694,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9700,7 +9734,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F210" t="b">
@@ -9770,7 +9804,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9810,7 +9844,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9850,7 +9884,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9890,7 +9924,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9930,7 +9964,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -9970,7 +10004,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -10010,7 +10044,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -10050,7 +10084,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -10090,7 +10124,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -10130,7 +10164,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -10170,7 +10204,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -10210,7 +10244,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -10250,7 +10284,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -10290,7 +10324,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -10330,7 +10364,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -10370,7 +10404,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -10410,7 +10444,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10450,7 +10484,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10490,7 +10524,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10530,7 +10564,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10570,7 +10604,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10610,7 +10644,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10650,7 +10684,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10690,7 +10724,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10730,7 +10764,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F236" t="b">
@@ -10815,7 +10849,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10855,7 +10889,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10895,7 +10929,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10930,7 +10964,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -10970,7 +11004,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -11010,7 +11044,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -11050,7 +11084,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -11090,7 +11124,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -11130,7 +11164,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -11170,7 +11204,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -11210,7 +11244,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -11250,7 +11284,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -11290,7 +11324,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -11330,7 +11364,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -11370,7 +11404,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -11410,7 +11444,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11450,7 +11484,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11490,7 +11524,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11530,7 +11564,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F256" t="b">
@@ -11600,7 +11634,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11640,7 +11674,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11680,7 +11714,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11720,7 +11754,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11760,7 +11794,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11800,7 +11834,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11840,7 +11874,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11880,7 +11914,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11920,7 +11954,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11960,7 +11994,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -12000,7 +12034,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -12035,7 +12069,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -12075,7 +12109,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -12115,7 +12149,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -12155,7 +12189,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -12195,7 +12229,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -12235,7 +12269,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -12275,7 +12309,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -12315,7 +12349,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -12350,7 +12384,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -12390,7 +12424,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -12430,7 +12464,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12470,7 +12504,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12510,7 +12544,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12550,7 +12584,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12590,7 +12624,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12630,7 +12664,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12670,7 +12704,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12710,7 +12744,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12750,7 +12784,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12790,7 +12824,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F288" t="b">
@@ -12860,7 +12894,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12900,7 +12934,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12940,7 +12974,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -12980,7 +13014,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -13020,7 +13054,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F294" t="b">
@@ -13090,7 +13124,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -13130,7 +13164,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -13170,7 +13204,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -13210,7 +13244,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -13250,7 +13284,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -13290,7 +13324,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -13330,7 +13364,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -13370,7 +13404,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -13410,7 +13444,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13450,7 +13484,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13490,7 +13524,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13530,7 +13564,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13570,7 +13604,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13610,7 +13644,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13650,7 +13684,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13690,7 +13724,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13730,7 +13764,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13770,7 +13804,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13810,7 +13844,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13850,7 +13884,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F315" t="b">
@@ -13920,7 +13954,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13960,7 +13994,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -14000,7 +14034,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -14040,7 +14074,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -14080,7 +14114,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -14120,7 +14154,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -14160,7 +14194,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -14200,7 +14234,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -14240,7 +14274,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -14280,7 +14314,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -14320,7 +14354,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -14360,7 +14394,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -14400,7 +14434,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -14440,7 +14474,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14480,7 +14514,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14520,7 +14554,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F332" t="b">
@@ -14590,7 +14624,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14630,7 +14664,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14670,7 +14704,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14710,7 +14744,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14750,7 +14784,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14790,7 +14824,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14830,7 +14864,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14870,7 +14904,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F341" t="b">
@@ -14940,7 +14974,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F343" t="b">
@@ -15040,7 +15074,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -15080,7 +15114,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -15120,7 +15154,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -15160,7 +15194,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -15200,7 +15234,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -15240,7 +15274,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -15280,7 +15314,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -15320,7 +15354,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -15360,7 +15394,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -15400,7 +15434,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F355" t="b">
@@ -15440,7 +15474,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="F356" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1422,6 +1422,40 @@
         <v>4</v>
       </c>
       <c r="J29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>335</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>176</v>
+      </c>
+      <c r="F30" t="n">
+        <v>119</v>
+      </c>
+      <c r="G30" t="n">
+        <v>24</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1509,7 +1543,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1549,7 +1583,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1589,7 +1623,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1629,7 +1663,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1669,7 +1703,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1709,7 +1743,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1749,7 +1783,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1789,7 +1823,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1829,7 +1863,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1869,7 +1903,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1909,7 +1943,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1949,7 +1983,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -1989,7 +2023,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -2029,7 +2063,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -2069,7 +2103,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -2109,7 +2143,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -2149,7 +2183,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -2189,7 +2223,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -2229,7 +2263,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -2269,7 +2303,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2339,7 +2373,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -2379,7 +2413,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2419,7 +2453,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2459,7 +2493,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2499,7 +2533,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2539,7 +2573,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2579,7 +2613,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2619,7 +2653,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2659,7 +2693,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2699,7 +2733,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2739,7 +2773,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F33" t="b">
@@ -2804,7 +2838,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F35" t="b">
@@ -2844,7 +2878,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2884,7 +2918,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2924,7 +2958,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -2964,7 +2998,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -3004,7 +3038,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -3044,7 +3078,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -3084,7 +3118,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -3124,7 +3158,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -3164,7 +3198,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -3204,7 +3238,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -3244,7 +3278,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -3284,7 +3318,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -3324,7 +3358,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -3364,7 +3398,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -3404,7 +3438,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -3444,7 +3478,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3484,7 +3518,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3524,7 +3558,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3564,7 +3598,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3604,7 +3638,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F55" t="b">
@@ -3674,7 +3708,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F57" t="b">
@@ -3714,7 +3748,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3754,7 +3788,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3794,7 +3828,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3834,7 +3868,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3874,7 +3908,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3914,7 +3948,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -3954,7 +3988,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -3994,7 +4028,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -4034,7 +4068,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -4074,7 +4108,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -4114,7 +4148,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -4154,7 +4188,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -4194,7 +4228,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -4234,7 +4268,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -4274,7 +4308,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -4314,7 +4348,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -4354,7 +4388,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -4394,7 +4428,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -4434,7 +4468,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -4474,7 +4508,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4514,7 +4548,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4554,7 +4588,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4594,7 +4628,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4634,7 +4668,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4674,7 +4708,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4714,7 +4748,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4754,7 +4788,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4789,7 +4823,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4824,7 +4858,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4864,7 +4898,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4904,7 +4938,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -4944,7 +4978,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -4984,7 +5018,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -5024,7 +5058,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -5064,7 +5098,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -5104,7 +5138,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -5144,7 +5178,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -5184,7 +5218,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -5224,7 +5258,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -5264,7 +5298,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -5304,7 +5338,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -5344,7 +5378,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -5429,7 +5463,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -5469,7 +5503,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F102" t="b">
@@ -5509,7 +5543,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5549,7 +5583,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5589,7 +5623,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5629,7 +5663,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5669,7 +5703,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5709,7 +5743,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5749,7 +5783,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5789,7 +5823,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5829,7 +5863,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F111" t="b">
@@ -5899,7 +5933,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -5939,7 +5973,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F114" t="b">
@@ -5979,7 +6013,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -6019,7 +6053,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -6059,7 +6093,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -6099,7 +6133,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -6139,7 +6173,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -6179,7 +6213,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -6219,7 +6253,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -6259,7 +6293,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -6299,7 +6333,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -6339,7 +6373,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -6379,7 +6413,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -6419,7 +6453,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -6459,7 +6493,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6499,7 +6533,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6539,7 +6573,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6579,7 +6613,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6619,7 +6653,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6659,7 +6693,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6699,7 +6733,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6739,7 +6773,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6779,7 +6813,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6819,7 +6853,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6859,7 +6893,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6899,7 +6933,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -6939,7 +6973,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -6979,7 +7013,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -7019,7 +7053,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F141" t="b">
@@ -7089,7 +7123,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -7129,7 +7163,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -7169,7 +7203,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -7209,7 +7243,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F146" t="b">
@@ -7249,7 +7283,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -7289,7 +7323,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -7329,7 +7363,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -7369,7 +7403,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -7409,7 +7443,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -7449,7 +7483,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7489,7 +7523,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7529,7 +7563,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7569,7 +7603,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7609,7 +7643,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7649,7 +7683,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7689,7 +7723,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7729,7 +7763,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7769,7 +7803,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7809,7 +7843,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7849,7 +7883,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7889,7 +7923,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7929,7 +7963,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -7969,7 +8003,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -8009,7 +8043,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -8049,7 +8083,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -8089,7 +8123,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -8129,7 +8163,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -8169,7 +8203,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -8204,7 +8238,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -8244,7 +8278,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -8284,7 +8318,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -8324,7 +8358,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -8364,7 +8398,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -8404,7 +8438,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -8444,7 +8478,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8484,7 +8518,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8524,7 +8558,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8564,7 +8598,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8604,7 +8638,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8644,7 +8678,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F182" t="b">
@@ -8714,7 +8748,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8754,7 +8788,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8794,7 +8828,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8834,7 +8868,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8874,7 +8908,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F188" t="b">
@@ -8914,7 +8948,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -8954,7 +8988,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F190" t="b">
@@ -9019,7 +9053,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -9059,7 +9093,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -9099,7 +9133,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -9139,7 +9173,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -9179,7 +9213,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F196" t="b">
@@ -9264,7 +9298,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -9304,7 +9338,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -9344,7 +9378,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F200" t="b">
@@ -9414,7 +9448,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9454,7 +9488,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F203" t="b">
@@ -9494,7 +9528,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9534,7 +9568,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9574,7 +9608,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9614,7 +9648,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F207" t="b">
@@ -9654,7 +9688,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9694,7 +9728,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9734,7 +9768,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F210" t="b">
@@ -9804,7 +9838,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9844,7 +9878,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9884,7 +9918,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -9924,7 +9958,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -9964,7 +9998,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -10004,7 +10038,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -10044,7 +10078,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F218" t="b">
@@ -10084,7 +10118,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -10124,7 +10158,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -10164,7 +10198,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -10204,7 +10238,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -10244,7 +10278,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -10284,7 +10318,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -10324,7 +10358,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -10364,7 +10398,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -10404,7 +10438,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -10444,7 +10478,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10484,7 +10518,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10524,7 +10558,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10564,7 +10598,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10604,7 +10638,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10644,7 +10678,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10684,7 +10718,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10724,7 +10758,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10764,7 +10798,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F236" t="b">
@@ -10849,7 +10883,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10889,7 +10923,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10929,7 +10963,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -10964,7 +10998,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -11004,7 +11038,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -11044,7 +11078,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -11084,7 +11118,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -11124,7 +11158,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F245" t="b">
@@ -11164,7 +11198,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -11204,7 +11238,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -11244,7 +11278,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -11284,7 +11318,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -11324,7 +11358,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -11364,7 +11398,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -11404,7 +11438,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -11444,7 +11478,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11484,7 +11518,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11524,7 +11558,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11564,7 +11598,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F256" t="b">
@@ -11634,7 +11668,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11674,7 +11708,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11714,7 +11748,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11754,7 +11788,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11794,7 +11828,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11834,7 +11868,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11874,7 +11908,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -11914,7 +11948,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F265" t="b">
@@ -11954,7 +11988,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -11994,7 +12028,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -12034,7 +12068,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -12069,7 +12103,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -12109,7 +12143,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -12149,7 +12183,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -12189,7 +12223,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -12229,7 +12263,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -12269,7 +12303,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -12309,7 +12343,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -12349,7 +12383,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -12384,7 +12418,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -12424,7 +12458,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -12464,7 +12498,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12504,7 +12538,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12544,7 +12578,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12584,7 +12618,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12624,7 +12658,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12664,7 +12698,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12704,7 +12738,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12744,7 +12778,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12784,7 +12818,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12824,7 +12858,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F288" t="b">
@@ -12894,7 +12928,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -12934,7 +12968,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -12974,7 +13008,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -13014,7 +13048,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -13054,7 +13088,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F294" t="b">
@@ -13124,7 +13158,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -13164,7 +13198,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -13204,7 +13238,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -13244,7 +13278,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -13284,7 +13318,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F300" t="b">
@@ -13324,7 +13358,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -13364,7 +13398,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -13404,7 +13438,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -13444,7 +13478,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13484,7 +13518,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13524,7 +13558,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13564,7 +13598,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F307" t="b">
@@ -13604,7 +13638,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13644,7 +13678,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13684,7 +13718,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13724,7 +13758,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13764,7 +13798,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13804,7 +13838,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13844,7 +13878,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13884,7 +13918,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F315" t="b">
@@ -13954,7 +13988,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -13994,7 +14028,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -14034,7 +14068,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -14074,7 +14108,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -14114,7 +14148,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -14154,7 +14188,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -14194,7 +14228,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -14234,7 +14268,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -14274,7 +14308,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -14314,7 +14348,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -14354,7 +14388,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -14394,7 +14428,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -14434,7 +14468,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -14474,7 +14508,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14514,7 +14548,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F331" t="b">
@@ -14554,7 +14588,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F332" t="b">
@@ -14624,7 +14658,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14664,7 +14698,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14704,7 +14738,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14744,7 +14778,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14784,7 +14818,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14824,7 +14858,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14864,7 +14898,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14904,7 +14938,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F341" t="b">
@@ -14974,7 +15008,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F343" t="b">
@@ -15074,7 +15108,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -15114,7 +15148,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -15154,7 +15188,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -15194,7 +15228,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F349" t="b">
@@ -15234,7 +15268,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -15274,7 +15308,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -15314,7 +15348,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -15354,7 +15388,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -15394,7 +15428,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -15434,7 +15468,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F355" t="b">
@@ -15474,7 +15508,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F356" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1490,6 +1490,40 @@
         <v>4</v>
       </c>
       <c r="J31" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>352</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>177</v>
+      </c>
+      <c r="F32" t="n">
+        <v>135</v>
+      </c>
+      <c r="G32" t="n">
+        <v>24</v>
+      </c>
+      <c r="H32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1577,7 +1611,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1617,7 +1651,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1657,7 +1691,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1697,7 +1731,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1737,7 +1771,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1777,7 +1811,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1817,7 +1851,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1857,7 +1891,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1897,7 +1931,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1937,7 +1971,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1977,7 +2011,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -2017,7 +2051,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -2057,7 +2091,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -2097,7 +2131,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -2137,7 +2171,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -2177,7 +2211,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -2217,7 +2251,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -2257,7 +2291,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -2297,7 +2331,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -2337,7 +2371,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2407,7 +2441,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -2447,7 +2481,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2487,7 +2521,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2527,7 +2561,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2567,7 +2601,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2607,7 +2641,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2647,7 +2681,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2687,7 +2721,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2727,7 +2761,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2767,7 +2801,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2807,7 +2841,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F33" t="b">
@@ -2847,7 +2881,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2912,7 +2946,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2952,7 +2986,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -2992,7 +3026,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -3032,7 +3066,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -3072,7 +3106,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -3112,7 +3146,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -3152,7 +3186,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -3192,7 +3226,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -3232,7 +3266,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -3272,7 +3306,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -3312,7 +3346,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -3352,7 +3386,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -3392,7 +3426,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -3432,7 +3466,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -3472,7 +3506,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -3512,7 +3546,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3552,7 +3586,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3592,7 +3626,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3632,7 +3666,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3672,7 +3706,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F55" t="b">
@@ -3712,7 +3746,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3782,7 +3816,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3822,7 +3856,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3862,7 +3896,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3902,7 +3936,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3942,7 +3976,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -3982,7 +4016,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -4022,7 +4056,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -4062,7 +4096,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -4102,7 +4136,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -4142,7 +4176,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -4182,7 +4216,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -4222,7 +4256,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -4262,7 +4296,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -4302,7 +4336,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -4342,7 +4376,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -4382,7 +4416,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -4422,7 +4456,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -4462,7 +4496,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -4502,7 +4536,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -4542,7 +4576,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4582,7 +4616,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4622,7 +4656,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4662,7 +4696,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4702,7 +4736,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4742,7 +4776,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4782,7 +4816,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4822,7 +4856,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4862,7 +4896,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4897,7 +4931,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4932,7 +4966,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -4972,7 +5006,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -5012,7 +5046,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -5052,7 +5086,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -5092,7 +5126,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -5132,7 +5166,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -5172,7 +5206,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -5212,7 +5246,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -5252,7 +5286,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -5292,7 +5326,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -5332,7 +5366,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -5372,7 +5406,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -5412,7 +5446,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -5452,7 +5486,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -5492,7 +5526,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -5577,7 +5611,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5617,7 +5651,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5657,7 +5691,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5697,7 +5731,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5737,7 +5771,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5777,7 +5811,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5817,7 +5851,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5857,7 +5891,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5897,7 +5931,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F111" t="b">
@@ -5937,7 +5971,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -5977,7 +6011,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -6047,7 +6081,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -6087,7 +6121,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -6127,7 +6161,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -6167,7 +6201,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -6207,7 +6241,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -6247,7 +6281,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -6287,7 +6321,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -6327,7 +6361,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -6367,7 +6401,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -6407,7 +6441,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -6447,7 +6481,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -6487,7 +6521,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -6527,7 +6561,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6567,7 +6601,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6607,7 +6641,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6647,7 +6681,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6687,7 +6721,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6727,7 +6761,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6767,7 +6801,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6807,7 +6841,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6847,7 +6881,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6887,7 +6921,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6927,7 +6961,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -6967,7 +7001,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -7007,7 +7041,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -7047,7 +7081,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -7087,7 +7121,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F141" t="b">
@@ -7127,7 +7161,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -7167,7 +7201,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -7207,7 +7241,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -7247,7 +7281,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -7317,7 +7351,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -7357,7 +7391,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -7397,7 +7431,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -7437,7 +7471,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -7477,7 +7511,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -7517,7 +7551,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7557,7 +7591,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7597,7 +7631,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7637,7 +7671,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7677,7 +7711,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7717,7 +7751,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7757,7 +7791,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7797,7 +7831,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7837,7 +7871,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7877,7 +7911,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7917,7 +7951,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7957,7 +7991,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -7997,7 +8031,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -8037,7 +8071,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -8077,7 +8111,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -8117,7 +8151,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -8157,7 +8191,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -8197,7 +8231,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -8237,7 +8271,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -8277,7 +8311,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -8317,7 +8351,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -8357,7 +8391,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -8397,7 +8431,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -8437,7 +8471,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -8472,7 +8506,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -8512,7 +8546,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8552,7 +8586,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8592,7 +8626,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8632,7 +8666,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8672,7 +8706,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8712,7 +8746,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F182" t="b">
@@ -8752,7 +8786,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8792,7 +8826,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8832,7 +8866,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8872,7 +8906,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8912,7 +8946,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -8982,7 +9016,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -9022,7 +9056,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F190" t="b">
@@ -9062,7 +9096,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -9102,7 +9136,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -9142,7 +9176,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -9182,7 +9216,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -9222,7 +9256,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -9262,7 +9296,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F196" t="b">
@@ -9327,7 +9361,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -9367,7 +9401,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -9407,7 +9441,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F200" t="b">
@@ -9447,7 +9481,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -9487,7 +9521,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9572,7 +9606,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9612,7 +9646,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9652,7 +9686,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9722,7 +9756,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9762,7 +9796,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9802,7 +9836,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F210" t="b">
@@ -9842,7 +9876,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9882,7 +9916,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9922,7 +9956,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9962,7 +9996,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -10002,7 +10036,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -10042,7 +10076,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -10082,7 +10116,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -10152,7 +10186,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -10192,7 +10226,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -10232,7 +10266,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -10272,7 +10306,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -10312,7 +10346,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -10352,7 +10386,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -10392,7 +10426,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -10432,7 +10466,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -10472,7 +10506,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -10512,7 +10546,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10552,7 +10586,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10592,7 +10626,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10632,7 +10666,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10672,7 +10706,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10712,7 +10746,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10752,7 +10786,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10792,7 +10826,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10832,7 +10866,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F236" t="b">
@@ -10872,7 +10906,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10912,7 +10946,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10952,7 +10986,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -10992,7 +11026,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -11032,7 +11066,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -11072,7 +11106,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -11112,7 +11146,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -11152,7 +11186,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -11237,7 +11271,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -11277,7 +11311,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -11317,7 +11351,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -11352,7 +11386,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -11392,7 +11426,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -11432,7 +11466,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -11472,7 +11506,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -11512,7 +11546,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11552,7 +11586,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11592,7 +11626,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11632,7 +11666,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F256" t="b">
@@ -11672,7 +11706,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11712,7 +11746,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11752,7 +11786,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11792,7 +11826,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11832,7 +11866,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11872,7 +11906,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11912,7 +11946,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11952,7 +11986,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -12022,7 +12056,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -12062,7 +12096,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -12102,7 +12136,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -12142,7 +12176,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -12182,7 +12216,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -12222,7 +12256,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -12262,7 +12296,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -12302,7 +12336,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -12342,7 +12376,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -12382,7 +12416,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -12422,7 +12456,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -12457,7 +12491,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -12497,7 +12531,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -12537,7 +12571,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12577,7 +12611,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12617,7 +12651,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12657,7 +12691,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12697,7 +12731,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12737,7 +12771,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12777,7 +12811,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12817,7 +12851,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12852,7 +12886,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12892,7 +12926,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F288" t="b">
@@ -12932,7 +12966,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -12972,7 +13006,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -13012,7 +13046,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -13052,7 +13086,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -13092,7 +13126,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -13132,7 +13166,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F294" t="b">
@@ -13172,7 +13206,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -13212,7 +13246,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -13252,7 +13286,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -13292,7 +13326,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -13332,7 +13366,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -13402,7 +13436,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -13442,7 +13476,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -13482,7 +13516,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -13522,7 +13556,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13562,7 +13596,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13602,7 +13636,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13672,7 +13706,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13712,7 +13746,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13752,7 +13786,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13792,7 +13826,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13832,7 +13866,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13872,7 +13906,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13912,7 +13946,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13952,7 +13986,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F315" t="b">
@@ -13992,7 +14026,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -14032,7 +14066,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -14072,7 +14106,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -14112,7 +14146,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -14152,7 +14186,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -14192,7 +14226,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -14232,7 +14266,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -14272,7 +14306,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -14312,7 +14346,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -14352,7 +14386,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -14392,7 +14426,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -14432,7 +14466,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -14472,7 +14506,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -14512,7 +14546,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -14552,7 +14586,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14622,7 +14656,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F332" t="b">
@@ -14662,7 +14696,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14702,7 +14736,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14742,7 +14776,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14782,7 +14816,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14822,7 +14856,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14862,7 +14896,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14902,7 +14936,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14942,7 +14976,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -14982,7 +15016,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F341" t="b">
@@ -15022,7 +15056,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -15062,7 +15096,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F343" t="b">
@@ -15102,7 +15136,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F344" t="b">
@@ -15142,7 +15176,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -15182,7 +15216,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -15222,7 +15256,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -15262,7 +15296,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -15332,7 +15366,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -15372,7 +15406,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -15412,7 +15446,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -15452,7 +15486,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -15492,7 +15526,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -15532,7 +15566,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F355" t="b">
@@ -15572,7 +15606,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F356" t="b">
@@ -15612,7 +15646,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F357" t="b">
@@ -15682,7 +15716,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F359" t="b">
@@ -15782,7 +15816,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F362" t="b">
@@ -15822,7 +15856,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F363" t="b">
@@ -15862,7 +15896,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F364" t="b">
@@ -15902,7 +15936,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F365" t="b">
@@ -15942,7 +15976,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F366" t="b">
@@ -15982,7 +16016,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F367" t="b">
@@ -16022,7 +16056,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F368" t="b">
@@ -16062,7 +16096,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F369" t="b">
@@ -16102,7 +16136,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F370" t="b">
@@ -16142,7 +16176,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F371" t="b">
@@ -16182,7 +16216,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F372" t="b">
@@ -16222,7 +16256,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F373" t="b">

--- a/data/opter_tenants.xlsx
+++ b/data/opter_tenants.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1524,6 +1524,40 @@
         <v>4</v>
       </c>
       <c r="J32" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>352</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>177</v>
+      </c>
+      <c r="F33" t="n">
+        <v>135</v>
+      </c>
+      <c r="G33" t="n">
+        <v>24</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1611,7 +1645,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F2" t="b">
@@ -1651,7 +1685,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1691,7 +1725,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F4" t="b">
@@ -1731,7 +1765,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1771,7 +1805,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F6" t="b">
@@ -1811,7 +1845,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F7" t="b">
@@ -1851,7 +1885,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1891,7 +1925,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F9" t="b">
@@ -1931,7 +1965,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1971,7 +2005,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -2011,7 +2045,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -2051,7 +2085,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -2091,7 +2125,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -2131,7 +2165,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -2171,7 +2205,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F16" t="b">
@@ -2211,7 +2245,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F17" t="b">
@@ -2251,7 +2285,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F18" t="b">
@@ -2291,7 +2325,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F19" t="b">
@@ -2331,7 +2365,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F20" t="b">
@@ -2371,7 +2405,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F21" t="b">
@@ -2441,7 +2475,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F23" t="b">
@@ -2481,7 +2515,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F24" t="b">
@@ -2521,7 +2555,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F25" t="b">
@@ -2561,7 +2595,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -2601,7 +2635,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -2641,7 +2675,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -2681,7 +2715,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -2721,7 +2755,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -2761,7 +2795,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -2801,7 +2835,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -2841,7 +2875,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F33" t="b">
@@ -2881,7 +2915,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F34" t="b">
@@ -2946,7 +2980,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F36" t="b">
@@ -2986,7 +3020,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -3026,7 +3060,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -3066,7 +3100,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -3106,7 +3140,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -3146,7 +3180,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -3186,7 +3220,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F42" t="b">
@@ -3226,7 +3260,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F43" t="b">
@@ -3266,7 +3300,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F44" t="b">
@@ -3306,7 +3340,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F45" t="b">
@@ -3346,7 +3380,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F46" t="b">
@@ -3386,7 +3420,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F47" t="b">
@@ -3426,7 +3460,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F48" t="b">
@@ -3466,7 +3500,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F49" t="b">
@@ -3506,7 +3540,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F50" t="b">
@@ -3546,7 +3580,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F51" t="b">
@@ -3586,7 +3620,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F52" t="b">
@@ -3626,7 +3660,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F53" t="b">
@@ -3666,7 +3700,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F54" t="b">
@@ -3706,7 +3740,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F55" t="b">
@@ -3746,7 +3780,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F56" t="b">
@@ -3816,7 +3850,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F58" t="b">
@@ -3856,7 +3890,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F59" t="b">
@@ -3896,7 +3930,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F60" t="b">
@@ -3936,7 +3970,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F61" t="b">
@@ -3976,7 +4010,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F62" t="b">
@@ -4016,7 +4050,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F63" t="b">
@@ -4056,7 +4090,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F64" t="b">
@@ -4096,7 +4130,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F65" t="b">
@@ -4136,7 +4170,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F66" t="b">
@@ -4176,7 +4210,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F67" t="b">
@@ -4216,7 +4250,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F68" t="b">
@@ -4256,7 +4290,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F69" t="b">
@@ -4296,7 +4330,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F70" t="b">
@@ -4336,7 +4370,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F71" t="b">
@@ -4376,7 +4410,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F72" t="b">
@@ -4416,7 +4450,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F73" t="b">
@@ -4456,7 +4490,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F74" t="b">
@@ -4496,7 +4530,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F75" t="b">
@@ -4536,7 +4570,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F76" t="b">
@@ -4576,7 +4610,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F77" t="b">
@@ -4616,7 +4650,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F78" t="b">
@@ -4656,7 +4690,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F79" t="b">
@@ -4696,7 +4730,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F80" t="b">
@@ -4736,7 +4770,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F81" t="b">
@@ -4776,7 +4810,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F82" t="b">
@@ -4816,7 +4850,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F83" t="b">
@@ -4856,7 +4890,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F84" t="b">
@@ -4896,7 +4930,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F85" t="b">
@@ -4931,7 +4965,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F86" t="b">
@@ -4966,7 +5000,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F87" t="b">
@@ -5006,7 +5040,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F88" t="b">
@@ -5046,7 +5080,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F89" t="b">
@@ -5086,7 +5120,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F90" t="b">
@@ -5126,7 +5160,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F91" t="b">
@@ -5166,7 +5200,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F92" t="b">
@@ -5206,7 +5240,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F93" t="b">
@@ -5246,7 +5280,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F94" t="b">
@@ -5286,7 +5320,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F95" t="b">
@@ -5326,7 +5360,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F96" t="b">
@@ -5366,7 +5400,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F97" t="b">
@@ -5406,7 +5440,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F98" t="b">
@@ -5446,7 +5480,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F99" t="b">
@@ -5486,7 +5520,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F100" t="b">
@@ -5526,7 +5560,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F101" t="b">
@@ -5611,7 +5645,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F103" t="b">
@@ -5651,7 +5685,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F104" t="b">
@@ -5691,7 +5725,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F105" t="b">
@@ -5731,7 +5765,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F106" t="b">
@@ -5771,7 +5805,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F107" t="b">
@@ -5811,7 +5845,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F108" t="b">
@@ -5851,7 +5885,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F109" t="b">
@@ -5891,7 +5925,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F110" t="b">
@@ -5931,7 +5965,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F111" t="b">
@@ -5971,7 +6005,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F112" t="b">
@@ -6011,7 +6045,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F113" t="b">
@@ -6081,7 +6115,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F115" t="b">
@@ -6121,7 +6155,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F116" t="b">
@@ -6161,7 +6195,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F117" t="b">
@@ -6201,7 +6235,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F118" t="b">
@@ -6241,7 +6275,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F119" t="b">
@@ -6281,7 +6315,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F120" t="b">
@@ -6321,7 +6355,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F121" t="b">
@@ -6361,7 +6395,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F122" t="b">
@@ -6401,7 +6435,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F123" t="b">
@@ -6441,7 +6475,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F124" t="b">
@@ -6481,7 +6515,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F125" t="b">
@@ -6521,7 +6555,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F126" t="b">
@@ -6561,7 +6595,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F127" t="b">
@@ -6601,7 +6635,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F128" t="b">
@@ -6641,7 +6675,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F129" t="b">
@@ -6681,7 +6715,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F130" t="b">
@@ -6721,7 +6755,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F131" t="b">
@@ -6761,7 +6795,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F132" t="b">
@@ -6801,7 +6835,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F133" t="b">
@@ -6841,7 +6875,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F134" t="b">
@@ -6881,7 +6915,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F135" t="b">
@@ -6921,7 +6955,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F136" t="b">
@@ -6961,7 +6995,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F137" t="b">
@@ -7001,7 +7035,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -7041,7 +7075,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F139" t="b">
@@ -7081,7 +7115,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F140" t="b">
@@ -7121,7 +7155,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F141" t="b">
@@ -7161,7 +7195,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F142" t="b">
@@ -7201,7 +7235,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F143" t="b">
@@ -7241,7 +7275,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F144" t="b">
@@ -7281,7 +7315,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F145" t="b">
@@ -7351,7 +7385,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F147" t="b">
@@ -7391,7 +7425,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F148" t="b">
@@ -7431,7 +7465,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F149" t="b">
@@ -7471,7 +7505,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F150" t="b">
@@ -7511,7 +7545,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F151" t="b">
@@ -7551,7 +7585,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F152" t="b">
@@ -7591,7 +7625,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F153" t="b">
@@ -7631,7 +7665,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F154" t="b">
@@ -7671,7 +7705,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F155" t="b">
@@ -7711,7 +7745,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F156" t="b">
@@ -7751,7 +7785,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F157" t="b">
@@ -7791,7 +7825,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F158" t="b">
@@ -7831,7 +7865,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F159" t="b">
@@ -7871,7 +7905,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F160" t="b">
@@ -7911,7 +7945,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F161" t="b">
@@ -7951,7 +7985,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F162" t="b">
@@ -7991,7 +8025,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F163" t="b">
@@ -8031,7 +8065,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F164" t="b">
@@ -8071,7 +8105,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F165" t="b">
@@ -8111,7 +8145,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F166" t="b">
@@ -8151,7 +8185,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F167" t="b">
@@ -8191,7 +8225,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F168" t="b">
@@ -8231,7 +8265,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F169" t="b">
@@ -8271,7 +8305,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F170" t="b">
@@ -8311,7 +8345,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F171" t="b">
@@ -8351,7 +8385,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F172" t="b">
@@ -8391,7 +8425,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F173" t="b">
@@ -8431,7 +8465,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F174" t="b">
@@ -8471,7 +8505,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F175" t="b">
@@ -8506,7 +8540,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F176" t="b">
@@ -8546,7 +8580,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F177" t="b">
@@ -8586,7 +8620,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F178" t="b">
@@ -8626,7 +8660,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F179" t="b">
@@ -8666,7 +8700,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F180" t="b">
@@ -8706,7 +8740,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F181" t="b">
@@ -8746,7 +8780,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F182" t="b">
@@ -8786,7 +8820,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F183" t="b">
@@ -8826,7 +8860,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F184" t="b">
@@ -8866,7 +8900,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F185" t="b">
@@ -8906,7 +8940,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F186" t="b">
@@ -8946,7 +8980,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F187" t="b">
@@ -9016,7 +9050,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F189" t="b">
@@ -9056,7 +9090,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F190" t="b">
@@ -9096,7 +9130,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F191" t="b">
@@ -9136,7 +9170,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F192" t="b">
@@ -9176,7 +9210,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F193" t="b">
@@ -9216,7 +9250,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F194" t="b">
@@ -9256,7 +9290,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F195" t="b">
@@ -9296,7 +9330,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F196" t="b">
@@ -9361,7 +9395,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F198" t="b">
@@ -9401,7 +9435,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F199" t="b">
@@ -9441,7 +9475,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F200" t="b">
@@ -9481,7 +9515,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F201" t="b">
@@ -9521,7 +9555,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F202" t="b">
@@ -9606,7 +9640,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F204" t="b">
@@ -9646,7 +9680,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F205" t="b">
@@ -9686,7 +9720,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F206" t="b">
@@ -9756,7 +9790,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F208" t="b">
@@ -9796,7 +9830,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F209" t="b">
@@ -9836,7 +9870,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F210" t="b">
@@ -9876,7 +9910,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F211" t="b">
@@ -9916,7 +9950,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F212" t="b">
@@ -9956,7 +9990,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F213" t="b">
@@ -9996,7 +10030,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F214" t="b">
@@ -10036,7 +10070,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F215" t="b">
@@ -10076,7 +10110,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F216" t="b">
@@ -10116,7 +10150,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F217" t="b">
@@ -10186,7 +10220,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F219" t="b">
@@ -10226,7 +10260,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F220" t="b">
@@ -10266,7 +10300,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F221" t="b">
@@ -10306,7 +10340,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F222" t="b">
@@ -10346,7 +10380,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F223" t="b">
@@ -10386,7 +10420,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F224" t="b">
@@ -10426,7 +10460,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F225" t="b">
@@ -10466,7 +10500,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F226" t="b">
@@ -10506,7 +10540,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F227" t="b">
@@ -10546,7 +10580,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F228" t="b">
@@ -10586,7 +10620,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F229" t="b">
@@ -10626,7 +10660,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F230" t="b">
@@ -10666,7 +10700,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F231" t="b">
@@ -10706,7 +10740,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F232" t="b">
@@ -10746,7 +10780,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F233" t="b">
@@ -10786,7 +10820,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F234" t="b">
@@ -10826,7 +10860,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F235" t="b">
@@ -10866,7 +10900,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F236" t="b">
@@ -10906,7 +10940,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F237" t="b">
@@ -10946,7 +10980,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F238" t="b">
@@ -10986,7 +11020,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F239" t="b">
@@ -11026,7 +11060,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F240" t="b">
@@ -11066,7 +11100,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F241" t="b">
@@ -11106,7 +11140,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F242" t="b">
@@ -11146,7 +11180,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F243" t="b">
@@ -11186,7 +11220,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F244" t="b">
@@ -11271,7 +11305,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F246" t="b">
@@ -11311,7 +11345,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F247" t="b">
@@ -11351,7 +11385,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F248" t="b">
@@ -11386,7 +11420,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F249" t="b">
@@ -11426,7 +11460,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F250" t="b">
@@ -11466,7 +11500,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F251" t="b">
@@ -11506,7 +11540,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F252" t="b">
@@ -11546,7 +11580,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F253" t="b">
@@ -11586,7 +11620,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F254" t="b">
@@ -11626,7 +11660,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F255" t="b">
@@ -11666,7 +11700,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F256" t="b">
@@ -11706,7 +11740,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F257" t="b">
@@ -11746,7 +11780,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F258" t="b">
@@ -11786,7 +11820,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F259" t="b">
@@ -11826,7 +11860,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F260" t="b">
@@ -11866,7 +11900,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F261" t="b">
@@ -11906,7 +11940,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F262" t="b">
@@ -11946,7 +11980,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F263" t="b">
@@ -11986,7 +12020,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F264" t="b">
@@ -12056,7 +12090,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F266" t="b">
@@ -12096,7 +12130,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F267" t="b">
@@ -12136,7 +12170,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F268" t="b">
@@ -12176,7 +12210,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F269" t="b">
@@ -12216,7 +12250,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F270" t="b">
@@ -12256,7 +12290,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F271" t="b">
@@ -12296,7 +12330,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F272" t="b">
@@ -12336,7 +12370,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F273" t="b">
@@ -12376,7 +12410,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F274" t="b">
@@ -12416,7 +12450,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F275" t="b">
@@ -12456,7 +12490,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F276" t="b">
@@ -12491,7 +12525,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F277" t="b">
@@ -12531,7 +12565,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F278" t="b">
@@ -12571,7 +12605,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F279" t="b">
@@ -12611,7 +12645,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F280" t="b">
@@ -12651,7 +12685,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F281" t="b">
@@ -12691,7 +12725,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F282" t="b">
@@ -12731,7 +12765,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F283" t="b">
@@ -12771,7 +12805,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F284" t="b">
@@ -12811,7 +12845,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F285" t="b">
@@ -12851,7 +12885,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F286" t="b">
@@ -12886,7 +12920,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F287" t="b">
@@ -12926,7 +12960,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F288" t="b">
@@ -12966,7 +13000,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F289" t="b">
@@ -13006,7 +13040,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F290" t="b">
@@ -13046,7 +13080,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F291" t="b">
@@ -13086,7 +13120,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F292" t="b">
@@ -13126,7 +13160,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F293" t="b">
@@ -13166,7 +13200,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F294" t="b">
@@ -13206,7 +13240,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F295" t="b">
@@ -13246,7 +13280,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F296" t="b">
@@ -13286,7 +13320,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F297" t="b">
@@ -13326,7 +13360,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F298" t="b">
@@ -13366,7 +13400,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F299" t="b">
@@ -13436,7 +13470,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F301" t="b">
@@ -13476,7 +13510,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F302" t="b">
@@ -13516,7 +13550,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F303" t="b">
@@ -13556,7 +13590,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F304" t="b">
@@ -13596,7 +13630,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F305" t="b">
@@ -13636,7 +13670,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F306" t="b">
@@ -13706,7 +13740,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F308" t="b">
@@ -13746,7 +13780,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F309" t="b">
@@ -13786,7 +13820,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F310" t="b">
@@ -13826,7 +13860,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F311" t="b">
@@ -13866,7 +13900,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F312" t="b">
@@ -13906,7 +13940,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F313" t="b">
@@ -13946,7 +13980,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F314" t="b">
@@ -13986,7 +14020,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F315" t="b">
@@ -14026,7 +14060,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F316" t="b">
@@ -14066,7 +14100,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F317" t="b">
@@ -14106,7 +14140,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F318" t="b">
@@ -14146,7 +14180,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F319" t="b">
@@ -14186,7 +14220,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F320" t="b">
@@ -14226,7 +14260,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F321" t="b">
@@ -14266,7 +14300,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F322" t="b">
@@ -14306,7 +14340,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F323" t="b">
@@ -14346,7 +14380,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F324" t="b">
@@ -14386,7 +14420,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F325" t="b">
@@ -14426,7 +14460,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F326" t="b">
@@ -14466,7 +14500,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F327" t="b">
@@ -14506,7 +14540,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F328" t="b">
@@ -14546,7 +14580,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F329" t="b">
@@ -14586,7 +14620,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F330" t="b">
@@ -14656,7 +14690,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F332" t="b">
@@ -14696,7 +14730,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F333" t="b">
@@ -14736,7 +14770,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F334" t="b">
@@ -14776,7 +14810,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F335" t="b">
@@ -14816,7 +14850,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F336" t="b">
@@ -14856,7 +14890,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F337" t="b">
@@ -14896,7 +14930,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -14936,7 +14970,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F339" t="b">
@@ -14976,7 +15010,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F340" t="b">
@@ -15016,7 +15050,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F341" t="b">
@@ -15056,7 +15090,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F342" t="b">
@@ -15096,7 +15130,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F343" t="b">
@@ -15136,7 +15170,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F344" t="b">
@@ -15176,7 +15210,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F345" t="b">
@@ -15216,7 +15250,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F346" t="b">
@@ -15256,7 +15290,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F347" t="b">
@@ -15296,7 +15330,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F348" t="b">
@@ -15366,7 +15400,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F350" t="b">
@@ -15406,7 +15440,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F351" t="b">
@@ -15446,7 +15480,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F352" t="b">
@@ -15486,7 +15520,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F353" t="b">
@@ -15526,7 +15560,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F354" t="b">
@@ -15566,7 +15600,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F355" t="b">
@@ -15606,7 +15640,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F356" t="b">
@@ -15646,7 +15680,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F357" t="b">
@@ -15716,7 +15750,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F359" t="b">
@@ -15816,7 +15850,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F362" t="b">
@@ -15856,7 +15890,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F363" t="b">
@@ -15896,7 +15930,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F364" t="b">
@@ -15936,7 +15970,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F365" t="b">
@@ -15976,7 +16010,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F366" t="b">
@@ -16016,7 +16050,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F367" t="b">
@@ -16056,7 +16090,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F368" t="b">
@@ -16096,7 +16130,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F369" t="b">
@@ -16136,7 +16170,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F370" t="b">
@@ -16176,7 +16210,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F371" t="b">
@@ -16216,7 +16250,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F372" t="b">
@@ -16256,7 +16290,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="F373" t="b">
